--- a/data/macro/USA/Logistic manager index.xlsx
+++ b/data/macro/USA/Logistic manager index.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{393C0D64-1010-49B8-9437-51FC703A6791}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{066F31FE-AE65-497A-B0AA-8240B0C23207}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="14">
   <si>
     <t>Inventory Costs</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -77,6 +77,10 @@
   </si>
   <si>
     <t>UTC+0</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Time</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -182,7 +186,7 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -216,6 +220,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="쉼표" xfId="1" builtinId="3"/>
@@ -519,7 +526,9 @@
       <c r="B1" s="7" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="6"/>
+      <c r="C1" s="13" t="s">
+        <v>13</v>
+      </c>
       <c r="D1" s="6" t="s">
         <v>11</v>
       </c>

--- a/data/macro/USA/Logistic manager index.xlsx
+++ b/data/macro/USA/Logistic manager index.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{066F31FE-AE65-497A-B0AA-8240B0C23207}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A9AB8A9-3448-482C-A42D-C699905D9C88}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="125" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="14">
   <si>
     <t>Inventory Costs</t>
     <phoneticPr fontId="5" type="noConversion"/>
@@ -88,10 +88,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="177" formatCode="[$-409]h:mm\ AM/PM;@"/>
     <numFmt numFmtId="178" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="179" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -197,12 +198,6 @@
     <xf numFmtId="178" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="176" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -210,18 +205,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="1" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="177" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="4" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -505,46 +506,46 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I113"/>
+  <dimension ref="A1:I114"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="10.875" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11.125" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="11.125" style="2" customWidth="1"/>
-    <col min="5" max="5" width="8" style="9"/>
-    <col min="6" max="6" width="10.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="16" style="10" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="18.375" style="10" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.5" style="10" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="8"/>
+    <col min="5" max="5" width="8" style="12"/>
+    <col min="6" max="6" width="10.5" style="13" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16" style="13" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="18.375" style="13" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.5" style="13" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A1" s="7" t="s">
+      <c r="A1" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="9" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="10" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="11" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="11" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="11" t="s">
         <v>0</v>
       </c>
     </row>
@@ -558,17 +559,17 @@
       <c r="D2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="9">
+      <c r="E2" s="12">
         <v>63.9</v>
       </c>
-      <c r="F2" s="9"/>
-      <c r="G2" s="9">
+      <c r="F2" s="12"/>
+      <c r="G2" s="12">
         <v>76.900000000000006</v>
       </c>
-      <c r="H2" s="9">
+      <c r="H2" s="12">
         <v>65.599999999999994</v>
       </c>
-      <c r="I2" s="9">
+      <c r="I2" s="12">
         <v>67.599999999999994</v>
       </c>
     </row>
@@ -582,17 +583,17 @@
       <c r="D3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="9">
+      <c r="E3" s="12">
         <v>54.9</v>
       </c>
-      <c r="F3" s="9"/>
-      <c r="G3" s="9">
+      <c r="F3" s="12"/>
+      <c r="G3" s="12">
         <v>68.900000000000006</v>
       </c>
-      <c r="H3" s="9">
+      <c r="H3" s="12">
         <v>65.099999999999994</v>
       </c>
-      <c r="I3" s="9">
+      <c r="I3" s="12">
         <v>59.5</v>
       </c>
     </row>
@@ -606,17 +607,17 @@
       <c r="D4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="9">
+      <c r="E4" s="12">
         <v>62.9</v>
       </c>
-      <c r="F4" s="9"/>
-      <c r="G4" s="9">
+      <c r="F4" s="12"/>
+      <c r="G4" s="12">
         <v>71.8</v>
       </c>
-      <c r="H4" s="9">
+      <c r="H4" s="12">
         <v>67.2</v>
       </c>
-      <c r="I4" s="9">
+      <c r="I4" s="12">
         <v>65.5</v>
       </c>
     </row>
@@ -630,17 +631,17 @@
       <c r="D5" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="12">
         <v>62.9</v>
       </c>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9">
+      <c r="F5" s="12"/>
+      <c r="G5" s="12">
         <v>71.8</v>
       </c>
-      <c r="H5" s="9">
+      <c r="H5" s="12">
         <v>67.2</v>
       </c>
-      <c r="I5" s="9">
+      <c r="I5" s="12">
         <v>65.5</v>
       </c>
     </row>
@@ -654,17 +655,17 @@
       <c r="D6" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="9">
+      <c r="E6" s="12">
         <v>66</v>
       </c>
-      <c r="F6" s="9"/>
-      <c r="G6" s="9">
+      <c r="F6" s="12"/>
+      <c r="G6" s="12">
         <v>69.7</v>
       </c>
-      <c r="H6" s="9">
+      <c r="H6" s="12">
         <v>75.3</v>
       </c>
-      <c r="I6" s="9">
+      <c r="I6" s="12">
         <v>65.400000000000006</v>
       </c>
     </row>
@@ -678,17 +679,17 @@
       <c r="D7" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="12">
         <v>66</v>
       </c>
-      <c r="F7" s="9"/>
-      <c r="G7" s="9">
+      <c r="F7" s="12"/>
+      <c r="G7" s="12">
         <v>69.7</v>
       </c>
-      <c r="H7" s="9">
+      <c r="H7" s="12">
         <v>75.3</v>
       </c>
-      <c r="I7" s="9">
+      <c r="I7" s="12">
         <v>65.400000000000006</v>
       </c>
     </row>
@@ -702,17 +703,17 @@
       <c r="D8" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E8" s="9">
+      <c r="E8" s="12">
         <v>65.599999999999994</v>
       </c>
-      <c r="F8" s="9"/>
-      <c r="G8" s="9">
+      <c r="F8" s="12"/>
+      <c r="G8" s="12">
         <v>61</v>
       </c>
-      <c r="H8" s="9">
+      <c r="H8" s="12">
         <v>70.5</v>
       </c>
-      <c r="I8" s="9">
+      <c r="I8" s="12">
         <v>68.900000000000006</v>
       </c>
     </row>
@@ -726,17 +727,17 @@
       <c r="D9" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E9" s="9">
+      <c r="E9" s="12">
         <v>65.599999999999994</v>
       </c>
-      <c r="F9" s="9"/>
-      <c r="G9" s="9">
+      <c r="F9" s="12"/>
+      <c r="G9" s="12">
         <v>61</v>
       </c>
-      <c r="H9" s="9">
+      <c r="H9" s="12">
         <v>70.5</v>
       </c>
-      <c r="I9" s="9">
+      <c r="I9" s="12">
         <v>68.900000000000006</v>
       </c>
     </row>
@@ -750,17 +751,17 @@
       <c r="D10" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E10" s="9">
+      <c r="E10" s="12">
         <v>65</v>
       </c>
-      <c r="F10" s="9"/>
-      <c r="G10" s="9">
+      <c r="F10" s="12"/>
+      <c r="G10" s="12">
         <v>70.900000000000006</v>
       </c>
-      <c r="H10" s="9">
+      <c r="H10" s="12">
         <v>76.3</v>
       </c>
-      <c r="I10" s="9">
+      <c r="I10" s="12">
         <v>75.5</v>
       </c>
     </row>
@@ -774,17 +775,17 @@
       <c r="D11" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="12">
         <v>65</v>
       </c>
-      <c r="F11" s="9"/>
-      <c r="G11" s="9">
+      <c r="F11" s="12"/>
+      <c r="G11" s="12">
         <v>70.900000000000006</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="12">
         <v>76.3</v>
       </c>
-      <c r="I11" s="9">
+      <c r="I11" s="12">
         <v>75.5</v>
       </c>
     </row>
@@ -798,17 +799,17 @@
       <c r="D12" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E12" s="9">
+      <c r="E12" s="12">
         <v>62.78</v>
       </c>
-      <c r="F12" s="9"/>
-      <c r="G12" s="9">
+      <c r="F12" s="12"/>
+      <c r="G12" s="12">
         <v>63.71</v>
       </c>
-      <c r="H12" s="9">
+      <c r="H12" s="12">
         <v>76.12</v>
       </c>
-      <c r="I12" s="9">
+      <c r="I12" s="12">
         <v>70.16</v>
       </c>
     </row>
@@ -822,17 +823,17 @@
       <c r="D13" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E13" s="9">
+      <c r="E13" s="12">
         <v>62.78</v>
       </c>
-      <c r="F13" s="9"/>
-      <c r="G13" s="9">
+      <c r="F13" s="12"/>
+      <c r="G13" s="12">
         <v>63.71</v>
       </c>
-      <c r="H13" s="9">
+      <c r="H13" s="12">
         <v>76.12</v>
       </c>
-      <c r="I13" s="9">
+      <c r="I13" s="12">
         <v>70.16</v>
       </c>
     </row>
@@ -846,17 +847,17 @@
       <c r="D14" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E14" s="9">
+      <c r="E14" s="12">
         <v>66.180000000000007</v>
       </c>
-      <c r="F14" s="9"/>
-      <c r="G14" s="9">
+      <c r="F14" s="12"/>
+      <c r="G14" s="12">
         <v>69.510000000000005</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="12">
         <v>86.03</v>
       </c>
-      <c r="I14" s="9">
+      <c r="I14" s="12">
         <v>70.8</v>
       </c>
     </row>
@@ -870,17 +871,17 @@
       <c r="D15" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E15" s="9">
+      <c r="E15" s="12">
         <v>66.180000000000007</v>
       </c>
-      <c r="F15" s="9"/>
-      <c r="G15" s="9">
+      <c r="F15" s="12"/>
+      <c r="G15" s="12">
         <v>69.510000000000005</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="12">
         <v>86.03</v>
       </c>
-      <c r="I15" s="9">
+      <c r="I15" s="12">
         <v>70.8</v>
       </c>
     </row>
@@ -894,17 +895,17 @@
       <c r="D16" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E16" s="9">
+      <c r="E16" s="12">
         <v>66.180000000000007</v>
       </c>
-      <c r="F16" s="9"/>
-      <c r="G16" s="9">
+      <c r="F16" s="12"/>
+      <c r="G16" s="12">
         <v>69.510000000000005</v>
       </c>
-      <c r="H16" s="9">
+      <c r="H16" s="12">
         <v>86.03</v>
       </c>
-      <c r="I16" s="9">
+      <c r="I16" s="12">
         <v>70.8</v>
       </c>
     </row>
@@ -918,17 +919,17 @@
       <c r="D17" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="12">
         <v>66.180000000000007</v>
       </c>
-      <c r="F17" s="9"/>
-      <c r="G17" s="9">
+      <c r="F17" s="12"/>
+      <c r="G17" s="12">
         <v>69.510000000000005</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="12">
         <v>86.03</v>
       </c>
-      <c r="I17" s="9">
+      <c r="I17" s="12">
         <v>70.8</v>
       </c>
     </row>
@@ -942,17 +943,17 @@
       <c r="D18" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="12">
         <v>64.099999999999994</v>
       </c>
-      <c r="F18" s="9"/>
-      <c r="G18" s="9">
+      <c r="F18" s="12"/>
+      <c r="G18" s="12">
         <v>75</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="12">
         <v>93.1</v>
       </c>
-      <c r="I18" s="9">
+      <c r="I18" s="12">
         <v>69.400000000000006</v>
       </c>
     </row>
@@ -966,17 +967,17 @@
       <c r="D19" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="12">
         <v>64.099999999999994</v>
       </c>
-      <c r="F19" s="9"/>
-      <c r="G19" s="9">
+      <c r="F19" s="12"/>
+      <c r="G19" s="12">
         <v>75</v>
       </c>
-      <c r="H19" s="9">
+      <c r="H19" s="12">
         <v>93.1</v>
       </c>
-      <c r="I19" s="9">
+      <c r="I19" s="12">
         <v>69.400000000000006</v>
       </c>
     </row>
@@ -990,17 +991,17 @@
       <c r="D20" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="12">
         <v>70.83</v>
       </c>
-      <c r="F20" s="9"/>
-      <c r="G20" s="9">
+      <c r="F20" s="12"/>
+      <c r="G20" s="12">
         <v>77.819999999999993</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="12">
         <v>95.81</v>
       </c>
-      <c r="I20" s="9">
+      <c r="I20" s="12">
         <v>81.34</v>
       </c>
     </row>
@@ -1014,17 +1015,17 @@
       <c r="D21" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E21" s="9">
+      <c r="E21" s="12">
         <v>70.83</v>
       </c>
-      <c r="F21" s="9"/>
-      <c r="G21" s="9">
+      <c r="F21" s="12"/>
+      <c r="G21" s="12">
         <v>77.819999999999993</v>
       </c>
-      <c r="H21" s="9">
+      <c r="H21" s="12">
         <v>95.81</v>
       </c>
-      <c r="I21" s="9">
+      <c r="I21" s="12">
         <v>81.34</v>
       </c>
     </row>
@@ -1038,17 +1039,17 @@
       <c r="D22" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E22" s="9">
+      <c r="E22" s="12">
         <v>69</v>
       </c>
-      <c r="F22" s="9"/>
-      <c r="G22" s="9">
+      <c r="F22" s="12"/>
+      <c r="G22" s="12">
         <v>79.12</v>
       </c>
-      <c r="H22" s="9">
+      <c r="H22" s="12">
         <v>94.05</v>
       </c>
-      <c r="I22" s="9">
+      <c r="I22" s="12">
         <v>76.94</v>
       </c>
     </row>
@@ -1062,17 +1063,17 @@
       <c r="D23" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E23" s="9">
+      <c r="E23" s="12">
         <v>69</v>
       </c>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9">
+      <c r="F23" s="12"/>
+      <c r="G23" s="12">
         <v>79.12</v>
       </c>
-      <c r="H23" s="9">
+      <c r="H23" s="12">
         <v>94.05</v>
       </c>
-      <c r="I23" s="9">
+      <c r="I23" s="12">
         <v>76.94</v>
       </c>
     </row>
@@ -1086,17 +1087,17 @@
       <c r="D24" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E24" s="9">
+      <c r="E24" s="12">
         <v>68.790000000000006</v>
       </c>
-      <c r="F24" s="9"/>
-      <c r="G24" s="9">
+      <c r="F24" s="12"/>
+      <c r="G24" s="12">
         <v>80.38</v>
       </c>
-      <c r="H24" s="9">
+      <c r="H24" s="12">
         <v>92.68</v>
       </c>
-      <c r="I24" s="9">
+      <c r="I24" s="12">
         <v>79.02</v>
       </c>
     </row>
@@ -1110,17 +1111,17 @@
       <c r="D25" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E25" s="9">
+      <c r="E25" s="12">
         <v>68.790000000000006</v>
       </c>
-      <c r="F25" s="9"/>
-      <c r="G25" s="9">
+      <c r="F25" s="12"/>
+      <c r="G25" s="12">
         <v>80.38</v>
       </c>
-      <c r="H25" s="9">
+      <c r="H25" s="12">
         <v>92.68</v>
       </c>
-      <c r="I25" s="9">
+      <c r="I25" s="12">
         <v>79.02</v>
       </c>
     </row>
@@ -1134,19 +1135,19 @@
       <c r="D26" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E26" s="9">
+      <c r="E26" s="12">
         <v>70.22</v>
       </c>
-      <c r="F26" s="9">
+      <c r="F26" s="12">
         <v>71</v>
       </c>
-      <c r="G26" s="9">
+      <c r="G26" s="12">
         <v>80.510000000000005</v>
       </c>
-      <c r="H26" s="9">
+      <c r="H26" s="12">
         <v>89.9</v>
       </c>
-      <c r="I26" s="9">
+      <c r="I26" s="12">
         <v>78.78</v>
       </c>
     </row>
@@ -1160,19 +1161,19 @@
       <c r="D27" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E27" s="9">
+      <c r="E27" s="12">
         <v>69.010000000000005</v>
       </c>
-      <c r="F27" s="9">
+      <c r="F27" s="12">
         <v>72</v>
       </c>
-      <c r="G27" s="9">
+      <c r="G27" s="12">
         <v>80.510000000000005</v>
       </c>
-      <c r="H27" s="9">
+      <c r="H27" s="12">
         <v>87.94</v>
       </c>
-      <c r="I27" s="9">
+      <c r="I27" s="12">
         <v>81.400000000000006</v>
       </c>
     </row>
@@ -1186,19 +1187,19 @@
       <c r="D28" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E28" s="9">
+      <c r="E28" s="12">
         <v>66.66</v>
       </c>
-      <c r="F28" s="9">
+      <c r="F28" s="12">
         <v>71.8</v>
       </c>
-      <c r="G28" s="9">
+      <c r="G28" s="12">
         <v>77.02</v>
       </c>
-      <c r="H28" s="9">
+      <c r="H28" s="12">
         <v>79.790000000000006</v>
       </c>
-      <c r="I28" s="9">
+      <c r="I28" s="12">
         <v>73.53</v>
       </c>
     </row>
@@ -1212,19 +1213,19 @@
       <c r="D29" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E29" s="9">
+      <c r="E29" s="12">
         <v>64.650000000000006</v>
       </c>
-      <c r="F29" s="9">
+      <c r="F29" s="12">
         <v>68.8</v>
       </c>
-      <c r="G29" s="9">
+      <c r="G29" s="12">
         <v>74.760000000000005</v>
       </c>
-      <c r="H29" s="9">
+      <c r="H29" s="12">
         <v>74.34</v>
       </c>
-      <c r="I29" s="9">
+      <c r="I29" s="12">
         <v>72.73</v>
       </c>
     </row>
@@ -1238,19 +1239,19 @@
       <c r="D30" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E30" s="9">
+      <c r="E30" s="12">
         <v>65.2</v>
       </c>
-      <c r="F30" s="9">
+      <c r="F30" s="12">
         <v>66.8</v>
       </c>
-      <c r="G30" s="9">
+      <c r="G30" s="12">
         <v>79.959999999999994</v>
       </c>
-      <c r="H30" s="9">
+      <c r="H30" s="12">
         <v>69.38</v>
       </c>
-      <c r="I30" s="9">
+      <c r="I30" s="12">
         <v>75.650000000000006</v>
       </c>
     </row>
@@ -1264,19 +1265,19 @@
       <c r="D31" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E31" s="9">
+      <c r="E31" s="12">
         <v>61.95</v>
       </c>
-      <c r="F31" s="9">
+      <c r="F31" s="12">
         <v>63.1</v>
       </c>
-      <c r="G31" s="9">
+      <c r="G31" s="12">
         <v>72.33</v>
       </c>
-      <c r="H31" s="9">
+      <c r="H31" s="12">
         <v>67.23</v>
       </c>
-      <c r="I31" s="9">
+      <c r="I31" s="12">
         <v>74.510000000000005</v>
       </c>
     </row>
@@ -1290,19 +1291,19 @@
       <c r="D32" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="12">
         <v>60.4</v>
       </c>
-      <c r="F32" s="9">
+      <c r="F32" s="12">
         <v>63.6</v>
       </c>
-      <c r="G32" s="9">
+      <c r="G32" s="12">
         <v>76.7</v>
       </c>
-      <c r="H32" s="9">
+      <c r="H32" s="12">
         <v>65.5</v>
       </c>
-      <c r="I32" s="9">
+      <c r="I32" s="12">
         <v>69.900000000000006</v>
       </c>
     </row>
@@ -1316,19 +1317,19 @@
       <c r="D33" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E33" s="9">
+      <c r="E33" s="12">
         <v>57.9</v>
       </c>
-      <c r="F33" s="9">
+      <c r="F33" s="12">
         <v>60.1</v>
       </c>
-      <c r="G33" s="9">
+      <c r="G33" s="12">
         <v>70.599999999999994</v>
       </c>
-      <c r="H33" s="9">
+      <c r="H33" s="12">
         <v>52.2</v>
       </c>
-      <c r="I33" s="9">
+      <c r="I33" s="12">
         <v>70.7</v>
       </c>
     </row>
@@ -1342,19 +1343,19 @@
       <c r="D34" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E34" s="9">
+      <c r="E34" s="12">
         <v>56.7</v>
       </c>
-      <c r="F34" s="9">
+      <c r="F34" s="12">
         <v>58.6</v>
       </c>
-      <c r="G34" s="9">
+      <c r="G34" s="12">
         <v>70.59</v>
       </c>
-      <c r="H34" s="9">
+      <c r="H34" s="12">
         <v>48.6</v>
       </c>
-      <c r="I34" s="9">
+      <c r="I34" s="12">
         <v>72.55</v>
       </c>
     </row>
@@ -1368,19 +1369,19 @@
       <c r="D35" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="12">
         <v>56</v>
       </c>
-      <c r="F35" s="9">
+      <c r="F35" s="12">
         <v>58.4</v>
       </c>
-      <c r="G35" s="9">
+      <c r="G35" s="12">
         <v>65.099999999999994</v>
       </c>
-      <c r="H35" s="9">
+      <c r="H35" s="12">
         <v>51</v>
       </c>
-      <c r="I35" s="9">
+      <c r="I35" s="12">
         <v>71.2</v>
       </c>
     </row>
@@ -1394,19 +1395,19 @@
       <c r="D36" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="12">
         <v>57.2</v>
       </c>
-      <c r="F36" s="9">
+      <c r="F36" s="12">
         <v>59.7</v>
       </c>
-      <c r="G36" s="9">
+      <c r="G36" s="12">
         <v>66.2</v>
       </c>
-      <c r="H36" s="9">
+      <c r="H36" s="12">
         <v>49.2</v>
       </c>
-      <c r="I36" s="9">
+      <c r="I36" s="12">
         <v>71.2</v>
       </c>
     </row>
@@ -1420,19 +1421,19 @@
       <c r="D37" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="12">
         <v>56.6</v>
       </c>
-      <c r="F37" s="9">
+      <c r="F37" s="12">
         <v>62.7</v>
       </c>
-      <c r="G37" s="9">
+      <c r="G37" s="12">
         <v>69.8</v>
       </c>
-      <c r="H37" s="9">
+      <c r="H37" s="12">
         <v>48.9</v>
       </c>
-      <c r="I37" s="9">
+      <c r="I37" s="12">
         <v>70.3</v>
       </c>
     </row>
@@ -1446,19 +1447,19 @@
       <c r="D38" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E38" s="9">
+      <c r="E38" s="12">
         <v>56.6</v>
       </c>
-      <c r="F38" s="9">
+      <c r="F38" s="12">
         <v>63.7</v>
       </c>
-      <c r="G38" s="9">
+      <c r="G38" s="12">
         <v>69.599999999999994</v>
       </c>
-      <c r="H38" s="9">
+      <c r="H38" s="12">
         <v>50.6</v>
       </c>
-      <c r="I38" s="9">
+      <c r="I38" s="12">
         <v>67.5</v>
       </c>
     </row>
@@ -1472,19 +1473,19 @@
       <c r="D39" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E39" s="9">
+      <c r="E39" s="12">
         <v>54.4</v>
       </c>
-      <c r="F39" s="9">
+      <c r="F39" s="12">
         <v>59.5</v>
       </c>
-      <c r="G39" s="9">
+      <c r="G39" s="12">
         <v>65.599999999999994</v>
       </c>
-      <c r="H39" s="9">
+      <c r="H39" s="12">
         <v>43.5</v>
       </c>
-      <c r="I39" s="9">
+      <c r="I39" s="12">
         <v>66.7</v>
       </c>
     </row>
@@ -1498,19 +1499,19 @@
       <c r="D40" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="12">
         <v>54.5</v>
       </c>
-      <c r="F40" s="9">
+      <c r="F40" s="12">
         <v>62.1</v>
       </c>
-      <c r="G40" s="9">
+      <c r="G40" s="12">
         <v>68.3</v>
       </c>
-      <c r="H40" s="9">
+      <c r="H40" s="12">
         <v>41</v>
       </c>
-      <c r="I40" s="9">
+      <c r="I40" s="12">
         <v>65.400000000000006</v>
       </c>
     </row>
@@ -1524,19 +1525,19 @@
       <c r="D41" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E41" s="9">
+      <c r="E41" s="12">
         <v>53.96</v>
       </c>
-      <c r="F41" s="9">
+      <c r="F41" s="12">
         <v>63.3</v>
       </c>
-      <c r="G41" s="9">
+      <c r="G41" s="12">
         <v>73.19</v>
       </c>
-      <c r="H41" s="9">
+      <c r="H41" s="12">
         <v>52.74</v>
       </c>
-      <c r="I41" s="9">
+      <c r="I41" s="12">
         <v>63.43</v>
       </c>
     </row>
@@ -1550,19 +1551,19 @@
       <c r="D42" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="12">
         <v>54.12</v>
       </c>
-      <c r="F42" s="9">
+      <c r="F42" s="12">
         <v>62.8</v>
       </c>
-      <c r="G42" s="9">
+      <c r="G42" s="12">
         <v>69.89</v>
       </c>
-      <c r="H42" s="9">
+      <c r="H42" s="12">
         <v>50</v>
       </c>
-      <c r="I42" s="9">
+      <c r="I42" s="12">
         <v>66.13</v>
       </c>
     </row>
@@ -1576,19 +1577,19 @@
       <c r="D43" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E43" s="12">
         <v>52.62</v>
       </c>
-      <c r="F43" s="9">
+      <c r="F43" s="12">
         <v>63.1</v>
       </c>
-      <c r="G43" s="9">
+      <c r="G43" s="12">
         <v>65.91</v>
       </c>
-      <c r="H43" s="9">
+      <c r="H43" s="12">
         <v>48.98</v>
       </c>
-      <c r="I43" s="9">
+      <c r="I43" s="12">
         <v>61.8</v>
       </c>
     </row>
@@ -1602,19 +1603,19 @@
       <c r="D44" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E44" s="12">
         <v>58.87</v>
       </c>
-      <c r="F44" s="9">
+      <c r="F44" s="12">
         <v>62.3</v>
       </c>
-      <c r="G44" s="9">
+      <c r="G44" s="12">
         <v>64.5</v>
       </c>
-      <c r="H44" s="9">
+      <c r="H44" s="12">
         <v>65.52</v>
       </c>
-      <c r="I44" s="9">
+      <c r="I44" s="12">
         <v>66.489999999999995</v>
       </c>
     </row>
@@ -1628,19 +1629,19 @@
       <c r="D45" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E45" s="12">
         <v>51.31</v>
       </c>
-      <c r="F45" s="9">
+      <c r="F45" s="12">
         <v>62.4</v>
       </c>
-      <c r="G45" s="9">
+      <c r="G45" s="12">
         <v>56.97</v>
       </c>
-      <c r="H45" s="9">
+      <c r="H45" s="12">
         <v>37.659999999999997</v>
       </c>
-      <c r="I45" s="9">
+      <c r="I45" s="12">
         <v>63.1</v>
       </c>
     </row>
@@ -1654,19 +1655,19 @@
       <c r="D46" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E46" s="9">
+      <c r="E46" s="12">
         <v>54.46</v>
       </c>
-      <c r="F46" s="9">
+      <c r="F46" s="12">
         <v>57.5</v>
       </c>
-      <c r="G46" s="9">
+      <c r="G46" s="12">
         <v>60.1</v>
       </c>
-      <c r="H46" s="9">
+      <c r="H46" s="12">
         <v>49.07</v>
       </c>
-      <c r="I46" s="9">
+      <c r="I46" s="12">
         <v>66.02</v>
       </c>
     </row>
@@ -1680,19 +1681,19 @@
       <c r="D47" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E47" s="9">
+      <c r="E47" s="12">
         <v>61.71</v>
       </c>
-      <c r="F47" s="9">
+      <c r="F47" s="12">
         <v>64.599999999999994</v>
       </c>
-      <c r="G47" s="9">
+      <c r="G47" s="12">
         <v>60.55</v>
       </c>
-      <c r="H47" s="9">
+      <c r="H47" s="12">
         <v>64.47</v>
       </c>
-      <c r="I47" s="9">
+      <c r="I47" s="12">
         <v>63.46</v>
       </c>
     </row>
@@ -1706,19 +1707,19 @@
       <c r="D48" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E48" s="9">
+      <c r="E48" s="12">
         <v>63.03</v>
       </c>
-      <c r="F48" s="9">
+      <c r="F48" s="12">
         <v>69.099999999999994</v>
       </c>
-      <c r="G48" s="9">
+      <c r="G48" s="12">
         <v>67.48</v>
       </c>
-      <c r="H48" s="9">
+      <c r="H48" s="12">
         <v>72.64</v>
       </c>
-      <c r="I48" s="9">
+      <c r="I48" s="12">
         <v>69.12</v>
       </c>
     </row>
@@ -1732,19 +1733,19 @@
       <c r="D49" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E49" s="9">
+      <c r="E49" s="12">
         <v>66</v>
       </c>
-      <c r="F49" s="9">
+      <c r="F49" s="12">
         <v>66</v>
       </c>
-      <c r="G49" s="9">
+      <c r="G49" s="12">
         <v>68.62</v>
       </c>
-      <c r="H49" s="9">
+      <c r="H49" s="12">
         <v>83.8</v>
       </c>
-      <c r="I49" s="9">
+      <c r="I49" s="12">
         <v>64.739999999999995</v>
       </c>
     </row>
@@ -1758,19 +1759,19 @@
       <c r="D50" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E50" s="9">
+      <c r="E50" s="12">
         <v>70.47</v>
       </c>
-      <c r="F50" s="9">
+      <c r="F50" s="12">
         <v>71.5</v>
       </c>
-      <c r="G50" s="9">
+      <c r="G50" s="12">
         <v>70.5</v>
       </c>
-      <c r="H50" s="9">
+      <c r="H50" s="12">
         <v>87.85</v>
       </c>
-      <c r="I50" s="9">
+      <c r="I50" s="12">
         <v>65.84</v>
       </c>
     </row>
@@ -1784,19 +1785,19 @@
       <c r="D51" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E51" s="9">
+      <c r="E51" s="12">
         <v>71.599999999999994</v>
       </c>
-      <c r="F51" s="9">
+      <c r="F51" s="12">
         <v>69.900000000000006</v>
       </c>
-      <c r="G51" s="9">
+      <c r="G51" s="12">
         <v>78.7</v>
       </c>
-      <c r="H51" s="9">
+      <c r="H51" s="12">
         <v>85.5</v>
       </c>
-      <c r="I51" s="9">
+      <c r="I51" s="12">
         <v>73.599999999999994</v>
       </c>
     </row>
@@ -1810,19 +1811,19 @@
       <c r="D52" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E52" s="12">
         <v>70.8</v>
       </c>
-      <c r="F52" s="9">
+      <c r="F52" s="12">
         <v>69.8</v>
       </c>
-      <c r="G52" s="9">
+      <c r="G52" s="12">
         <v>78.400000000000006</v>
       </c>
-      <c r="H52" s="9">
+      <c r="H52" s="12">
         <v>85.8</v>
       </c>
-      <c r="I52" s="9">
+      <c r="I52" s="12">
         <v>73.099999999999994</v>
       </c>
     </row>
@@ -1836,19 +1837,19 @@
       <c r="D53" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E53" s="9">
+      <c r="E53" s="12">
         <v>66.7</v>
       </c>
-      <c r="F53" s="9">
+      <c r="F53" s="12">
         <v>66.5</v>
       </c>
-      <c r="G53" s="9">
+      <c r="G53" s="12">
         <v>76.900000000000006</v>
       </c>
-      <c r="H53" s="9">
+      <c r="H53" s="12">
         <v>85.1</v>
       </c>
-      <c r="I53" s="9">
+      <c r="I53" s="12">
         <v>71.8</v>
       </c>
     </row>
@@ -1862,19 +1863,19 @@
       <c r="D54" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E54" s="9">
+      <c r="E54" s="12">
         <v>67.2</v>
       </c>
-      <c r="F54" s="9">
+      <c r="F54" s="12">
         <v>68.400000000000006</v>
       </c>
-      <c r="G54" s="9">
+      <c r="G54" s="12">
         <v>77.8</v>
       </c>
-      <c r="H54" s="9">
+      <c r="H54" s="12">
         <v>81</v>
       </c>
-      <c r="I54" s="9">
+      <c r="I54" s="12">
         <v>75</v>
       </c>
     </row>
@@ -1888,19 +1889,19 @@
       <c r="D55" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E55" s="9">
+      <c r="E55" s="12">
         <v>71.400000000000006</v>
       </c>
-      <c r="F55" s="9">
+      <c r="F55" s="12">
         <v>71</v>
       </c>
-      <c r="G55" s="9">
+      <c r="G55" s="12">
         <v>79</v>
       </c>
-      <c r="H55" s="9">
+      <c r="H55" s="12">
         <v>88</v>
       </c>
-      <c r="I55" s="9">
+      <c r="I55" s="12">
         <v>76.8</v>
       </c>
     </row>
@@ -1914,19 +1915,19 @@
       <c r="D56" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E56" s="9">
+      <c r="E56" s="12">
         <v>72.2</v>
       </c>
-      <c r="F56" s="9">
+      <c r="F56" s="12">
         <v>71.7</v>
       </c>
-      <c r="G56" s="9">
+      <c r="G56" s="12">
         <v>81.5</v>
       </c>
-      <c r="H56" s="9">
+      <c r="H56" s="12">
         <v>90.6</v>
       </c>
-      <c r="I56" s="9">
+      <c r="I56" s="12">
         <v>80</v>
       </c>
     </row>
@@ -1940,19 +1941,19 @@
       <c r="D57" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E57" s="9">
+      <c r="E57" s="12">
         <v>74.5</v>
       </c>
-      <c r="F57" s="9">
+      <c r="F57" s="12">
         <v>72.7</v>
       </c>
-      <c r="G57" s="9">
+      <c r="G57" s="12">
         <v>83.5</v>
       </c>
-      <c r="H57" s="9">
+      <c r="H57" s="12">
         <v>92.6</v>
       </c>
-      <c r="I57" s="9">
+      <c r="I57" s="12">
         <v>84.6</v>
       </c>
     </row>
@@ -1966,19 +1967,19 @@
       <c r="D58" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E58" s="9">
+      <c r="E58" s="12">
         <v>71.3</v>
       </c>
-      <c r="F58" s="9">
+      <c r="F58" s="12">
         <v>73</v>
       </c>
-      <c r="G58" s="9">
+      <c r="G58" s="12">
         <v>83.1</v>
       </c>
-      <c r="H58" s="9">
+      <c r="H58" s="12">
         <v>91.2</v>
       </c>
-      <c r="I58" s="9">
+      <c r="I58" s="12">
         <v>83.8</v>
       </c>
     </row>
@@ -1992,19 +1993,19 @@
       <c r="D59" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E59" s="9">
+      <c r="E59" s="12">
         <v>75</v>
       </c>
-      <c r="F59" s="9">
+      <c r="F59" s="12">
         <v>69.7</v>
       </c>
-      <c r="G59" s="9">
+      <c r="G59" s="12">
         <v>85.4</v>
       </c>
-      <c r="H59" s="9">
+      <c r="H59" s="12">
         <v>87.3</v>
       </c>
-      <c r="I59" s="9">
+      <c r="I59" s="12">
         <v>89.4</v>
       </c>
     </row>
@@ -2018,19 +2019,19 @@
       <c r="D60" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E60" s="9">
+      <c r="E60" s="12">
         <v>74.5</v>
       </c>
-      <c r="F60" s="9">
+      <c r="F60" s="12">
         <v>71.7</v>
       </c>
-      <c r="G60" s="9">
+      <c r="G60" s="12">
         <v>88</v>
       </c>
-      <c r="H60" s="9">
+      <c r="H60" s="12">
         <v>91</v>
       </c>
-      <c r="I60" s="9">
+      <c r="I60" s="12">
         <v>88.8</v>
       </c>
     </row>
@@ -2044,19 +2045,19 @@
       <c r="D61" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E61" s="9">
+      <c r="E61" s="12">
         <v>73.8</v>
       </c>
-      <c r="F61" s="9">
+      <c r="F61" s="12">
         <v>73.599999999999994</v>
       </c>
-      <c r="G61" s="9">
+      <c r="G61" s="12">
         <v>88</v>
       </c>
-      <c r="H61" s="9">
+      <c r="H61" s="12">
         <v>93.7</v>
       </c>
-      <c r="I61" s="9">
+      <c r="I61" s="12">
         <v>85.9</v>
       </c>
     </row>
@@ -2070,19 +2071,19 @@
       <c r="D62" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E62" s="9">
+      <c r="E62" s="12">
         <v>72.2</v>
       </c>
-      <c r="F62" s="9">
+      <c r="F62" s="12">
         <v>72.599999999999994</v>
       </c>
-      <c r="G62" s="9">
+      <c r="G62" s="12">
         <v>89.3</v>
       </c>
-      <c r="H62" s="9">
+      <c r="H62" s="12">
         <v>92.4</v>
       </c>
-      <c r="I62" s="9">
+      <c r="I62" s="12">
         <v>86.6</v>
       </c>
     </row>
@@ -2096,19 +2097,19 @@
       <c r="D63" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E63" s="9">
+      <c r="E63" s="12">
         <v>72.599999999999994</v>
       </c>
-      <c r="F63" s="9">
+      <c r="F63" s="12">
         <v>70.599999999999994</v>
       </c>
-      <c r="G63" s="9">
+      <c r="G63" s="12">
         <v>85.8</v>
       </c>
-      <c r="H63" s="9">
+      <c r="H63" s="12">
         <v>90.7</v>
       </c>
-      <c r="I63" s="9">
+      <c r="I63" s="12">
         <v>85.9</v>
       </c>
     </row>
@@ -2122,19 +2123,19 @@
       <c r="D64" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E64" s="9">
+      <c r="E64" s="12">
         <v>73.400000000000006</v>
       </c>
-      <c r="F64" s="9">
+      <c r="F64" s="12">
         <v>71.2</v>
       </c>
-      <c r="G64" s="9">
+      <c r="G64" s="12">
         <v>90.3</v>
       </c>
-      <c r="H64" s="9">
+      <c r="H64" s="12">
         <v>93.2</v>
       </c>
-      <c r="I64" s="9">
+      <c r="I64" s="12">
         <v>87.6</v>
       </c>
     </row>
@@ -2148,19 +2149,19 @@
       <c r="D65" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E65" s="9">
+      <c r="E65" s="12">
         <v>70.099999999999994</v>
       </c>
-      <c r="F65" s="9">
+      <c r="F65" s="12">
         <v>72.900000000000006</v>
       </c>
-      <c r="G65" s="9">
+      <c r="G65" s="12">
         <v>82.1</v>
       </c>
-      <c r="H65" s="9">
+      <c r="H65" s="12">
         <v>87.6</v>
       </c>
-      <c r="I65" s="9">
+      <c r="I65" s="12">
         <v>84</v>
       </c>
     </row>
@@ -2174,19 +2175,19 @@
       <c r="D66" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E66" s="9">
+      <c r="E66" s="12">
         <v>71.900000000000006</v>
       </c>
-      <c r="F66" s="9">
+      <c r="F66" s="12">
         <v>70.7</v>
       </c>
-      <c r="G66" s="9">
+      <c r="G66" s="12">
         <v>85.9</v>
       </c>
-      <c r="H66" s="9">
+      <c r="H66" s="12">
         <v>88.7</v>
       </c>
-      <c r="I66" s="9">
+      <c r="I66" s="12">
         <v>87.9</v>
       </c>
     </row>
@@ -2200,19 +2201,19 @@
       <c r="D67" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E67" s="9">
+      <c r="E67" s="12">
         <v>75.2</v>
       </c>
-      <c r="F67" s="9">
+      <c r="F67" s="12">
         <v>69.900000000000006</v>
       </c>
-      <c r="G67" s="9">
+      <c r="G67" s="12">
         <v>86.4</v>
       </c>
-      <c r="H67" s="9">
+      <c r="H67" s="12">
         <v>89</v>
       </c>
-      <c r="I67" s="9">
+      <c r="I67" s="12">
         <v>90.3</v>
       </c>
     </row>
@@ -2226,19 +2227,19 @@
       <c r="D68" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E68" s="9">
+      <c r="E68" s="12">
         <v>76.2</v>
       </c>
-      <c r="F68" s="9">
+      <c r="F68" s="12">
         <v>70.2</v>
       </c>
-      <c r="G68" s="9">
+      <c r="G68" s="12">
         <v>90.5</v>
       </c>
-      <c r="H68" s="9">
+      <c r="H68" s="12">
         <v>89.7</v>
       </c>
-      <c r="I68" s="9">
+      <c r="I68" s="12">
         <v>91</v>
       </c>
     </row>
@@ -2252,19 +2253,19 @@
       <c r="D69" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E69" s="9">
+      <c r="E69" s="12">
         <v>69.7</v>
       </c>
-      <c r="F69" s="9">
+      <c r="F69" s="12">
         <v>67.8</v>
       </c>
-      <c r="G69" s="9">
+      <c r="G69" s="12">
         <v>85.8</v>
       </c>
-      <c r="H69" s="9">
+      <c r="H69" s="12">
         <v>73.900000000000006</v>
       </c>
-      <c r="I69" s="9">
+      <c r="I69" s="12">
         <v>87.7</v>
       </c>
     </row>
@@ -2278,19 +2279,19 @@
       <c r="D70" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E70" s="9">
+      <c r="E70" s="12">
         <v>67.099999999999994</v>
       </c>
-      <c r="F70" s="9">
+      <c r="F70" s="12">
         <v>66</v>
       </c>
-      <c r="G70" s="9">
+      <c r="G70" s="12">
         <v>87.5</v>
       </c>
-      <c r="H70" s="9">
+      <c r="H70" s="12">
         <v>65.3</v>
       </c>
-      <c r="I70" s="9">
+      <c r="I70" s="12">
         <v>88.1</v>
       </c>
     </row>
@@ -2304,19 +2305,19 @@
       <c r="D71" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E71" s="9">
+      <c r="E71" s="12">
         <v>65</v>
       </c>
-      <c r="F71" s="9">
+      <c r="F71" s="12">
         <v>60.4</v>
       </c>
-      <c r="G71" s="9">
+      <c r="G71" s="12">
         <v>78.400000000000006</v>
       </c>
-      <c r="H71" s="9">
+      <c r="H71" s="12">
         <v>61.3</v>
       </c>
-      <c r="I71" s="9">
+      <c r="I71" s="12">
         <v>83.8</v>
       </c>
     </row>
@@ -2330,19 +2331,19 @@
       <c r="D72" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E72" s="9">
+      <c r="E72" s="12">
         <v>60.7</v>
       </c>
-      <c r="F72" s="9">
+      <c r="F72" s="12">
         <v>62.1</v>
       </c>
-      <c r="G72" s="9">
+      <c r="G72" s="12">
         <v>76.2</v>
       </c>
-      <c r="H72" s="9">
+      <c r="H72" s="12">
         <v>49.5</v>
       </c>
-      <c r="I72" s="9">
+      <c r="I72" s="12">
         <v>79</v>
       </c>
     </row>
@@ -2356,19 +2357,19 @@
       <c r="D73" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E73" s="9">
+      <c r="E73" s="12">
         <v>59.7</v>
       </c>
-      <c r="F73" s="9">
+      <c r="F73" s="12">
         <v>57.6</v>
       </c>
-      <c r="G73" s="9">
+      <c r="G73" s="12">
         <v>75</v>
       </c>
-      <c r="H73" s="9">
+      <c r="H73" s="12">
         <v>48</v>
       </c>
-      <c r="I73" s="9">
+      <c r="I73" s="12">
         <v>76.8</v>
       </c>
     </row>
@@ -2382,19 +2383,19 @@
       <c r="D74" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E74" s="9">
+      <c r="E74" s="12">
         <v>61.4</v>
       </c>
-      <c r="F74" s="9">
+      <c r="F74" s="12">
         <v>56.2</v>
       </c>
-      <c r="G74" s="9">
+      <c r="G74" s="12">
         <v>75.400000000000006</v>
       </c>
-      <c r="H74" s="9">
+      <c r="H74" s="12">
         <v>44.5</v>
       </c>
-      <c r="I74" s="9">
+      <c r="I74" s="12">
         <v>77.2</v>
       </c>
     </row>
@@ -2408,19 +2409,19 @@
       <c r="D75" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E75" s="9">
+      <c r="E75" s="12">
         <v>57.5</v>
       </c>
-      <c r="F75" s="9">
+      <c r="F75" s="12">
         <v>55.2</v>
       </c>
-      <c r="G75" s="9">
+      <c r="G75" s="12">
         <v>75.5</v>
       </c>
-      <c r="H75" s="9">
+      <c r="H75" s="12">
         <v>42.2</v>
       </c>
-      <c r="I75" s="9">
+      <c r="I75" s="12">
         <v>80.900000000000006</v>
       </c>
     </row>
@@ -2434,19 +2435,19 @@
       <c r="D76" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E76" s="9">
+      <c r="E76" s="12">
         <v>53.6</v>
       </c>
-      <c r="F76" s="9">
+      <c r="F76" s="12">
         <v>51.5</v>
       </c>
-      <c r="G76" s="9">
+      <c r="G76" s="12">
         <v>74.400000000000006</v>
       </c>
-      <c r="H76" s="9">
+      <c r="H76" s="12">
         <v>37.4</v>
       </c>
-      <c r="I76" s="9">
+      <c r="I76" s="12">
         <v>73.400000000000006</v>
       </c>
     </row>
@@ -2460,19 +2461,19 @@
       <c r="D77" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E77" s="9">
+      <c r="E77" s="12">
         <v>54.6</v>
       </c>
-      <c r="F77" s="9">
+      <c r="F77" s="12">
         <v>53.2</v>
       </c>
-      <c r="G77" s="9">
+      <c r="G77" s="12">
         <v>72.099999999999994</v>
       </c>
-      <c r="H77" s="9">
+      <c r="H77" s="12">
         <v>36.9</v>
       </c>
-      <c r="I77" s="9">
+      <c r="I77" s="12">
         <v>72.8</v>
       </c>
     </row>
@@ -2486,19 +2487,19 @@
       <c r="D78" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E78" s="9">
+      <c r="E78" s="12">
         <v>57.6</v>
       </c>
-      <c r="F78" s="9">
+      <c r="F78" s="12">
         <v>56.1</v>
       </c>
-      <c r="G78" s="9">
+      <c r="G78" s="12">
         <v>75</v>
       </c>
-      <c r="H78" s="9">
+      <c r="H78" s="12">
         <v>42</v>
       </c>
-      <c r="I78" s="9">
+      <c r="I78" s="12">
         <v>74.2</v>
       </c>
     </row>
@@ -2512,19 +2513,19 @@
       <c r="D79" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E79" s="9">
+      <c r="E79" s="12">
         <v>54.7</v>
       </c>
-      <c r="F79" s="9">
+      <c r="F79" s="12">
         <v>56.7</v>
       </c>
-      <c r="G79" s="9">
+      <c r="G79" s="12">
         <v>73.3</v>
       </c>
-      <c r="H79" s="9">
+      <c r="H79" s="12">
         <v>36.1</v>
       </c>
-      <c r="I79" s="9">
+      <c r="I79" s="12">
         <v>70.900000000000006</v>
       </c>
     </row>
@@ -2538,19 +2539,19 @@
       <c r="D80" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E80" s="9">
+      <c r="E80" s="12">
         <v>51.1</v>
       </c>
-      <c r="F80" s="9">
+      <c r="F80" s="12">
         <v>52.7</v>
       </c>
-      <c r="G80" s="9">
+      <c r="G80" s="12">
         <v>70.900000000000006</v>
       </c>
-      <c r="H80" s="9">
+      <c r="H80" s="12">
         <v>31.1</v>
       </c>
-      <c r="I80" s="9">
+      <c r="I80" s="12">
         <v>66</v>
       </c>
     </row>
@@ -2564,19 +2565,19 @@
       <c r="D81" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E81" s="9">
+      <c r="E81" s="12">
         <v>50.9</v>
       </c>
-      <c r="F81" s="9">
+      <c r="F81" s="12">
         <v>51.1</v>
       </c>
-      <c r="G81" s="9">
+      <c r="G81" s="12">
         <v>69.8</v>
       </c>
-      <c r="H81" s="9">
+      <c r="H81" s="12">
         <v>36.799999999999997</v>
       </c>
-      <c r="I81" s="9">
+      <c r="I81" s="12">
         <v>65.099999999999994</v>
       </c>
     </row>
@@ -2590,19 +2591,19 @@
       <c r="D82" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E82" s="9">
+      <c r="E82" s="12">
         <v>47.3</v>
       </c>
-      <c r="F82" s="9">
+      <c r="F82" s="12">
         <v>49.6</v>
       </c>
-      <c r="G82" s="9">
+      <c r="G82" s="12">
         <v>62.8</v>
       </c>
-      <c r="H82" s="9">
+      <c r="H82" s="12">
         <v>27.9</v>
       </c>
-      <c r="I82" s="9">
+      <c r="I82" s="12">
         <v>64.400000000000006</v>
       </c>
     </row>
@@ -2616,19 +2617,19 @@
       <c r="D83" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E83" s="9">
+      <c r="E83" s="12">
         <v>45.6</v>
       </c>
-      <c r="F83" s="9">
+      <c r="F83" s="12">
         <v>55.4</v>
       </c>
-      <c r="G83" s="9">
+      <c r="G83" s="12">
         <v>63.3</v>
       </c>
-      <c r="H83" s="9">
+      <c r="H83" s="12">
         <v>32.799999999999997</v>
       </c>
-      <c r="I83" s="9">
+      <c r="I83" s="12">
         <v>57.1</v>
       </c>
     </row>
@@ -2642,19 +2643,19 @@
       <c r="D84" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E84" s="9">
+      <c r="E84" s="12">
         <v>45.4</v>
       </c>
-      <c r="F84" s="9">
+      <c r="F84" s="12">
         <v>52.8</v>
       </c>
-      <c r="G84" s="9">
+      <c r="G84" s="12">
         <v>60.6</v>
       </c>
-      <c r="H84" s="9">
+      <c r="H84" s="12">
         <v>35.6</v>
       </c>
-      <c r="I84" s="9">
+      <c r="I84" s="12">
         <v>60.5</v>
       </c>
     </row>
@@ -2668,19 +2669,19 @@
       <c r="D85" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E85" s="9">
+      <c r="E85" s="12">
         <v>51.2</v>
       </c>
-      <c r="F85" s="9">
+      <c r="F85" s="12">
         <v>58.6</v>
       </c>
-      <c r="G85" s="9">
+      <c r="G85" s="12">
         <v>63.4</v>
       </c>
-      <c r="H85" s="9">
+      <c r="H85" s="12">
         <v>42.9</v>
       </c>
-      <c r="I85" s="9">
+      <c r="I85" s="12">
         <v>69.099999999999994</v>
       </c>
     </row>
@@ -2694,19 +2695,19 @@
       <c r="D86" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E86" s="9">
+      <c r="E86" s="12">
         <v>52.4</v>
       </c>
-      <c r="F86" s="9">
+      <c r="F86" s="12">
         <v>60.1</v>
       </c>
-      <c r="G86" s="9">
+      <c r="G86" s="12">
         <v>71.2</v>
       </c>
-      <c r="H86" s="9">
+      <c r="H86" s="12">
         <v>43.5</v>
       </c>
-      <c r="I86" s="9">
+      <c r="I86" s="12">
         <v>64.599999999999994</v>
       </c>
     </row>
@@ -2720,19 +2721,19 @@
       <c r="D87" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E87" s="9">
+      <c r="E87" s="12">
         <v>56.5</v>
       </c>
-      <c r="F87" s="9">
+      <c r="F87" s="12">
         <v>60.8</v>
       </c>
-      <c r="G87" s="9">
+      <c r="G87" s="12">
         <v>70.7</v>
       </c>
-      <c r="H87" s="9">
+      <c r="H87" s="12">
         <v>44.4</v>
       </c>
-      <c r="I87" s="9">
+      <c r="I87" s="12">
         <v>69.8</v>
       </c>
     </row>
@@ -2746,19 +2747,19 @@
       <c r="D88" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E88" s="9">
+      <c r="E88" s="12">
         <v>49.4</v>
       </c>
-      <c r="F88" s="9">
+      <c r="F88" s="12">
         <v>57.4</v>
       </c>
-      <c r="G88" s="9">
+      <c r="G88" s="12">
         <v>64.2</v>
       </c>
-      <c r="H88" s="9">
+      <c r="H88" s="12">
         <v>44.2</v>
       </c>
-      <c r="I88" s="9">
+      <c r="I88" s="12">
         <v>62.1</v>
       </c>
     </row>
@@ -2772,19 +2773,19 @@
       <c r="D89" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E89" s="9">
+      <c r="E89" s="12">
         <v>50.6</v>
       </c>
-      <c r="F89" s="9">
+      <c r="F89" s="12">
         <v>59.9</v>
       </c>
-      <c r="G89" s="9">
+      <c r="G89" s="12">
         <v>65.5</v>
       </c>
-      <c r="H89" s="9">
+      <c r="H89" s="12">
         <v>43.1</v>
       </c>
-      <c r="I89" s="9">
+      <c r="I89" s="12">
         <v>55.8</v>
       </c>
     </row>
@@ -2798,19 +2799,19 @@
       <c r="D90" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E90" s="9">
+      <c r="E90" s="12">
         <v>55.6</v>
       </c>
-      <c r="F90" s="9">
+      <c r="F90" s="12">
         <v>62.8</v>
       </c>
-      <c r="G90" s="9">
+      <c r="G90" s="12">
         <v>64.2</v>
       </c>
-      <c r="H90" s="9">
+      <c r="H90" s="12">
         <v>55.8</v>
       </c>
-      <c r="I90" s="9">
+      <c r="I90" s="12">
         <v>66.8</v>
       </c>
     </row>
@@ -2824,19 +2825,19 @@
       <c r="D91" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E91" s="9">
+      <c r="E91" s="12">
         <v>56.5</v>
       </c>
-      <c r="F91" s="9">
+      <c r="F91" s="12">
         <v>61.8</v>
       </c>
-      <c r="G91" s="9">
+      <c r="G91" s="12">
         <v>64.2</v>
       </c>
-      <c r="H91" s="9">
+      <c r="H91" s="12">
         <v>57.6</v>
       </c>
-      <c r="I91" s="9">
+      <c r="I91" s="12">
         <v>62.9</v>
       </c>
     </row>
@@ -2850,19 +2851,19 @@
       <c r="D92" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E92" s="9">
+      <c r="E92" s="12">
         <v>58.3</v>
       </c>
-      <c r="F92" s="9">
+      <c r="F92" s="12">
         <v>63.5</v>
       </c>
-      <c r="G92" s="9">
+      <c r="G92" s="12">
         <v>66.3</v>
       </c>
-      <c r="H92" s="9">
+      <c r="H92" s="12">
         <v>53</v>
       </c>
-      <c r="I92" s="9">
+      <c r="I92" s="12">
         <v>66.8</v>
       </c>
     </row>
@@ -2876,19 +2877,19 @@
       <c r="D93" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E93" s="9">
+      <c r="E93" s="12">
         <v>52.9</v>
       </c>
-      <c r="F93" s="9">
+      <c r="F93" s="12">
         <v>62.7</v>
       </c>
-      <c r="G93" s="9">
+      <c r="G93" s="12">
         <v>63.8</v>
       </c>
-      <c r="H93" s="9">
+      <c r="H93" s="12">
         <v>44.1</v>
       </c>
-      <c r="I93" s="9">
+      <c r="I93" s="12">
         <v>68.5</v>
       </c>
     </row>
@@ -2902,19 +2903,19 @@
       <c r="D94" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E94" s="9">
+      <c r="E94" s="12">
         <v>55.6</v>
       </c>
-      <c r="F94" s="9">
+      <c r="F94" s="12">
         <v>65.5</v>
       </c>
-      <c r="G94" s="9">
+      <c r="G94" s="12">
         <v>64.900000000000006</v>
       </c>
-      <c r="H94" s="9">
+      <c r="H94" s="12">
         <v>57.8</v>
       </c>
-      <c r="I94" s="9">
+      <c r="I94" s="12">
         <v>65.2</v>
       </c>
     </row>
@@ -2928,19 +2929,19 @@
       <c r="D95" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E95" s="9">
+      <c r="E95" s="12">
         <v>55.3</v>
       </c>
-      <c r="F95" s="9">
+      <c r="F95" s="12">
         <v>66.099999999999994</v>
       </c>
-      <c r="G95" s="9">
+      <c r="G95" s="12">
         <v>64.5</v>
       </c>
-      <c r="H95" s="9">
+      <c r="H95" s="12">
         <v>61</v>
       </c>
-      <c r="I95" s="9">
+      <c r="I95" s="12">
         <v>63.6</v>
       </c>
     </row>
@@ -2954,19 +2955,19 @@
       <c r="D96" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E96" s="9">
+      <c r="E96" s="12">
         <v>56.5</v>
       </c>
-      <c r="F96" s="9">
+      <c r="F96" s="12">
         <v>62</v>
       </c>
-      <c r="G96" s="9">
+      <c r="G96" s="12">
         <v>60.9</v>
       </c>
-      <c r="H96" s="9">
+      <c r="H96" s="12">
         <v>63.8</v>
       </c>
-      <c r="I96" s="9">
+      <c r="I96" s="12">
         <v>65.7</v>
       </c>
     </row>
@@ -2980,19 +2981,19 @@
       <c r="D97" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E97" s="9">
+      <c r="E97" s="12">
         <v>56.4</v>
       </c>
-      <c r="F97" s="9">
+      <c r="F97" s="12">
         <v>62.4</v>
       </c>
-      <c r="G97" s="9">
+      <c r="G97" s="12">
         <v>63.8</v>
       </c>
-      <c r="H97" s="9">
+      <c r="H97" s="12">
         <v>61.6</v>
       </c>
-      <c r="I97" s="9">
+      <c r="I97" s="12">
         <v>69</v>
       </c>
     </row>
@@ -3006,19 +3007,19 @@
       <c r="D98" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E98" s="9">
+      <c r="E98" s="12">
         <v>58.6</v>
       </c>
-      <c r="F98" s="9">
+      <c r="F98" s="12">
         <v>65.400000000000006</v>
       </c>
-      <c r="G98" s="9">
+      <c r="G98" s="12">
         <v>66.900000000000006</v>
       </c>
-      <c r="H98" s="9">
+      <c r="H98" s="12">
         <v>58.4</v>
       </c>
-      <c r="I98" s="9">
+      <c r="I98" s="12">
         <v>71.3</v>
       </c>
     </row>
@@ -3032,19 +3033,19 @@
       <c r="D99" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E99" s="9">
+      <c r="E99" s="12">
         <v>58.9</v>
       </c>
-      <c r="F99" s="9">
+      <c r="F99" s="12">
         <v>65.7</v>
       </c>
-      <c r="G99" s="9">
+      <c r="G99" s="12">
         <v>65.8</v>
       </c>
-      <c r="H99" s="9">
+      <c r="H99" s="12">
         <v>64.099999999999994</v>
       </c>
-      <c r="I99" s="9">
+      <c r="I99" s="12">
         <v>65.8</v>
       </c>
     </row>
@@ -3058,19 +3059,19 @@
       <c r="D100" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E100" s="9">
+      <c r="E100" s="12">
         <v>58.4</v>
       </c>
-      <c r="F100" s="9">
+      <c r="F100" s="12">
         <v>63.6</v>
       </c>
-      <c r="G100" s="9">
+      <c r="G100" s="12">
         <v>68.8</v>
       </c>
-      <c r="H100" s="9">
+      <c r="H100" s="12">
         <v>63.8</v>
       </c>
-      <c r="I100" s="9">
+      <c r="I100" s="12">
         <v>68.8</v>
       </c>
     </row>
@@ -3087,19 +3088,19 @@
       <c r="D101" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E101" s="9">
+      <c r="E101" s="12">
         <v>57.3</v>
       </c>
-      <c r="F101" s="9">
+      <c r="F101" s="12">
         <v>65.8</v>
       </c>
-      <c r="G101" s="9">
+      <c r="G101" s="12">
         <v>68</v>
       </c>
-      <c r="H101" s="9">
+      <c r="H101" s="12">
         <v>66.8</v>
       </c>
-      <c r="I101" s="9">
+      <c r="I101" s="12">
         <v>61.6</v>
       </c>
     </row>
@@ -3116,19 +3117,19 @@
       <c r="D102" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E102" s="9">
+      <c r="E102" s="12">
         <v>62</v>
       </c>
-      <c r="F102" s="9">
+      <c r="F102" s="12">
         <v>66.099999999999994</v>
       </c>
-      <c r="G102" s="9">
+      <c r="G102" s="12">
         <v>73.099999999999994</v>
       </c>
-      <c r="H102" s="9">
+      <c r="H102" s="12">
         <v>70.400000000000006</v>
       </c>
-      <c r="I102" s="9">
+      <c r="I102" s="12">
         <v>70.2</v>
       </c>
     </row>
@@ -3145,19 +3146,19 @@
       <c r="D103" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E103" s="9">
+      <c r="E103" s="12">
         <v>62.8</v>
       </c>
-      <c r="F103" s="9">
+      <c r="F103" s="12">
         <v>66.2</v>
       </c>
-      <c r="G103" s="9">
+      <c r="G103" s="12">
         <v>77</v>
       </c>
-      <c r="H103" s="9">
+      <c r="H103" s="12">
         <v>65.5</v>
       </c>
-      <c r="I103" s="9">
+      <c r="I103" s="12">
         <v>77.3</v>
       </c>
     </row>
@@ -3174,19 +3175,19 @@
       <c r="D104" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E104" s="9">
+      <c r="E104" s="12">
         <v>57.1</v>
       </c>
-      <c r="F104" s="9">
+      <c r="F104" s="12">
         <v>60.6</v>
       </c>
-      <c r="G104" s="9">
+      <c r="G104" s="12">
         <v>61</v>
       </c>
-      <c r="H104" s="9">
+      <c r="H104" s="12">
         <v>56.4</v>
       </c>
-      <c r="I104" s="9">
+      <c r="I104" s="12">
         <v>70.599999999999994</v>
       </c>
     </row>
@@ -3203,19 +3204,19 @@
       <c r="D105" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E105" s="9">
+      <c r="E105" s="12">
         <v>58.8</v>
       </c>
-      <c r="F105" s="9">
+      <c r="F105" s="12">
         <v>60.6</v>
       </c>
-      <c r="G105" s="9">
+      <c r="G105" s="12">
         <v>72.3</v>
       </c>
-      <c r="H105" s="9">
+      <c r="H105" s="12">
         <v>62.3</v>
       </c>
-      <c r="I105" s="9">
+      <c r="I105" s="12">
         <v>75.599999999999994</v>
       </c>
     </row>
@@ -3232,19 +3233,19 @@
       <c r="D106" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E106" s="9">
+      <c r="E106" s="12">
         <v>59.4</v>
       </c>
-      <c r="F106" s="9">
+      <c r="F106" s="12">
         <v>65.099999999999994</v>
       </c>
-      <c r="G106" s="9">
+      <c r="G106" s="12">
         <v>72.099999999999994</v>
       </c>
-      <c r="H106" s="9">
+      <c r="H106" s="12">
         <v>63.1</v>
       </c>
-      <c r="I106" s="9">
+      <c r="I106" s="12">
         <v>78.400000000000006</v>
       </c>
     </row>
@@ -3261,19 +3262,19 @@
       <c r="D107" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E107" s="9">
+      <c r="E107" s="12">
         <v>60.7</v>
       </c>
-      <c r="F107" s="9">
+      <c r="F107" s="12">
         <v>64.5</v>
       </c>
-      <c r="G107" s="9">
+      <c r="G107" s="12">
         <v>68.3</v>
       </c>
-      <c r="H107" s="9">
+      <c r="H107" s="12">
         <v>62</v>
       </c>
-      <c r="I107" s="9">
+      <c r="I107" s="12">
         <v>80.900000000000006</v>
       </c>
     </row>
@@ -3290,19 +3291,19 @@
       <c r="D108" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E108" s="9">
+      <c r="E108" s="12">
         <v>59.2</v>
       </c>
-      <c r="F108" s="9">
+      <c r="F108" s="12">
         <v>62.6</v>
       </c>
-      <c r="G108" s="9">
+      <c r="G108" s="12">
         <v>68.3</v>
       </c>
-      <c r="H108" s="9">
+      <c r="H108" s="12">
         <v>63</v>
       </c>
-      <c r="I108" s="9">
+      <c r="I108" s="12">
         <v>71.900000000000006</v>
       </c>
     </row>
@@ -3319,19 +3320,19 @@
       <c r="D109" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E109" s="9">
+      <c r="E109" s="12">
         <v>59.3</v>
       </c>
-      <c r="F109" s="9">
+      <c r="F109" s="12">
         <v>63.9</v>
       </c>
-      <c r="G109" s="9">
+      <c r="G109" s="12">
         <v>72.2</v>
       </c>
-      <c r="H109" s="9">
+      <c r="H109" s="12">
         <v>65.099999999999994</v>
       </c>
-      <c r="I109" s="9">
+      <c r="I109" s="12">
         <v>79.2</v>
       </c>
     </row>
@@ -3348,19 +3349,19 @@
       <c r="D110" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E110" s="9">
+      <c r="E110" s="12">
         <v>57.4</v>
       </c>
-      <c r="F110" s="9">
+      <c r="F110" s="12">
         <v>59.6</v>
       </c>
-      <c r="G110" s="9">
+      <c r="G110" s="12">
         <v>66</v>
       </c>
-      <c r="H110" s="9">
+      <c r="H110" s="12">
         <v>54.2</v>
       </c>
-      <c r="I110" s="9">
+      <c r="I110" s="12">
         <v>75.5</v>
       </c>
     </row>
@@ -3377,19 +3378,19 @@
       <c r="D111" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E111" s="9">
+      <c r="E111" s="12">
         <v>57.4</v>
       </c>
-      <c r="F111" s="9">
+      <c r="F111" s="12">
         <v>64.599999999999994</v>
       </c>
-      <c r="G111" s="9">
+      <c r="G111" s="12">
         <v>67.7</v>
       </c>
-      <c r="H111" s="9">
+      <c r="H111" s="12">
         <v>61.7</v>
       </c>
-      <c r="I111" s="9">
+      <c r="I111" s="12">
         <v>73.2</v>
       </c>
     </row>
@@ -3406,23 +3407,23 @@
       <c r="D112" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="E112" s="9">
+      <c r="E112" s="12">
         <v>55.7</v>
       </c>
-      <c r="F112" s="9">
+      <c r="F112" s="12">
         <v>62.9</v>
       </c>
-      <c r="G112" s="9">
+      <c r="G112" s="12">
         <v>62.9</v>
       </c>
-      <c r="H112" s="9">
+      <c r="H112" s="12">
         <v>64.900000000000006</v>
       </c>
-      <c r="I112" s="9">
+      <c r="I112" s="12">
         <v>70.8</v>
       </c>
     </row>
-    <row r="113" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A113" s="3">
         <v>45992</v>
       </c>
@@ -3433,6 +3434,35 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D113" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="E113" s="12">
+        <v>54.2</v>
+      </c>
+      <c r="F113" s="13">
+        <v>65.3</v>
+      </c>
+      <c r="G113" s="13">
+        <v>66.2</v>
+      </c>
+      <c r="H113" s="13">
+        <v>66.7</v>
+      </c>
+      <c r="I113" s="13">
+        <v>62.9</v>
+      </c>
+    </row>
+    <row r="114" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A114" s="3">
+        <v>46023</v>
+      </c>
+      <c r="B114" s="3">
+        <v>45691</v>
+      </c>
+      <c r="C114" s="2">
+        <v>0.45833333333333331</v>
+      </c>
+      <c r="D114" s="2" t="s">
         <v>12</v>
       </c>
     </row>
@@ -3452,10 +3482,10 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C2" s="11" t="s">
+      <c r="C2" s="7" t="s">
         <v>7</v>
       </c>
       <c r="D2" s="1"/>
@@ -3468,7 +3498,7 @@
       <c r="K2" s="1"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B3" s="12" t="s">
+      <c r="B3" s="8" t="s">
         <v>9</v>
       </c>
       <c r="C3" t="s">

--- a/data/macro/USA/Logistic manager index.xlsx
+++ b/data/macro/USA/Logistic manager index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tommy/Desktop/Pycharm/AlternativeData/data/macro/USA/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AC2FC860-D069-274A-B4B6-FF269AFCB551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A9A4B4-AC35-4633-B17A-346F9021296C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28500" yWindow="1020" windowWidth="22260" windowHeight="12640" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28500" yWindow="1020" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LMI" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="14">
   <si>
     <t>Inventory Costs</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -89,30 +89,31 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="[$-409]h:mm\ AM/PM;@"/>
-    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+  <numFmts count="5">
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="176" formatCode="[$-409]h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="180" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="9">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -127,7 +128,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -135,7 +136,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
+      <name val="맑은 고딕"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -179,12 +180,12 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -193,40 +194,43 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="180" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
-    <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="쉼표" xfId="1" builtinId="3"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="하이퍼링크" xfId="2" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -244,7 +248,7 @@
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
+  <c:lang val="ko-KR"/>
   <c:roundedCorners val="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
@@ -289,10 +293,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>LMI!$A$2:$A$114</c:f>
+              <c:f>LMI!$A$2:$A$1114</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="1113"/>
                 <c:pt idx="0">
                   <c:v>42614</c:v>
                 </c:pt>
@@ -631,16 +635,22 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>46023</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46054</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>46082</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>LMI!$E$2:$E$114</c:f>
+              <c:f>LMI!$E$2:$E$1114</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.0_-;\-* #,##0.0_-;_-* "-"??_-;_-@_-</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="1113"/>
                 <c:pt idx="0">
                   <c:v>63.9</c:v>
                 </c:pt>
@@ -979,6 +989,9 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>59.6</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>61.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1018,10 +1031,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>LMI!$A$2:$A$114</c:f>
+              <c:f>LMI!$A$2:$A$1114</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="1113"/>
                 <c:pt idx="0">
                   <c:v>42614</c:v>
                 </c:pt>
@@ -1360,16 +1373,22 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>46023</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46054</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>46082</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>LMI!$F$2:$F$114</c:f>
+              <c:f>LMI!$F$2:$F$1114</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.0_-;\-* #,##0.0_-;_-* "-"??_-;_-@_-</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="1113"/>
                 <c:pt idx="24">
                   <c:v>71</c:v>
                 </c:pt>
@@ -1636,6 +1655,9 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>65.8</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>66.3</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1675,10 +1697,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>LMI!$A$2:$A$114</c:f>
+              <c:f>LMI!$A$2:$A$1114</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="1113"/>
                 <c:pt idx="0">
                   <c:v>42614</c:v>
                 </c:pt>
@@ -2017,16 +2039,22 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>46023</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46054</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>46082</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>LMI!$G$2:$G$114</c:f>
+              <c:f>LMI!$G$2:$G$1114</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.0_-;\-* #,##0.0_-;_-* "-"??_-;_-@_-</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="1113"/>
                 <c:pt idx="0">
                   <c:v>76.900000000000006</c:v>
                 </c:pt>
@@ -2365,6 +2393,9 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>64.8</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>62.6</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2404,10 +2435,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>LMI!$A$2:$A$114</c:f>
+              <c:f>LMI!$A$2:$A$1114</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="1113"/>
                 <c:pt idx="0">
                   <c:v>42614</c:v>
                 </c:pt>
@@ -2746,16 +2777,22 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>46023</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46054</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>46082</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>LMI!$H$2:$H$114</c:f>
+              <c:f>LMI!$H$2:$H$1114</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.0_-;\-* #,##0.0_-;_-* "-"??_-;_-@_-</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="1113"/>
                 <c:pt idx="0">
                   <c:v>65.599999999999994</c:v>
                 </c:pt>
@@ -3094,6 +3131,9 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>71.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>76.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3133,10 +3173,10 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>LMI!$A$2:$A$114</c:f>
+              <c:f>LMI!$A$2:$A$1114</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd;@</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="1113"/>
                 <c:pt idx="0">
                   <c:v>42614</c:v>
                 </c:pt>
@@ -3475,16 +3515,22 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>46023</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>46054</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>46082</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>LMI!$I$2:$I$114</c:f>
+              <c:f>LMI!$I$2:$I$1114</c:f>
               <c:numCache>
                 <c:formatCode>_-* #,##0.0_-;\-* #,##0.0_-;_-* "-"??_-;_-@_-</c:formatCode>
-                <c:ptCount val="113"/>
+                <c:ptCount val="1113"/>
                 <c:pt idx="0">
                   <c:v>67.599999999999994</c:v>
                 </c:pt>
@@ -3823,6 +3869,9 @@
                 </c:pt>
                 <c:pt idx="112">
                   <c:v>71.3</c:v>
+                </c:pt>
+                <c:pt idx="113">
+                  <c:v>67.8</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3904,6 +3953,8 @@
         <c:axId val="2086269119"/>
         <c:scaling>
           <c:orientation val="minMax"/>
+          <c:max val="100"/>
+          <c:min val="20"/>
         </c:scaling>
         <c:delete val="0"/>
         <c:axPos val="l"/>
@@ -3921,7 +3972,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-" sourceLinked="1"/>
+        <c:numFmt formatCode="#,##0_);[Red]\(#,##0\)" sourceLinked="0"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -3955,6 +4006,7 @@
         <c:crossAx val="174805823"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
+        <c:majorUnit val="10"/>
       </c:valAx>
       <c:spPr>
         <a:noFill/>
@@ -3997,7 +4049,6 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
-    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4005,6 +4056,7 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
+    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4896,2998 +4948,3025 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I115"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="13"/>
+  <dimension ref="A1:I116"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="11.33203125" style="10" bestFit="1" customWidth="1"/>
-    <col min="3" max="4" width="11.1640625" style="11" customWidth="1"/>
-    <col min="5" max="5" width="8.1640625" style="12" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.6640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.6640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.1640625" style="13" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="19" style="13" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="9" style="9"/>
+    <col min="1" max="2" width="11.375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.125" style="10" customWidth="1"/>
+    <col min="5" max="5" width="8.125" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.625" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.625" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="19" style="12" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>5</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="14" t="s">
         <v>13</v>
       </c>
-      <c r="D1" s="6" t="s">
+      <c r="D1" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="6" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="8" t="s">
+      <c r="F1" s="7" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="8" t="s">
+      <c r="G1" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="H1" s="8" t="s">
+      <c r="H1" s="7" t="s">
         <v>1</v>
       </c>
-      <c r="I1" s="8" t="s">
+      <c r="I1" s="7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="10">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A2" s="9">
         <v>42614</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="9">
         <v>42647</v>
       </c>
-      <c r="D2" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E2" s="11">
         <v>63.9</v>
       </c>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12">
+      <c r="F2" s="11"/>
+      <c r="G2" s="11">
         <v>76.900000000000006</v>
       </c>
-      <c r="H2" s="12">
+      <c r="H2" s="11">
         <v>65.599999999999994</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>67.599999999999994</v>
       </c>
     </row>
-    <row r="3" spans="1:9">
-      <c r="A3" s="10">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A3" s="9">
         <v>42644</v>
       </c>
-      <c r="B3" s="10">
+      <c r="B3" s="9">
         <v>42675</v>
       </c>
-      <c r="D3" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" s="12">
+      <c r="D3" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E3" s="11">
         <v>54.9</v>
       </c>
-      <c r="F3" s="12"/>
-      <c r="G3" s="12">
+      <c r="F3" s="11"/>
+      <c r="G3" s="11">
         <v>68.900000000000006</v>
       </c>
-      <c r="H3" s="12">
+      <c r="H3" s="11">
         <v>65.099999999999994</v>
       </c>
-      <c r="I3" s="12">
+      <c r="I3" s="11">
         <v>59.5</v>
       </c>
     </row>
-    <row r="4" spans="1:9">
-      <c r="A4" s="10">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A4" s="9">
         <v>42675</v>
       </c>
-      <c r="B4" s="10">
+      <c r="B4" s="9">
         <v>42710</v>
       </c>
-      <c r="D4" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E4" s="12">
+      <c r="D4" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="11">
         <v>62.9</v>
       </c>
-      <c r="F4" s="12"/>
-      <c r="G4" s="12">
+      <c r="F4" s="11"/>
+      <c r="G4" s="11">
         <v>71.8</v>
       </c>
-      <c r="H4" s="12">
+      <c r="H4" s="11">
         <v>67.2</v>
       </c>
-      <c r="I4" s="12">
+      <c r="I4" s="11">
         <v>65.5</v>
       </c>
     </row>
-    <row r="5" spans="1:9">
-      <c r="A5" s="10">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A5" s="9">
         <v>42705</v>
       </c>
-      <c r="B5" s="10">
+      <c r="B5" s="9">
         <v>42738</v>
       </c>
-      <c r="D5" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E5" s="12">
+      <c r="D5" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="11">
         <v>62.9</v>
       </c>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12">
+      <c r="F5" s="11"/>
+      <c r="G5" s="11">
         <v>71.8</v>
       </c>
-      <c r="H5" s="12">
+      <c r="H5" s="11">
         <v>67.2</v>
       </c>
-      <c r="I5" s="12">
+      <c r="I5" s="11">
         <v>65.5</v>
       </c>
     </row>
-    <row r="6" spans="1:9">
-      <c r="A6" s="10">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A6" s="9">
         <v>42736</v>
       </c>
-      <c r="B6" s="10">
+      <c r="B6" s="9">
         <v>42773</v>
       </c>
-      <c r="D6" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E6" s="12">
+      <c r="D6" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="11">
         <v>66</v>
       </c>
-      <c r="F6" s="12"/>
-      <c r="G6" s="12">
+      <c r="F6" s="11"/>
+      <c r="G6" s="11">
         <v>69.7</v>
       </c>
-      <c r="H6" s="12">
+      <c r="H6" s="11">
         <v>75.3</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="11">
         <v>65.400000000000006</v>
       </c>
     </row>
-    <row r="7" spans="1:9">
-      <c r="A7" s="10">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A7" s="9">
         <v>42767</v>
       </c>
-      <c r="B7" s="10">
+      <c r="B7" s="9">
         <v>42801</v>
       </c>
-      <c r="D7" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E7" s="12">
+      <c r="D7" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E7" s="11">
         <v>66</v>
       </c>
-      <c r="F7" s="12"/>
-      <c r="G7" s="12">
+      <c r="F7" s="11"/>
+      <c r="G7" s="11">
         <v>69.7</v>
       </c>
-      <c r="H7" s="12">
+      <c r="H7" s="11">
         <v>75.3</v>
       </c>
-      <c r="I7" s="12">
+      <c r="I7" s="11">
         <v>65.400000000000006</v>
       </c>
     </row>
-    <row r="8" spans="1:9">
-      <c r="A8" s="10">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A8" s="9">
         <v>42795</v>
       </c>
-      <c r="B8" s="10">
+      <c r="B8" s="9">
         <v>42829</v>
       </c>
-      <c r="D8" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E8" s="12">
+      <c r="D8" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E8" s="11">
         <v>65.599999999999994</v>
       </c>
-      <c r="F8" s="12"/>
-      <c r="G8" s="12">
+      <c r="F8" s="11"/>
+      <c r="G8" s="11">
         <v>61</v>
       </c>
-      <c r="H8" s="12">
+      <c r="H8" s="11">
         <v>70.5</v>
       </c>
-      <c r="I8" s="12">
+      <c r="I8" s="11">
         <v>68.900000000000006</v>
       </c>
     </row>
-    <row r="9" spans="1:9">
-      <c r="A9" s="10">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A9" s="9">
         <v>42826</v>
       </c>
-      <c r="B9" s="10">
+      <c r="B9" s="9">
         <v>42857</v>
       </c>
-      <c r="D9" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E9" s="12">
+      <c r="D9" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E9" s="11">
         <v>65.599999999999994</v>
       </c>
-      <c r="F9" s="12"/>
-      <c r="G9" s="12">
+      <c r="F9" s="11"/>
+      <c r="G9" s="11">
         <v>61</v>
       </c>
-      <c r="H9" s="12">
+      <c r="H9" s="11">
         <v>70.5</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="11">
         <v>68.900000000000006</v>
       </c>
     </row>
-    <row r="10" spans="1:9">
-      <c r="A10" s="10">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A10" s="9">
         <v>42856</v>
       </c>
-      <c r="B10" s="10">
+      <c r="B10" s="9">
         <v>42892</v>
       </c>
-      <c r="D10" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E10" s="12">
+      <c r="D10" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E10" s="11">
         <v>65</v>
       </c>
-      <c r="F10" s="12"/>
-      <c r="G10" s="12">
+      <c r="F10" s="11"/>
+      <c r="G10" s="11">
         <v>70.900000000000006</v>
       </c>
-      <c r="H10" s="12">
+      <c r="H10" s="11">
         <v>76.3</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="11">
         <v>75.5</v>
       </c>
     </row>
-    <row r="11" spans="1:9">
-      <c r="A11" s="10">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A11" s="9">
         <v>42887</v>
       </c>
-      <c r="B11" s="10">
+      <c r="B11" s="9">
         <v>42920</v>
       </c>
-      <c r="D11" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E11" s="12">
+      <c r="D11" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" s="11">
         <v>65</v>
       </c>
-      <c r="F11" s="12"/>
-      <c r="G11" s="12">
+      <c r="F11" s="11"/>
+      <c r="G11" s="11">
         <v>70.900000000000006</v>
       </c>
-      <c r="H11" s="12">
+      <c r="H11" s="11">
         <v>76.3</v>
       </c>
-      <c r="I11" s="12">
+      <c r="I11" s="11">
         <v>75.5</v>
       </c>
     </row>
-    <row r="12" spans="1:9">
-      <c r="A12" s="10">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A12" s="9">
         <v>42917</v>
       </c>
-      <c r="B12" s="10">
+      <c r="B12" s="9">
         <v>42948</v>
       </c>
-      <c r="D12" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E12" s="12">
+      <c r="D12" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E12" s="11">
         <v>62.78</v>
       </c>
-      <c r="F12" s="12"/>
-      <c r="G12" s="12">
+      <c r="F12" s="11"/>
+      <c r="G12" s="11">
         <v>63.71</v>
       </c>
-      <c r="H12" s="12">
+      <c r="H12" s="11">
         <v>76.12</v>
       </c>
-      <c r="I12" s="12">
+      <c r="I12" s="11">
         <v>70.16</v>
       </c>
     </row>
-    <row r="13" spans="1:9">
-      <c r="A13" s="10">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A13" s="9">
         <v>42948</v>
       </c>
-      <c r="B13" s="10">
+      <c r="B13" s="9">
         <v>42983</v>
       </c>
-      <c r="D13" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="12">
+      <c r="D13" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="11">
         <v>62.78</v>
       </c>
-      <c r="F13" s="12"/>
-      <c r="G13" s="12">
+      <c r="F13" s="11"/>
+      <c r="G13" s="11">
         <v>63.71</v>
       </c>
-      <c r="H13" s="12">
+      <c r="H13" s="11">
         <v>76.12</v>
       </c>
-      <c r="I13" s="12">
+      <c r="I13" s="11">
         <v>70.16</v>
       </c>
     </row>
-    <row r="14" spans="1:9">
-      <c r="A14" s="10">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A14" s="9">
         <v>42979</v>
       </c>
-      <c r="B14" s="10">
+      <c r="B14" s="9">
         <v>43011</v>
       </c>
-      <c r="D14" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E14" s="12">
+      <c r="D14" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E14" s="11">
         <v>66.180000000000007</v>
       </c>
-      <c r="F14" s="12"/>
-      <c r="G14" s="12">
+      <c r="F14" s="11"/>
+      <c r="G14" s="11">
         <v>69.510000000000005</v>
       </c>
-      <c r="H14" s="12">
+      <c r="H14" s="11">
         <v>86.03</v>
       </c>
-      <c r="I14" s="12">
+      <c r="I14" s="11">
         <v>70.8</v>
       </c>
     </row>
-    <row r="15" spans="1:9">
-      <c r="A15" s="10">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A15" s="9">
         <v>43009</v>
       </c>
-      <c r="B15" s="10">
+      <c r="B15" s="9">
         <v>43046</v>
       </c>
-      <c r="D15" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E15" s="12">
+      <c r="D15" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E15" s="11">
         <v>66.180000000000007</v>
       </c>
-      <c r="F15" s="12"/>
-      <c r="G15" s="12">
+      <c r="F15" s="11"/>
+      <c r="G15" s="11">
         <v>69.510000000000005</v>
       </c>
-      <c r="H15" s="12">
+      <c r="H15" s="11">
         <v>86.03</v>
       </c>
-      <c r="I15" s="12">
+      <c r="I15" s="11">
         <v>70.8</v>
       </c>
     </row>
-    <row r="16" spans="1:9">
-      <c r="A16" s="10">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A16" s="9">
         <v>43040</v>
       </c>
-      <c r="B16" s="10">
+      <c r="B16" s="9">
         <v>43074</v>
       </c>
-      <c r="D16" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E16" s="12">
+      <c r="D16" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="11">
         <v>66.180000000000007</v>
       </c>
-      <c r="F16" s="12"/>
-      <c r="G16" s="12">
+      <c r="F16" s="11"/>
+      <c r="G16" s="11">
         <v>69.510000000000005</v>
       </c>
-      <c r="H16" s="12">
+      <c r="H16" s="11">
         <v>86.03</v>
       </c>
-      <c r="I16" s="12">
+      <c r="I16" s="11">
         <v>70.8</v>
       </c>
     </row>
-    <row r="17" spans="1:9">
-      <c r="A17" s="10">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A17" s="9">
         <v>43070</v>
       </c>
-      <c r="B17" s="10">
+      <c r="B17" s="9">
         <v>43102</v>
       </c>
-      <c r="D17" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E17" s="12">
+      <c r="D17" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="11">
         <v>66.180000000000007</v>
       </c>
-      <c r="F17" s="12"/>
-      <c r="G17" s="12">
+      <c r="F17" s="11"/>
+      <c r="G17" s="11">
         <v>69.510000000000005</v>
       </c>
-      <c r="H17" s="12">
+      <c r="H17" s="11">
         <v>86.03</v>
       </c>
-      <c r="I17" s="12">
+      <c r="I17" s="11">
         <v>70.8</v>
       </c>
     </row>
-    <row r="18" spans="1:9">
-      <c r="A18" s="10">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A18" s="9">
         <v>43101</v>
       </c>
-      <c r="B18" s="10">
+      <c r="B18" s="9">
         <v>43137</v>
       </c>
-      <c r="D18" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E18" s="12">
+      <c r="D18" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E18" s="11">
         <v>64.099999999999994</v>
       </c>
-      <c r="F18" s="12"/>
-      <c r="G18" s="12">
+      <c r="F18" s="11"/>
+      <c r="G18" s="11">
         <v>75</v>
       </c>
-      <c r="H18" s="12">
+      <c r="H18" s="11">
         <v>93.1</v>
       </c>
-      <c r="I18" s="12">
+      <c r="I18" s="11">
         <v>69.400000000000006</v>
       </c>
     </row>
-    <row r="19" spans="1:9">
-      <c r="A19" s="10">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A19" s="9">
         <v>43132</v>
       </c>
-      <c r="B19" s="10">
+      <c r="B19" s="9">
         <v>43165</v>
       </c>
-      <c r="D19" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E19" s="12">
+      <c r="D19" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="11">
         <v>64.099999999999994</v>
       </c>
-      <c r="F19" s="12"/>
-      <c r="G19" s="12">
+      <c r="F19" s="11"/>
+      <c r="G19" s="11">
         <v>75</v>
       </c>
-      <c r="H19" s="12">
+      <c r="H19" s="11">
         <v>93.1</v>
       </c>
-      <c r="I19" s="12">
+      <c r="I19" s="11">
         <v>69.400000000000006</v>
       </c>
     </row>
-    <row r="20" spans="1:9">
-      <c r="A20" s="10">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="9">
         <v>43160</v>
       </c>
-      <c r="B20" s="10">
+      <c r="B20" s="9">
         <v>43193</v>
       </c>
-      <c r="D20" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="12">
+      <c r="D20" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="11">
         <v>70.83</v>
       </c>
-      <c r="F20" s="12"/>
-      <c r="G20" s="12">
+      <c r="F20" s="11"/>
+      <c r="G20" s="11">
         <v>77.819999999999993</v>
       </c>
-      <c r="H20" s="12">
+      <c r="H20" s="11">
         <v>95.81</v>
       </c>
-      <c r="I20" s="12">
+      <c r="I20" s="11">
         <v>81.34</v>
       </c>
     </row>
-    <row r="21" spans="1:9">
-      <c r="A21" s="10">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A21" s="9">
         <v>43191</v>
       </c>
-      <c r="B21" s="10">
+      <c r="B21" s="9">
         <v>43221</v>
       </c>
-      <c r="D21" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E21" s="12">
+      <c r="D21" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="11">
         <v>70.83</v>
       </c>
-      <c r="F21" s="12"/>
-      <c r="G21" s="12">
+      <c r="F21" s="11"/>
+      <c r="G21" s="11">
         <v>77.819999999999993</v>
       </c>
-      <c r="H21" s="12">
+      <c r="H21" s="11">
         <v>95.81</v>
       </c>
-      <c r="I21" s="12">
+      <c r="I21" s="11">
         <v>81.34</v>
       </c>
     </row>
-    <row r="22" spans="1:9">
-      <c r="A22" s="10">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="9">
         <v>43221</v>
       </c>
-      <c r="B22" s="10">
+      <c r="B22" s="9">
         <v>43256</v>
       </c>
-      <c r="D22" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E22" s="12">
+      <c r="D22" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E22" s="11">
         <v>69</v>
       </c>
-      <c r="F22" s="12"/>
-      <c r="G22" s="12">
+      <c r="F22" s="11"/>
+      <c r="G22" s="11">
         <v>79.12</v>
       </c>
-      <c r="H22" s="12">
+      <c r="H22" s="11">
         <v>94.05</v>
       </c>
-      <c r="I22" s="12">
+      <c r="I22" s="11">
         <v>76.94</v>
       </c>
     </row>
-    <row r="23" spans="1:9">
-      <c r="A23" s="10">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="9">
         <v>43252</v>
       </c>
-      <c r="B23" s="10">
+      <c r="B23" s="9">
         <v>43284</v>
       </c>
-      <c r="D23" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E23" s="12">
+      <c r="D23" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E23" s="11">
         <v>69</v>
       </c>
-      <c r="F23" s="12"/>
-      <c r="G23" s="12">
+      <c r="F23" s="11"/>
+      <c r="G23" s="11">
         <v>79.12</v>
       </c>
-      <c r="H23" s="12">
+      <c r="H23" s="11">
         <v>94.05</v>
       </c>
-      <c r="I23" s="12">
+      <c r="I23" s="11">
         <v>76.94</v>
       </c>
     </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="10">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A24" s="9">
         <v>43282</v>
       </c>
-      <c r="B24" s="10">
+      <c r="B24" s="9">
         <v>43319</v>
       </c>
-      <c r="D24" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E24" s="12">
+      <c r="D24" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E24" s="11">
         <v>68.790000000000006</v>
       </c>
-      <c r="F24" s="12"/>
-      <c r="G24" s="12">
+      <c r="F24" s="11"/>
+      <c r="G24" s="11">
         <v>80.38</v>
       </c>
-      <c r="H24" s="12">
+      <c r="H24" s="11">
         <v>92.68</v>
       </c>
-      <c r="I24" s="12">
+      <c r="I24" s="11">
         <v>79.02</v>
       </c>
     </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="10">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A25" s="9">
         <v>43313</v>
       </c>
-      <c r="B25" s="10">
+      <c r="B25" s="9">
         <v>43347</v>
       </c>
-      <c r="D25" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="12">
+      <c r="D25" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="11">
         <v>68.790000000000006</v>
       </c>
-      <c r="F25" s="12"/>
-      <c r="G25" s="12">
+      <c r="F25" s="11"/>
+      <c r="G25" s="11">
         <v>80.38</v>
       </c>
-      <c r="H25" s="12">
+      <c r="H25" s="11">
         <v>92.68</v>
       </c>
-      <c r="I25" s="12">
+      <c r="I25" s="11">
         <v>79.02</v>
       </c>
     </row>
-    <row r="26" spans="1:9">
-      <c r="A26" s="10">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A26" s="9">
         <v>43344</v>
       </c>
-      <c r="B26" s="10">
+      <c r="B26" s="9">
         <v>43375</v>
       </c>
-      <c r="D26" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E26" s="12">
+      <c r="D26" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E26" s="11">
         <v>70.22</v>
       </c>
-      <c r="F26" s="12">
+      <c r="F26" s="11">
         <v>71</v>
       </c>
-      <c r="G26" s="12">
+      <c r="G26" s="11">
         <v>80.510000000000005</v>
       </c>
-      <c r="H26" s="12">
+      <c r="H26" s="11">
         <v>89.9</v>
       </c>
-      <c r="I26" s="12">
+      <c r="I26" s="11">
         <v>78.78</v>
       </c>
     </row>
-    <row r="27" spans="1:9">
-      <c r="A27" s="10">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A27" s="9">
         <v>43374</v>
       </c>
-      <c r="B27" s="10">
+      <c r="B27" s="9">
         <v>43410</v>
       </c>
-      <c r="D27" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E27" s="12">
+      <c r="D27" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E27" s="11">
         <v>69.010000000000005</v>
       </c>
-      <c r="F27" s="12">
+      <c r="F27" s="11">
         <v>72</v>
       </c>
-      <c r="G27" s="12">
+      <c r="G27" s="11">
         <v>80.510000000000005</v>
       </c>
-      <c r="H27" s="12">
+      <c r="H27" s="11">
         <v>87.94</v>
       </c>
-      <c r="I27" s="12">
+      <c r="I27" s="11">
         <v>81.400000000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:9">
-      <c r="A28" s="10">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A28" s="9">
         <v>43405</v>
       </c>
-      <c r="B28" s="10">
+      <c r="B28" s="9">
         <v>43438</v>
       </c>
-      <c r="D28" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E28" s="12">
+      <c r="D28" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E28" s="11">
         <v>66.66</v>
       </c>
-      <c r="F28" s="12">
+      <c r="F28" s="11">
         <v>71.8</v>
       </c>
-      <c r="G28" s="12">
+      <c r="G28" s="11">
         <v>77.02</v>
       </c>
-      <c r="H28" s="12">
+      <c r="H28" s="11">
         <v>79.790000000000006</v>
       </c>
-      <c r="I28" s="12">
+      <c r="I28" s="11">
         <v>73.53</v>
       </c>
     </row>
-    <row r="29" spans="1:9">
-      <c r="A29" s="10">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A29" s="9">
         <v>43435</v>
       </c>
-      <c r="B29" s="10">
+      <c r="B29" s="9">
         <v>43467</v>
       </c>
-      <c r="D29" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E29" s="12">
+      <c r="D29" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E29" s="11">
         <v>64.650000000000006</v>
       </c>
-      <c r="F29" s="12">
+      <c r="F29" s="11">
         <v>68.8</v>
       </c>
-      <c r="G29" s="12">
+      <c r="G29" s="11">
         <v>74.760000000000005</v>
       </c>
-      <c r="H29" s="12">
+      <c r="H29" s="11">
         <v>74.34</v>
       </c>
-      <c r="I29" s="12">
+      <c r="I29" s="11">
         <v>72.73</v>
       </c>
     </row>
-    <row r="30" spans="1:9">
-      <c r="A30" s="10">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" s="9">
         <v>43466</v>
       </c>
-      <c r="B30" s="10">
+      <c r="B30" s="9">
         <v>43501</v>
       </c>
-      <c r="D30" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E30" s="12">
+      <c r="D30" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E30" s="11">
         <v>65.2</v>
       </c>
-      <c r="F30" s="12">
+      <c r="F30" s="11">
         <v>66.8</v>
       </c>
-      <c r="G30" s="12">
+      <c r="G30" s="11">
         <v>79.959999999999994</v>
       </c>
-      <c r="H30" s="12">
+      <c r="H30" s="11">
         <v>69.38</v>
       </c>
-      <c r="I30" s="12">
+      <c r="I30" s="11">
         <v>75.650000000000006</v>
       </c>
     </row>
-    <row r="31" spans="1:9">
-      <c r="A31" s="10">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" s="9">
         <v>43497</v>
       </c>
-      <c r="B31" s="10">
+      <c r="B31" s="9">
         <v>43529</v>
       </c>
-      <c r="D31" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E31" s="12">
+      <c r="D31" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E31" s="11">
         <v>61.95</v>
       </c>
-      <c r="F31" s="12">
+      <c r="F31" s="11">
         <v>63.1</v>
       </c>
-      <c r="G31" s="12">
+      <c r="G31" s="11">
         <v>72.33</v>
       </c>
-      <c r="H31" s="12">
+      <c r="H31" s="11">
         <v>67.23</v>
       </c>
-      <c r="I31" s="12">
+      <c r="I31" s="11">
         <v>74.510000000000005</v>
       </c>
     </row>
-    <row r="32" spans="1:9">
-      <c r="A32" s="10">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A32" s="9">
         <v>43525</v>
       </c>
-      <c r="B32" s="10">
+      <c r="B32" s="9">
         <v>43557</v>
       </c>
-      <c r="D32" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E32" s="12">
+      <c r="D32" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E32" s="11">
         <v>60.4</v>
       </c>
-      <c r="F32" s="12">
+      <c r="F32" s="11">
         <v>63.6</v>
       </c>
-      <c r="G32" s="12">
+      <c r="G32" s="11">
         <v>76.7</v>
       </c>
-      <c r="H32" s="12">
+      <c r="H32" s="11">
         <v>65.5</v>
       </c>
-      <c r="I32" s="12">
+      <c r="I32" s="11">
         <v>69.900000000000006</v>
       </c>
     </row>
-    <row r="33" spans="1:9">
-      <c r="A33" s="10">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A33" s="9">
         <v>43556</v>
       </c>
-      <c r="B33" s="10">
+      <c r="B33" s="9">
         <v>43592</v>
       </c>
-      <c r="D33" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E33" s="12">
+      <c r="D33" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E33" s="11">
         <v>57.9</v>
       </c>
-      <c r="F33" s="12">
+      <c r="F33" s="11">
         <v>60.1</v>
       </c>
-      <c r="G33" s="12">
+      <c r="G33" s="11">
         <v>70.599999999999994</v>
       </c>
-      <c r="H33" s="12">
+      <c r="H33" s="11">
         <v>52.2</v>
       </c>
-      <c r="I33" s="12">
+      <c r="I33" s="11">
         <v>70.7</v>
       </c>
     </row>
-    <row r="34" spans="1:9">
-      <c r="A34" s="10">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A34" s="9">
         <v>43586</v>
       </c>
-      <c r="B34" s="10">
+      <c r="B34" s="9">
         <v>43620</v>
       </c>
-      <c r="D34" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E34" s="12">
+      <c r="D34" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E34" s="11">
         <v>56.7</v>
       </c>
-      <c r="F34" s="12">
+      <c r="F34" s="11">
         <v>58.6</v>
       </c>
-      <c r="G34" s="12">
+      <c r="G34" s="11">
         <v>70.59</v>
       </c>
-      <c r="H34" s="12">
+      <c r="H34" s="11">
         <v>48.6</v>
       </c>
-      <c r="I34" s="12">
+      <c r="I34" s="11">
         <v>72.55</v>
       </c>
     </row>
-    <row r="35" spans="1:9">
-      <c r="A35" s="10">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35" s="9">
         <v>43617</v>
       </c>
-      <c r="B35" s="10">
+      <c r="B35" s="9">
         <v>43648</v>
       </c>
-      <c r="D35" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E35" s="12">
+      <c r="D35" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E35" s="11">
         <v>56</v>
       </c>
-      <c r="F35" s="12">
+      <c r="F35" s="11">
         <v>58.4</v>
       </c>
-      <c r="G35" s="12">
+      <c r="G35" s="11">
         <v>65.099999999999994</v>
       </c>
-      <c r="H35" s="12">
+      <c r="H35" s="11">
         <v>51</v>
       </c>
-      <c r="I35" s="12">
+      <c r="I35" s="11">
         <v>71.2</v>
       </c>
     </row>
-    <row r="36" spans="1:9">
-      <c r="A36" s="10">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A36" s="9">
         <v>43647</v>
       </c>
-      <c r="B36" s="10">
+      <c r="B36" s="9">
         <v>43683</v>
       </c>
-      <c r="D36" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E36" s="12">
+      <c r="D36" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E36" s="11">
         <v>57.2</v>
       </c>
-      <c r="F36" s="12">
+      <c r="F36" s="11">
         <v>59.7</v>
       </c>
-      <c r="G36" s="12">
+      <c r="G36" s="11">
         <v>66.2</v>
       </c>
-      <c r="H36" s="12">
+      <c r="H36" s="11">
         <v>49.2</v>
       </c>
-      <c r="I36" s="12">
+      <c r="I36" s="11">
         <v>71.2</v>
       </c>
     </row>
-    <row r="37" spans="1:9">
-      <c r="A37" s="10">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37" s="9">
         <v>43678</v>
       </c>
-      <c r="B37" s="10">
+      <c r="B37" s="9">
         <v>43711</v>
       </c>
-      <c r="D37" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E37" s="12">
+      <c r="D37" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E37" s="11">
         <v>56.6</v>
       </c>
-      <c r="F37" s="12">
+      <c r="F37" s="11">
         <v>62.7</v>
       </c>
-      <c r="G37" s="12">
+      <c r="G37" s="11">
         <v>69.8</v>
       </c>
-      <c r="H37" s="12">
+      <c r="H37" s="11">
         <v>48.9</v>
       </c>
-      <c r="I37" s="12">
+      <c r="I37" s="11">
         <v>70.3</v>
       </c>
     </row>
-    <row r="38" spans="1:9">
-      <c r="A38" s="10">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A38" s="9">
         <v>43709</v>
       </c>
-      <c r="B38" s="10">
+      <c r="B38" s="9">
         <v>43739</v>
       </c>
-      <c r="D38" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E38" s="12">
+      <c r="D38" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E38" s="11">
         <v>56.6</v>
       </c>
-      <c r="F38" s="12">
+      <c r="F38" s="11">
         <v>63.7</v>
       </c>
-      <c r="G38" s="12">
+      <c r="G38" s="11">
         <v>69.599999999999994</v>
       </c>
-      <c r="H38" s="12">
+      <c r="H38" s="11">
         <v>50.6</v>
       </c>
-      <c r="I38" s="12">
+      <c r="I38" s="11">
         <v>67.5</v>
       </c>
     </row>
-    <row r="39" spans="1:9">
-      <c r="A39" s="10">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A39" s="9">
         <v>43739</v>
       </c>
-      <c r="B39" s="10">
+      <c r="B39" s="9">
         <v>43774</v>
       </c>
-      <c r="D39" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E39" s="12">
+      <c r="D39" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E39" s="11">
         <v>54.4</v>
       </c>
-      <c r="F39" s="12">
+      <c r="F39" s="11">
         <v>59.5</v>
       </c>
-      <c r="G39" s="12">
+      <c r="G39" s="11">
         <v>65.599999999999994</v>
       </c>
-      <c r="H39" s="12">
+      <c r="H39" s="11">
         <v>43.5</v>
       </c>
-      <c r="I39" s="12">
+      <c r="I39" s="11">
         <v>66.7</v>
       </c>
     </row>
-    <row r="40" spans="1:9">
-      <c r="A40" s="10">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A40" s="9">
         <v>43770</v>
       </c>
-      <c r="B40" s="10">
+      <c r="B40" s="9">
         <v>43802</v>
       </c>
-      <c r="D40" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E40" s="12">
+      <c r="D40" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E40" s="11">
         <v>54.5</v>
       </c>
-      <c r="F40" s="12">
+      <c r="F40" s="11">
         <v>62.1</v>
       </c>
-      <c r="G40" s="12">
+      <c r="G40" s="11">
         <v>68.3</v>
       </c>
-      <c r="H40" s="12">
+      <c r="H40" s="11">
         <v>41</v>
       </c>
-      <c r="I40" s="12">
+      <c r="I40" s="11">
         <v>65.400000000000006</v>
       </c>
     </row>
-    <row r="41" spans="1:9">
-      <c r="A41" s="10">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A41" s="9">
         <v>43800</v>
       </c>
-      <c r="B41" s="10">
+      <c r="B41" s="9">
         <v>43837</v>
       </c>
-      <c r="D41" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E41" s="12">
+      <c r="D41" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E41" s="11">
         <v>53.96</v>
       </c>
-      <c r="F41" s="12">
+      <c r="F41" s="11">
         <v>63.3</v>
       </c>
-      <c r="G41" s="12">
+      <c r="G41" s="11">
         <v>73.19</v>
       </c>
-      <c r="H41" s="12">
+      <c r="H41" s="11">
         <v>52.74</v>
       </c>
-      <c r="I41" s="12">
+      <c r="I41" s="11">
         <v>63.43</v>
       </c>
     </row>
-    <row r="42" spans="1:9">
-      <c r="A42" s="10">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" s="9">
         <v>43831</v>
       </c>
-      <c r="B42" s="10">
+      <c r="B42" s="9">
         <v>43865</v>
       </c>
-      <c r="D42" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E42" s="12">
+      <c r="D42" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E42" s="11">
         <v>54.12</v>
       </c>
-      <c r="F42" s="12">
+      <c r="F42" s="11">
         <v>62.8</v>
       </c>
-      <c r="G42" s="12">
+      <c r="G42" s="11">
         <v>69.89</v>
       </c>
-      <c r="H42" s="12">
+      <c r="H42" s="11">
         <v>50</v>
       </c>
-      <c r="I42" s="12">
+      <c r="I42" s="11">
         <v>66.13</v>
       </c>
     </row>
-    <row r="43" spans="1:9">
-      <c r="A43" s="10">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A43" s="9">
         <v>43862</v>
       </c>
-      <c r="B43" s="10">
+      <c r="B43" s="9">
         <v>43893</v>
       </c>
-      <c r="D43" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E43" s="12">
+      <c r="D43" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E43" s="11">
         <v>52.62</v>
       </c>
-      <c r="F43" s="12">
+      <c r="F43" s="11">
         <v>63.1</v>
       </c>
-      <c r="G43" s="12">
+      <c r="G43" s="11">
         <v>65.91</v>
       </c>
-      <c r="H43" s="12">
+      <c r="H43" s="11">
         <v>48.98</v>
       </c>
-      <c r="I43" s="12">
+      <c r="I43" s="11">
         <v>61.8</v>
       </c>
     </row>
-    <row r="44" spans="1:9">
-      <c r="A44" s="10">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A44" s="9">
         <v>43891</v>
       </c>
-      <c r="B44" s="10">
+      <c r="B44" s="9">
         <v>43928</v>
       </c>
-      <c r="D44" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E44" s="12">
+      <c r="D44" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E44" s="11">
         <v>58.87</v>
       </c>
-      <c r="F44" s="12">
+      <c r="F44" s="11">
         <v>62.3</v>
       </c>
-      <c r="G44" s="12">
+      <c r="G44" s="11">
         <v>64.5</v>
       </c>
-      <c r="H44" s="12">
+      <c r="H44" s="11">
         <v>65.52</v>
       </c>
-      <c r="I44" s="12">
+      <c r="I44" s="11">
         <v>66.489999999999995</v>
       </c>
     </row>
-    <row r="45" spans="1:9">
-      <c r="A45" s="10">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A45" s="9">
         <v>43922</v>
       </c>
-      <c r="B45" s="10">
+      <c r="B45" s="9">
         <v>43956</v>
       </c>
-      <c r="D45" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E45" s="12">
+      <c r="D45" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E45" s="11">
         <v>51.31</v>
       </c>
-      <c r="F45" s="12">
+      <c r="F45" s="11">
         <v>62.4</v>
       </c>
-      <c r="G45" s="12">
+      <c r="G45" s="11">
         <v>56.97</v>
       </c>
-      <c r="H45" s="12">
+      <c r="H45" s="11">
         <v>37.659999999999997</v>
       </c>
-      <c r="I45" s="12">
+      <c r="I45" s="11">
         <v>63.1</v>
       </c>
     </row>
-    <row r="46" spans="1:9">
-      <c r="A46" s="10">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A46" s="9">
         <v>43952</v>
       </c>
-      <c r="B46" s="10">
+      <c r="B46" s="9">
         <v>43984</v>
       </c>
-      <c r="D46" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E46" s="12">
+      <c r="D46" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E46" s="11">
         <v>54.46</v>
       </c>
-      <c r="F46" s="12">
+      <c r="F46" s="11">
         <v>57.5</v>
       </c>
-      <c r="G46" s="12">
+      <c r="G46" s="11">
         <v>60.1</v>
       </c>
-      <c r="H46" s="12">
+      <c r="H46" s="11">
         <v>49.07</v>
       </c>
-      <c r="I46" s="12">
+      <c r="I46" s="11">
         <v>66.02</v>
       </c>
     </row>
-    <row r="47" spans="1:9">
-      <c r="A47" s="10">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A47" s="9">
         <v>43983</v>
       </c>
-      <c r="B47" s="10">
+      <c r="B47" s="9">
         <v>44019</v>
       </c>
-      <c r="D47" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E47" s="12">
+      <c r="D47" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E47" s="11">
         <v>61.71</v>
       </c>
-      <c r="F47" s="12">
+      <c r="F47" s="11">
         <v>64.599999999999994</v>
       </c>
-      <c r="G47" s="12">
+      <c r="G47" s="11">
         <v>60.55</v>
       </c>
-      <c r="H47" s="12">
+      <c r="H47" s="11">
         <v>64.47</v>
       </c>
-      <c r="I47" s="12">
+      <c r="I47" s="11">
         <v>63.46</v>
       </c>
     </row>
-    <row r="48" spans="1:9">
-      <c r="A48" s="10">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A48" s="9">
         <v>44013</v>
       </c>
-      <c r="B48" s="10">
+      <c r="B48" s="9">
         <v>44047</v>
       </c>
-      <c r="D48" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E48" s="12">
+      <c r="D48" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E48" s="11">
         <v>63.03</v>
       </c>
-      <c r="F48" s="12">
+      <c r="F48" s="11">
         <v>69.099999999999994</v>
       </c>
-      <c r="G48" s="12">
+      <c r="G48" s="11">
         <v>67.48</v>
       </c>
-      <c r="H48" s="12">
+      <c r="H48" s="11">
         <v>72.64</v>
       </c>
-      <c r="I48" s="12">
+      <c r="I48" s="11">
         <v>69.12</v>
       </c>
     </row>
-    <row r="49" spans="1:9">
-      <c r="A49" s="10">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A49" s="9">
         <v>44044</v>
       </c>
-      <c r="B49" s="10">
+      <c r="B49" s="9">
         <v>44075</v>
       </c>
-      <c r="D49" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E49" s="12">
+      <c r="D49" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E49" s="11">
         <v>66</v>
       </c>
-      <c r="F49" s="12">
+      <c r="F49" s="11">
         <v>66</v>
       </c>
-      <c r="G49" s="12">
+      <c r="G49" s="11">
         <v>68.62</v>
       </c>
-      <c r="H49" s="12">
+      <c r="H49" s="11">
         <v>83.8</v>
       </c>
-      <c r="I49" s="12">
+      <c r="I49" s="11">
         <v>64.739999999999995</v>
       </c>
     </row>
-    <row r="50" spans="1:9">
-      <c r="A50" s="10">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A50" s="9">
         <v>44075</v>
       </c>
-      <c r="B50" s="10">
+      <c r="B50" s="9">
         <v>44110</v>
       </c>
-      <c r="D50" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E50" s="12">
+      <c r="D50" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E50" s="11">
         <v>70.47</v>
       </c>
-      <c r="F50" s="12">
+      <c r="F50" s="11">
         <v>71.5</v>
       </c>
-      <c r="G50" s="12">
+      <c r="G50" s="11">
         <v>70.5</v>
       </c>
-      <c r="H50" s="12">
+      <c r="H50" s="11">
         <v>87.85</v>
       </c>
-      <c r="I50" s="12">
+      <c r="I50" s="11">
         <v>65.84</v>
       </c>
     </row>
-    <row r="51" spans="1:9">
-      <c r="A51" s="10">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A51" s="9">
         <v>44105</v>
       </c>
-      <c r="B51" s="10">
+      <c r="B51" s="9">
         <v>44138</v>
       </c>
-      <c r="D51" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E51" s="12">
+      <c r="D51" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E51" s="11">
         <v>71.599999999999994</v>
       </c>
-      <c r="F51" s="12">
+      <c r="F51" s="11">
         <v>69.900000000000006</v>
       </c>
-      <c r="G51" s="12">
+      <c r="G51" s="11">
         <v>78.7</v>
       </c>
-      <c r="H51" s="12">
+      <c r="H51" s="11">
         <v>85.5</v>
       </c>
-      <c r="I51" s="12">
+      <c r="I51" s="11">
         <v>73.599999999999994</v>
       </c>
     </row>
-    <row r="52" spans="1:9">
-      <c r="A52" s="10">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A52" s="9">
         <v>44136</v>
       </c>
-      <c r="B52" s="10">
+      <c r="B52" s="9">
         <v>44166</v>
       </c>
-      <c r="D52" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E52" s="12">
+      <c r="D52" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E52" s="11">
         <v>70.8</v>
       </c>
-      <c r="F52" s="12">
+      <c r="F52" s="11">
         <v>69.8</v>
       </c>
-      <c r="G52" s="12">
+      <c r="G52" s="11">
         <v>78.400000000000006</v>
       </c>
-      <c r="H52" s="12">
+      <c r="H52" s="11">
         <v>85.8</v>
       </c>
-      <c r="I52" s="12">
+      <c r="I52" s="11">
         <v>73.099999999999994</v>
       </c>
     </row>
-    <row r="53" spans="1:9">
-      <c r="A53" s="10">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A53" s="9">
         <v>44166</v>
       </c>
-      <c r="B53" s="10">
+      <c r="B53" s="9">
         <v>44201</v>
       </c>
-      <c r="D53" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E53" s="12">
+      <c r="D53" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E53" s="11">
         <v>66.7</v>
       </c>
-      <c r="F53" s="12">
+      <c r="F53" s="11">
         <v>66.5</v>
       </c>
-      <c r="G53" s="12">
+      <c r="G53" s="11">
         <v>76.900000000000006</v>
       </c>
-      <c r="H53" s="12">
+      <c r="H53" s="11">
         <v>85.1</v>
       </c>
-      <c r="I53" s="12">
+      <c r="I53" s="11">
         <v>71.8</v>
       </c>
     </row>
-    <row r="54" spans="1:9">
-      <c r="A54" s="10">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A54" s="9">
         <v>44197</v>
       </c>
-      <c r="B54" s="10">
+      <c r="B54" s="9">
         <v>44229</v>
       </c>
-      <c r="D54" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E54" s="12">
+      <c r="D54" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E54" s="11">
         <v>67.2</v>
       </c>
-      <c r="F54" s="12">
+      <c r="F54" s="11">
         <v>68.400000000000006</v>
       </c>
-      <c r="G54" s="12">
+      <c r="G54" s="11">
         <v>77.8</v>
       </c>
-      <c r="H54" s="12">
+      <c r="H54" s="11">
         <v>81</v>
       </c>
-      <c r="I54" s="12">
+      <c r="I54" s="11">
         <v>75</v>
       </c>
     </row>
-    <row r="55" spans="1:9">
-      <c r="A55" s="10">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A55" s="9">
         <v>44228</v>
       </c>
-      <c r="B55" s="10">
+      <c r="B55" s="9">
         <v>44257</v>
       </c>
-      <c r="D55" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E55" s="12">
+      <c r="D55" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E55" s="11">
         <v>71.400000000000006</v>
       </c>
-      <c r="F55" s="12">
+      <c r="F55" s="11">
         <v>71</v>
       </c>
-      <c r="G55" s="12">
+      <c r="G55" s="11">
         <v>79</v>
       </c>
-      <c r="H55" s="12">
+      <c r="H55" s="11">
         <v>88</v>
       </c>
-      <c r="I55" s="12">
+      <c r="I55" s="11">
         <v>76.8</v>
       </c>
     </row>
-    <row r="56" spans="1:9">
-      <c r="A56" s="10">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A56" s="9">
         <v>44256</v>
       </c>
-      <c r="B56" s="10">
+      <c r="B56" s="9">
         <v>44292</v>
       </c>
-      <c r="D56" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E56" s="12">
+      <c r="D56" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E56" s="11">
         <v>72.2</v>
       </c>
-      <c r="F56" s="12">
+      <c r="F56" s="11">
         <v>71.7</v>
       </c>
-      <c r="G56" s="12">
+      <c r="G56" s="11">
         <v>81.5</v>
       </c>
-      <c r="H56" s="12">
+      <c r="H56" s="11">
         <v>90.6</v>
       </c>
-      <c r="I56" s="12">
+      <c r="I56" s="11">
         <v>80</v>
       </c>
     </row>
-    <row r="57" spans="1:9">
-      <c r="A57" s="10">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A57" s="9">
         <v>44287</v>
       </c>
-      <c r="B57" s="10">
+      <c r="B57" s="9">
         <v>44320</v>
       </c>
-      <c r="D57" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E57" s="12">
+      <c r="D57" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E57" s="11">
         <v>74.5</v>
       </c>
-      <c r="F57" s="12">
+      <c r="F57" s="11">
         <v>72.7</v>
       </c>
-      <c r="G57" s="12">
+      <c r="G57" s="11">
         <v>83.5</v>
       </c>
-      <c r="H57" s="12">
+      <c r="H57" s="11">
         <v>92.6</v>
       </c>
-      <c r="I57" s="12">
+      <c r="I57" s="11">
         <v>84.6</v>
       </c>
     </row>
-    <row r="58" spans="1:9">
-      <c r="A58" s="10">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A58" s="9">
         <v>44317</v>
       </c>
-      <c r="B58" s="10">
+      <c r="B58" s="9">
         <v>44348</v>
       </c>
-      <c r="D58" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E58" s="12">
+      <c r="D58" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E58" s="11">
         <v>71.3</v>
       </c>
-      <c r="F58" s="12">
+      <c r="F58" s="11">
         <v>73</v>
       </c>
-      <c r="G58" s="12">
+      <c r="G58" s="11">
         <v>83.1</v>
       </c>
-      <c r="H58" s="12">
+      <c r="H58" s="11">
         <v>91.2</v>
       </c>
-      <c r="I58" s="12">
+      <c r="I58" s="11">
         <v>83.8</v>
       </c>
     </row>
-    <row r="59" spans="1:9">
-      <c r="A59" s="10">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A59" s="9">
         <v>44348</v>
       </c>
-      <c r="B59" s="10">
+      <c r="B59" s="9">
         <v>44383</v>
       </c>
-      <c r="D59" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E59" s="12">
+      <c r="D59" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E59" s="11">
         <v>75</v>
       </c>
-      <c r="F59" s="12">
+      <c r="F59" s="11">
         <v>69.7</v>
       </c>
-      <c r="G59" s="12">
+      <c r="G59" s="11">
         <v>85.4</v>
       </c>
-      <c r="H59" s="12">
+      <c r="H59" s="11">
         <v>87.3</v>
       </c>
-      <c r="I59" s="12">
+      <c r="I59" s="11">
         <v>89.4</v>
       </c>
     </row>
-    <row r="60" spans="1:9">
-      <c r="A60" s="10">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A60" s="9">
         <v>44378</v>
       </c>
-      <c r="B60" s="10">
+      <c r="B60" s="9">
         <v>44411</v>
       </c>
-      <c r="D60" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E60" s="12">
+      <c r="D60" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E60" s="11">
         <v>74.5</v>
       </c>
-      <c r="F60" s="12">
+      <c r="F60" s="11">
         <v>71.7</v>
       </c>
-      <c r="G60" s="12">
+      <c r="G60" s="11">
         <v>88</v>
       </c>
-      <c r="H60" s="12">
+      <c r="H60" s="11">
         <v>91</v>
       </c>
-      <c r="I60" s="12">
+      <c r="I60" s="11">
         <v>88.8</v>
       </c>
     </row>
-    <row r="61" spans="1:9">
-      <c r="A61" s="10">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A61" s="9">
         <v>44409</v>
       </c>
-      <c r="B61" s="10">
+      <c r="B61" s="9">
         <v>44446</v>
       </c>
-      <c r="D61" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E61" s="12">
+      <c r="D61" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E61" s="11">
         <v>73.8</v>
       </c>
-      <c r="F61" s="12">
+      <c r="F61" s="11">
         <v>73.599999999999994</v>
       </c>
-      <c r="G61" s="12">
+      <c r="G61" s="11">
         <v>88</v>
       </c>
-      <c r="H61" s="12">
+      <c r="H61" s="11">
         <v>93.7</v>
       </c>
-      <c r="I61" s="12">
+      <c r="I61" s="11">
         <v>85.9</v>
       </c>
     </row>
-    <row r="62" spans="1:9">
-      <c r="A62" s="10">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A62" s="9">
         <v>44440</v>
       </c>
-      <c r="B62" s="10">
+      <c r="B62" s="9">
         <v>44474</v>
       </c>
-      <c r="D62" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E62" s="12">
+      <c r="D62" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E62" s="11">
         <v>72.2</v>
       </c>
-      <c r="F62" s="12">
+      <c r="F62" s="11">
         <v>72.599999999999994</v>
       </c>
-      <c r="G62" s="12">
+      <c r="G62" s="11">
         <v>89.3</v>
       </c>
-      <c r="H62" s="12">
+      <c r="H62" s="11">
         <v>92.4</v>
       </c>
-      <c r="I62" s="12">
+      <c r="I62" s="11">
         <v>86.6</v>
       </c>
     </row>
-    <row r="63" spans="1:9">
-      <c r="A63" s="10">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A63" s="9">
         <v>44470</v>
       </c>
-      <c r="B63" s="10">
+      <c r="B63" s="9">
         <v>44502</v>
       </c>
-      <c r="D63" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E63" s="12">
+      <c r="D63" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E63" s="11">
         <v>72.599999999999994</v>
       </c>
-      <c r="F63" s="12">
+      <c r="F63" s="11">
         <v>70.599999999999994</v>
       </c>
-      <c r="G63" s="12">
+      <c r="G63" s="11">
         <v>85.8</v>
       </c>
-      <c r="H63" s="12">
+      <c r="H63" s="11">
         <v>90.7</v>
       </c>
-      <c r="I63" s="12">
+      <c r="I63" s="11">
         <v>85.9</v>
       </c>
     </row>
-    <row r="64" spans="1:9">
-      <c r="A64" s="10">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A64" s="9">
         <v>44501</v>
       </c>
-      <c r="B64" s="10">
+      <c r="B64" s="9">
         <v>44537</v>
       </c>
-      <c r="D64" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E64" s="12">
+      <c r="D64" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E64" s="11">
         <v>73.400000000000006</v>
       </c>
-      <c r="F64" s="12">
+      <c r="F64" s="11">
         <v>71.2</v>
       </c>
-      <c r="G64" s="12">
+      <c r="G64" s="11">
         <v>90.3</v>
       </c>
-      <c r="H64" s="12">
+      <c r="H64" s="11">
         <v>93.2</v>
       </c>
-      <c r="I64" s="12">
+      <c r="I64" s="11">
         <v>87.6</v>
       </c>
     </row>
-    <row r="65" spans="1:9">
-      <c r="A65" s="10">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A65" s="9">
         <v>44531</v>
       </c>
-      <c r="B65" s="10">
+      <c r="B65" s="9">
         <v>44565</v>
       </c>
-      <c r="D65" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E65" s="12">
+      <c r="D65" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E65" s="11">
         <v>70.099999999999994</v>
       </c>
-      <c r="F65" s="12">
+      <c r="F65" s="11">
         <v>72.900000000000006</v>
       </c>
-      <c r="G65" s="12">
+      <c r="G65" s="11">
         <v>82.1</v>
       </c>
-      <c r="H65" s="12">
+      <c r="H65" s="11">
         <v>87.6</v>
       </c>
-      <c r="I65" s="12">
+      <c r="I65" s="11">
         <v>84</v>
       </c>
     </row>
-    <row r="66" spans="1:9">
-      <c r="A66" s="10">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A66" s="9">
         <v>44562</v>
       </c>
-      <c r="B66" s="10">
+      <c r="B66" s="9">
         <v>44593</v>
       </c>
-      <c r="D66" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E66" s="12">
+      <c r="D66" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E66" s="11">
         <v>71.900000000000006</v>
       </c>
-      <c r="F66" s="12">
+      <c r="F66" s="11">
         <v>70.7</v>
       </c>
-      <c r="G66" s="12">
+      <c r="G66" s="11">
         <v>85.9</v>
       </c>
-      <c r="H66" s="12">
+      <c r="H66" s="11">
         <v>88.7</v>
       </c>
-      <c r="I66" s="12">
+      <c r="I66" s="11">
         <v>87.9</v>
       </c>
     </row>
-    <row r="67" spans="1:9">
-      <c r="A67" s="10">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A67" s="9">
         <v>44593</v>
       </c>
-      <c r="B67" s="10">
+      <c r="B67" s="9">
         <v>44621</v>
       </c>
-      <c r="D67" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E67" s="12">
+      <c r="D67" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E67" s="11">
         <v>75.2</v>
       </c>
-      <c r="F67" s="12">
+      <c r="F67" s="11">
         <v>69.900000000000006</v>
       </c>
-      <c r="G67" s="12">
+      <c r="G67" s="11">
         <v>86.4</v>
       </c>
-      <c r="H67" s="12">
+      <c r="H67" s="11">
         <v>89</v>
       </c>
-      <c r="I67" s="12">
+      <c r="I67" s="11">
         <v>90.3</v>
       </c>
     </row>
-    <row r="68" spans="1:9">
-      <c r="A68" s="10">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A68" s="9">
         <v>44621</v>
       </c>
-      <c r="B68" s="10">
+      <c r="B68" s="9">
         <v>44656</v>
       </c>
-      <c r="D68" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E68" s="12">
+      <c r="D68" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E68" s="11">
         <v>76.2</v>
       </c>
-      <c r="F68" s="12">
+      <c r="F68" s="11">
         <v>70.2</v>
       </c>
-      <c r="G68" s="12">
+      <c r="G68" s="11">
         <v>90.5</v>
       </c>
-      <c r="H68" s="12">
+      <c r="H68" s="11">
         <v>89.7</v>
       </c>
-      <c r="I68" s="12">
+      <c r="I68" s="11">
         <v>91</v>
       </c>
     </row>
-    <row r="69" spans="1:9">
-      <c r="A69" s="10">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A69" s="9">
         <v>44652</v>
       </c>
-      <c r="B69" s="10">
+      <c r="B69" s="9">
         <v>44684</v>
       </c>
-      <c r="D69" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E69" s="12">
+      <c r="D69" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E69" s="11">
         <v>69.7</v>
       </c>
-      <c r="F69" s="12">
+      <c r="F69" s="11">
         <v>67.8</v>
       </c>
-      <c r="G69" s="12">
+      <c r="G69" s="11">
         <v>85.8</v>
       </c>
-      <c r="H69" s="12">
+      <c r="H69" s="11">
         <v>73.900000000000006</v>
       </c>
-      <c r="I69" s="12">
+      <c r="I69" s="11">
         <v>87.7</v>
       </c>
     </row>
-    <row r="70" spans="1:9">
-      <c r="A70" s="10">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A70" s="9">
         <v>44682</v>
       </c>
-      <c r="B70" s="10">
+      <c r="B70" s="9">
         <v>44719</v>
       </c>
-      <c r="D70" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E70" s="12">
+      <c r="D70" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E70" s="11">
         <v>67.099999999999994</v>
       </c>
-      <c r="F70" s="12">
+      <c r="F70" s="11">
         <v>66</v>
       </c>
-      <c r="G70" s="12">
+      <c r="G70" s="11">
         <v>87.5</v>
       </c>
-      <c r="H70" s="12">
+      <c r="H70" s="11">
         <v>65.3</v>
       </c>
-      <c r="I70" s="12">
+      <c r="I70" s="11">
         <v>88.1</v>
       </c>
     </row>
-    <row r="71" spans="1:9">
-      <c r="A71" s="10">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A71" s="9">
         <v>44713</v>
       </c>
-      <c r="B71" s="10">
+      <c r="B71" s="9">
         <v>44747</v>
       </c>
-      <c r="D71" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E71" s="12">
+      <c r="D71" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E71" s="11">
         <v>65</v>
       </c>
-      <c r="F71" s="12">
+      <c r="F71" s="11">
         <v>60.4</v>
       </c>
-      <c r="G71" s="12">
+      <c r="G71" s="11">
         <v>78.400000000000006</v>
       </c>
-      <c r="H71" s="12">
+      <c r="H71" s="11">
         <v>61.3</v>
       </c>
-      <c r="I71" s="12">
+      <c r="I71" s="11">
         <v>83.8</v>
       </c>
     </row>
-    <row r="72" spans="1:9">
-      <c r="A72" s="10">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A72" s="9">
         <v>44743</v>
       </c>
-      <c r="B72" s="10">
+      <c r="B72" s="9">
         <v>44775</v>
       </c>
-      <c r="D72" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E72" s="12">
+      <c r="D72" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E72" s="11">
         <v>60.7</v>
       </c>
-      <c r="F72" s="12">
+      <c r="F72" s="11">
         <v>62.1</v>
       </c>
-      <c r="G72" s="12">
+      <c r="G72" s="11">
         <v>76.2</v>
       </c>
-      <c r="H72" s="12">
+      <c r="H72" s="11">
         <v>49.5</v>
       </c>
-      <c r="I72" s="12">
+      <c r="I72" s="11">
         <v>79</v>
       </c>
     </row>
-    <row r="73" spans="1:9">
-      <c r="A73" s="10">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A73" s="9">
         <v>44774</v>
       </c>
-      <c r="B73" s="10">
+      <c r="B73" s="9">
         <v>44810</v>
       </c>
-      <c r="D73" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E73" s="12">
+      <c r="D73" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E73" s="11">
         <v>59.7</v>
       </c>
-      <c r="F73" s="12">
+      <c r="F73" s="11">
         <v>57.6</v>
       </c>
-      <c r="G73" s="12">
+      <c r="G73" s="11">
         <v>75</v>
       </c>
-      <c r="H73" s="12">
+      <c r="H73" s="11">
         <v>48</v>
       </c>
-      <c r="I73" s="12">
+      <c r="I73" s="11">
         <v>76.8</v>
       </c>
     </row>
-    <row r="74" spans="1:9">
-      <c r="A74" s="10">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A74" s="9">
         <v>44805</v>
       </c>
-      <c r="B74" s="10">
+      <c r="B74" s="9">
         <v>44838</v>
       </c>
-      <c r="D74" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E74" s="12">
+      <c r="D74" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E74" s="11">
         <v>61.4</v>
       </c>
-      <c r="F74" s="12">
+      <c r="F74" s="11">
         <v>56.2</v>
       </c>
-      <c r="G74" s="12">
+      <c r="G74" s="11">
         <v>75.400000000000006</v>
       </c>
-      <c r="H74" s="12">
+      <c r="H74" s="11">
         <v>44.5</v>
       </c>
-      <c r="I74" s="12">
+      <c r="I74" s="11">
         <v>77.2</v>
       </c>
     </row>
-    <row r="75" spans="1:9">
-      <c r="A75" s="10">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A75" s="9">
         <v>44835</v>
       </c>
-      <c r="B75" s="10">
+      <c r="B75" s="9">
         <v>44866</v>
       </c>
-      <c r="D75" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E75" s="12">
+      <c r="D75" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E75" s="11">
         <v>57.5</v>
       </c>
-      <c r="F75" s="12">
+      <c r="F75" s="11">
         <v>55.2</v>
       </c>
-      <c r="G75" s="12">
+      <c r="G75" s="11">
         <v>75.5</v>
       </c>
-      <c r="H75" s="12">
+      <c r="H75" s="11">
         <v>42.2</v>
       </c>
-      <c r="I75" s="12">
+      <c r="I75" s="11">
         <v>80.900000000000006</v>
       </c>
     </row>
-    <row r="76" spans="1:9">
-      <c r="A76" s="10">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A76" s="9">
         <v>44866</v>
       </c>
-      <c r="B76" s="10">
+      <c r="B76" s="9">
         <v>44901</v>
       </c>
-      <c r="D76" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E76" s="12">
+      <c r="D76" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E76" s="11">
         <v>53.6</v>
       </c>
-      <c r="F76" s="12">
+      <c r="F76" s="11">
         <v>51.5</v>
       </c>
-      <c r="G76" s="12">
+      <c r="G76" s="11">
         <v>74.400000000000006</v>
       </c>
-      <c r="H76" s="12">
+      <c r="H76" s="11">
         <v>37.4</v>
       </c>
-      <c r="I76" s="12">
+      <c r="I76" s="11">
         <v>73.400000000000006</v>
       </c>
     </row>
-    <row r="77" spans="1:9">
-      <c r="A77" s="10">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A77" s="9">
         <v>44896</v>
       </c>
-      <c r="B77" s="10">
+      <c r="B77" s="9">
         <v>44929</v>
       </c>
-      <c r="D77" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E77" s="12">
+      <c r="D77" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E77" s="11">
         <v>54.6</v>
       </c>
-      <c r="F77" s="12">
+      <c r="F77" s="11">
         <v>53.2</v>
       </c>
-      <c r="G77" s="12">
+      <c r="G77" s="11">
         <v>72.099999999999994</v>
       </c>
-      <c r="H77" s="12">
+      <c r="H77" s="11">
         <v>36.9</v>
       </c>
-      <c r="I77" s="12">
+      <c r="I77" s="11">
         <v>72.8</v>
       </c>
     </row>
-    <row r="78" spans="1:9">
-      <c r="A78" s="10">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A78" s="9">
         <v>44927</v>
       </c>
-      <c r="B78" s="10">
+      <c r="B78" s="9">
         <v>44964</v>
       </c>
-      <c r="D78" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E78" s="12">
+      <c r="D78" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E78" s="11">
         <v>57.6</v>
       </c>
-      <c r="F78" s="12">
+      <c r="F78" s="11">
         <v>56.1</v>
       </c>
-      <c r="G78" s="12">
+      <c r="G78" s="11">
         <v>75</v>
       </c>
-      <c r="H78" s="12">
+      <c r="H78" s="11">
         <v>42</v>
       </c>
-      <c r="I78" s="12">
+      <c r="I78" s="11">
         <v>74.2</v>
       </c>
     </row>
-    <row r="79" spans="1:9">
-      <c r="A79" s="10">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A79" s="9">
         <v>44958</v>
       </c>
-      <c r="B79" s="10">
+      <c r="B79" s="9">
         <v>44992</v>
       </c>
-      <c r="D79" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E79" s="12">
+      <c r="D79" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E79" s="11">
         <v>54.7</v>
       </c>
-      <c r="F79" s="12">
+      <c r="F79" s="11">
         <v>56.7</v>
       </c>
-      <c r="G79" s="12">
+      <c r="G79" s="11">
         <v>73.3</v>
       </c>
-      <c r="H79" s="12">
+      <c r="H79" s="11">
         <v>36.1</v>
       </c>
-      <c r="I79" s="12">
+      <c r="I79" s="11">
         <v>70.900000000000006</v>
       </c>
     </row>
-    <row r="80" spans="1:9">
-      <c r="A80" s="10">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A80" s="9">
         <v>44986</v>
       </c>
-      <c r="B80" s="10">
+      <c r="B80" s="9">
         <v>45020</v>
       </c>
-      <c r="D80" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E80" s="12">
+      <c r="D80" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E80" s="11">
         <v>51.1</v>
       </c>
-      <c r="F80" s="12">
+      <c r="F80" s="11">
         <v>52.7</v>
       </c>
-      <c r="G80" s="12">
+      <c r="G80" s="11">
         <v>70.900000000000006</v>
       </c>
-      <c r="H80" s="12">
+      <c r="H80" s="11">
         <v>31.1</v>
       </c>
-      <c r="I80" s="12">
+      <c r="I80" s="11">
         <v>66</v>
       </c>
     </row>
-    <row r="81" spans="1:9">
-      <c r="A81" s="10">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A81" s="9">
         <v>45017</v>
       </c>
-      <c r="B81" s="10">
+      <c r="B81" s="9">
         <v>45048</v>
       </c>
-      <c r="D81" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E81" s="12">
+      <c r="D81" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E81" s="11">
         <v>50.9</v>
       </c>
-      <c r="F81" s="12">
+      <c r="F81" s="11">
         <v>51.1</v>
       </c>
-      <c r="G81" s="12">
+      <c r="G81" s="11">
         <v>69.8</v>
       </c>
-      <c r="H81" s="12">
+      <c r="H81" s="11">
         <v>36.799999999999997</v>
       </c>
-      <c r="I81" s="12">
+      <c r="I81" s="11">
         <v>65.099999999999994</v>
       </c>
     </row>
-    <row r="82" spans="1:9">
-      <c r="A82" s="10">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A82" s="9">
         <v>45047</v>
       </c>
-      <c r="B82" s="10">
+      <c r="B82" s="9">
         <v>45083</v>
       </c>
-      <c r="D82" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E82" s="12">
+      <c r="D82" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E82" s="11">
         <v>47.3</v>
       </c>
-      <c r="F82" s="12">
+      <c r="F82" s="11">
         <v>49.6</v>
       </c>
-      <c r="G82" s="12">
+      <c r="G82" s="11">
         <v>62.8</v>
       </c>
-      <c r="H82" s="12">
+      <c r="H82" s="11">
         <v>27.9</v>
       </c>
-      <c r="I82" s="12">
+      <c r="I82" s="11">
         <v>64.400000000000006</v>
       </c>
     </row>
-    <row r="83" spans="1:9">
-      <c r="A83" s="10">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A83" s="9">
         <v>45078</v>
       </c>
-      <c r="B83" s="10">
+      <c r="B83" s="9">
         <v>45111</v>
       </c>
-      <c r="D83" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E83" s="12">
+      <c r="D83" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E83" s="11">
         <v>45.6</v>
       </c>
-      <c r="F83" s="12">
+      <c r="F83" s="11">
         <v>55.4</v>
       </c>
-      <c r="G83" s="12">
+      <c r="G83" s="11">
         <v>63.3</v>
       </c>
-      <c r="H83" s="12">
+      <c r="H83" s="11">
         <v>32.799999999999997</v>
       </c>
-      <c r="I83" s="12">
+      <c r="I83" s="11">
         <v>57.1</v>
       </c>
     </row>
-    <row r="84" spans="1:9">
-      <c r="A84" s="10">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A84" s="9">
         <v>45108</v>
       </c>
-      <c r="B84" s="10">
+      <c r="B84" s="9">
         <v>45139</v>
       </c>
-      <c r="D84" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E84" s="12">
+      <c r="D84" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E84" s="11">
         <v>45.4</v>
       </c>
-      <c r="F84" s="12">
+      <c r="F84" s="11">
         <v>52.8</v>
       </c>
-      <c r="G84" s="12">
+      <c r="G84" s="11">
         <v>60.6</v>
       </c>
-      <c r="H84" s="12">
+      <c r="H84" s="11">
         <v>35.6</v>
       </c>
-      <c r="I84" s="12">
+      <c r="I84" s="11">
         <v>60.5</v>
       </c>
     </row>
-    <row r="85" spans="1:9">
-      <c r="A85" s="10">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A85" s="9">
         <v>45139</v>
       </c>
-      <c r="B85" s="10">
+      <c r="B85" s="9">
         <v>45174</v>
       </c>
-      <c r="D85" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E85" s="12">
+      <c r="D85" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E85" s="11">
         <v>51.2</v>
       </c>
-      <c r="F85" s="12">
+      <c r="F85" s="11">
         <v>58.6</v>
       </c>
-      <c r="G85" s="12">
+      <c r="G85" s="11">
         <v>63.4</v>
       </c>
-      <c r="H85" s="12">
+      <c r="H85" s="11">
         <v>42.9</v>
       </c>
-      <c r="I85" s="12">
+      <c r="I85" s="11">
         <v>69.099999999999994</v>
       </c>
     </row>
-    <row r="86" spans="1:9">
-      <c r="A86" s="10">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A86" s="9">
         <v>45170</v>
       </c>
-      <c r="B86" s="10">
+      <c r="B86" s="9">
         <v>45202</v>
       </c>
-      <c r="D86" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E86" s="12">
+      <c r="D86" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E86" s="11">
         <v>52.4</v>
       </c>
-      <c r="F86" s="12">
+      <c r="F86" s="11">
         <v>60.1</v>
       </c>
-      <c r="G86" s="12">
+      <c r="G86" s="11">
         <v>71.2</v>
       </c>
-      <c r="H86" s="12">
+      <c r="H86" s="11">
         <v>43.5</v>
       </c>
-      <c r="I86" s="12">
+      <c r="I86" s="11">
         <v>64.599999999999994</v>
       </c>
     </row>
-    <row r="87" spans="1:9">
-      <c r="A87" s="10">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A87" s="9">
         <v>45200</v>
       </c>
-      <c r="B87" s="10">
+      <c r="B87" s="9">
         <v>45237</v>
       </c>
-      <c r="D87" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E87" s="12">
+      <c r="D87" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E87" s="11">
         <v>56.5</v>
       </c>
-      <c r="F87" s="12">
+      <c r="F87" s="11">
         <v>60.8</v>
       </c>
-      <c r="G87" s="12">
+      <c r="G87" s="11">
         <v>70.7</v>
       </c>
-      <c r="H87" s="12">
+      <c r="H87" s="11">
         <v>44.4</v>
       </c>
-      <c r="I87" s="12">
+      <c r="I87" s="11">
         <v>69.8</v>
       </c>
     </row>
-    <row r="88" spans="1:9">
-      <c r="A88" s="10">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A88" s="9">
         <v>45231</v>
       </c>
-      <c r="B88" s="10">
+      <c r="B88" s="9">
         <v>45265</v>
       </c>
-      <c r="D88" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E88" s="12">
+      <c r="D88" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E88" s="11">
         <v>49.4</v>
       </c>
-      <c r="F88" s="12">
+      <c r="F88" s="11">
         <v>57.4</v>
       </c>
-      <c r="G88" s="12">
+      <c r="G88" s="11">
         <v>64.2</v>
       </c>
-      <c r="H88" s="12">
+      <c r="H88" s="11">
         <v>44.2</v>
       </c>
-      <c r="I88" s="12">
+      <c r="I88" s="11">
         <v>62.1</v>
       </c>
     </row>
-    <row r="89" spans="1:9">
-      <c r="A89" s="10">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A89" s="9">
         <v>45261</v>
       </c>
-      <c r="B89" s="10">
+      <c r="B89" s="9">
         <v>45293</v>
       </c>
-      <c r="D89" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E89" s="12">
+      <c r="D89" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E89" s="11">
         <v>50.6</v>
       </c>
-      <c r="F89" s="12">
+      <c r="F89" s="11">
         <v>59.9</v>
       </c>
-      <c r="G89" s="12">
+      <c r="G89" s="11">
         <v>65.5</v>
       </c>
-      <c r="H89" s="12">
+      <c r="H89" s="11">
         <v>43.1</v>
       </c>
-      <c r="I89" s="12">
+      <c r="I89" s="11">
         <v>55.8</v>
       </c>
     </row>
-    <row r="90" spans="1:9">
-      <c r="A90" s="10">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A90" s="9">
         <v>45292</v>
       </c>
-      <c r="B90" s="10">
+      <c r="B90" s="9">
         <v>45328</v>
       </c>
-      <c r="D90" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E90" s="12">
+      <c r="D90" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E90" s="11">
         <v>55.6</v>
       </c>
-      <c r="F90" s="12">
+      <c r="F90" s="11">
         <v>62.8</v>
       </c>
-      <c r="G90" s="12">
+      <c r="G90" s="11">
         <v>64.2</v>
       </c>
-      <c r="H90" s="12">
+      <c r="H90" s="11">
         <v>55.8</v>
       </c>
-      <c r="I90" s="12">
+      <c r="I90" s="11">
         <v>66.8</v>
       </c>
     </row>
-    <row r="91" spans="1:9">
-      <c r="A91" s="10">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A91" s="9">
         <v>45323</v>
       </c>
-      <c r="B91" s="10">
+      <c r="B91" s="9">
         <v>45356</v>
       </c>
-      <c r="D91" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E91" s="12">
+      <c r="D91" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E91" s="11">
         <v>56.5</v>
       </c>
-      <c r="F91" s="12">
+      <c r="F91" s="11">
         <v>61.8</v>
       </c>
-      <c r="G91" s="12">
+      <c r="G91" s="11">
         <v>64.2</v>
       </c>
-      <c r="H91" s="12">
+      <c r="H91" s="11">
         <v>57.6</v>
       </c>
-      <c r="I91" s="12">
+      <c r="I91" s="11">
         <v>62.9</v>
       </c>
     </row>
-    <row r="92" spans="1:9">
-      <c r="A92" s="10">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A92" s="9">
         <v>45352</v>
       </c>
-      <c r="B92" s="10">
+      <c r="B92" s="9">
         <v>45384</v>
       </c>
-      <c r="D92" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E92" s="12">
+      <c r="D92" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E92" s="11">
         <v>58.3</v>
       </c>
-      <c r="F92" s="12">
+      <c r="F92" s="11">
         <v>63.5</v>
       </c>
-      <c r="G92" s="12">
+      <c r="G92" s="11">
         <v>66.3</v>
       </c>
-      <c r="H92" s="12">
+      <c r="H92" s="11">
         <v>53</v>
       </c>
-      <c r="I92" s="12">
+      <c r="I92" s="11">
         <v>66.8</v>
       </c>
     </row>
-    <row r="93" spans="1:9">
-      <c r="A93" s="10">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A93" s="9">
         <v>45383</v>
       </c>
-      <c r="B93" s="10">
+      <c r="B93" s="9">
         <v>45419</v>
       </c>
-      <c r="D93" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E93" s="12">
+      <c r="D93" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E93" s="11">
         <v>52.9</v>
       </c>
-      <c r="F93" s="12">
+      <c r="F93" s="11">
         <v>62.7</v>
       </c>
-      <c r="G93" s="12">
+      <c r="G93" s="11">
         <v>63.8</v>
       </c>
-      <c r="H93" s="12">
+      <c r="H93" s="11">
         <v>44.1</v>
       </c>
-      <c r="I93" s="12">
+      <c r="I93" s="11">
         <v>68.5</v>
       </c>
     </row>
-    <row r="94" spans="1:9">
-      <c r="A94" s="10">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A94" s="9">
         <v>45413</v>
       </c>
-      <c r="B94" s="10">
+      <c r="B94" s="9">
         <v>45447</v>
       </c>
-      <c r="D94" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E94" s="12">
+      <c r="D94" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E94" s="11">
         <v>55.6</v>
       </c>
-      <c r="F94" s="12">
+      <c r="F94" s="11">
         <v>65.5</v>
       </c>
-      <c r="G94" s="12">
+      <c r="G94" s="11">
         <v>64.900000000000006</v>
       </c>
-      <c r="H94" s="12">
+      <c r="H94" s="11">
         <v>57.8</v>
       </c>
-      <c r="I94" s="12">
+      <c r="I94" s="11">
         <v>65.2</v>
       </c>
     </row>
-    <row r="95" spans="1:9">
-      <c r="A95" s="10">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A95" s="9">
         <v>45444</v>
       </c>
-      <c r="B95" s="10">
+      <c r="B95" s="9">
         <v>45475</v>
       </c>
-      <c r="D95" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E95" s="12">
+      <c r="D95" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E95" s="11">
         <v>55.3</v>
       </c>
-      <c r="F95" s="12">
+      <c r="F95" s="11">
         <v>66.099999999999994</v>
       </c>
-      <c r="G95" s="12">
+      <c r="G95" s="11">
         <v>64.5</v>
       </c>
-      <c r="H95" s="12">
+      <c r="H95" s="11">
         <v>61</v>
       </c>
-      <c r="I95" s="12">
+      <c r="I95" s="11">
         <v>63.6</v>
       </c>
     </row>
-    <row r="96" spans="1:9">
-      <c r="A96" s="10">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A96" s="9">
         <v>45474</v>
       </c>
-      <c r="B96" s="10">
+      <c r="B96" s="9">
         <v>45510</v>
       </c>
-      <c r="D96" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E96" s="12">
+      <c r="D96" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E96" s="11">
         <v>56.5</v>
       </c>
-      <c r="F96" s="12">
+      <c r="F96" s="11">
         <v>62</v>
       </c>
-      <c r="G96" s="12">
+      <c r="G96" s="11">
         <v>60.9</v>
       </c>
-      <c r="H96" s="12">
+      <c r="H96" s="11">
         <v>63.8</v>
       </c>
-      <c r="I96" s="12">
+      <c r="I96" s="11">
         <v>65.7</v>
       </c>
     </row>
-    <row r="97" spans="1:9">
-      <c r="A97" s="10">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A97" s="9">
         <v>45505</v>
       </c>
-      <c r="B97" s="10">
+      <c r="B97" s="9">
         <v>45538</v>
       </c>
-      <c r="D97" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E97" s="12">
+      <c r="D97" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E97" s="11">
         <v>56.4</v>
       </c>
-      <c r="F97" s="12">
+      <c r="F97" s="11">
         <v>62.4</v>
       </c>
-      <c r="G97" s="12">
+      <c r="G97" s="11">
         <v>63.8</v>
       </c>
-      <c r="H97" s="12">
+      <c r="H97" s="11">
         <v>61.6</v>
       </c>
-      <c r="I97" s="12">
+      <c r="I97" s="11">
         <v>69</v>
       </c>
     </row>
-    <row r="98" spans="1:9">
-      <c r="A98" s="10">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A98" s="9">
         <v>45536</v>
       </c>
-      <c r="B98" s="10">
+      <c r="B98" s="9">
         <v>45566</v>
       </c>
-      <c r="C98" s="11">
+      <c r="C98" s="15">
         <v>0.39583333333333331</v>
       </c>
-      <c r="D98" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E98" s="12">
+      <c r="D98" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E98" s="11">
         <v>58.6</v>
       </c>
-      <c r="F98" s="12">
+      <c r="F98" s="11">
         <v>65.400000000000006</v>
       </c>
-      <c r="G98" s="12">
+      <c r="G98" s="11">
         <v>66.900000000000006</v>
       </c>
-      <c r="H98" s="12">
+      <c r="H98" s="11">
         <v>58.4</v>
       </c>
-      <c r="I98" s="12">
+      <c r="I98" s="11">
         <v>71.3</v>
       </c>
     </row>
-    <row r="99" spans="1:9">
-      <c r="A99" s="10">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A99" s="9">
         <v>45566</v>
       </c>
-      <c r="B99" s="10">
+      <c r="B99" s="9">
         <v>45601</v>
       </c>
-      <c r="C99" s="11">
+      <c r="C99" s="15">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D99" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E99" s="12">
+      <c r="D99" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E99" s="11">
         <v>58.9</v>
       </c>
-      <c r="F99" s="12">
+      <c r="F99" s="11">
         <v>65.7</v>
       </c>
-      <c r="G99" s="12">
+      <c r="G99" s="11">
         <v>65.8</v>
       </c>
-      <c r="H99" s="12">
+      <c r="H99" s="11">
         <v>64.099999999999994</v>
       </c>
-      <c r="I99" s="12">
+      <c r="I99" s="11">
         <v>65.8</v>
       </c>
     </row>
-    <row r="100" spans="1:9">
-      <c r="A100" s="10">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A100" s="9">
         <v>45597</v>
       </c>
-      <c r="B100" s="10">
+      <c r="B100" s="9">
         <v>45629</v>
       </c>
-      <c r="C100" s="11">
+      <c r="C100" s="15">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D100" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E100" s="12">
+      <c r="D100" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E100" s="11">
         <v>58.4</v>
       </c>
-      <c r="F100" s="12">
+      <c r="F100" s="11">
         <v>63.6</v>
       </c>
-      <c r="G100" s="12">
+      <c r="G100" s="11">
         <v>68.8</v>
       </c>
-      <c r="H100" s="12">
+      <c r="H100" s="11">
         <v>63.8</v>
       </c>
-      <c r="I100" s="12">
+      <c r="I100" s="11">
         <v>68.8</v>
       </c>
     </row>
-    <row r="101" spans="1:9">
-      <c r="A101" s="10">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A101" s="9">
         <v>45627</v>
       </c>
-      <c r="B101" s="10">
+      <c r="B101" s="9">
         <v>45664</v>
       </c>
-      <c r="C101" s="11">
+      <c r="C101" s="15">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D101" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E101" s="12">
+      <c r="D101" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E101" s="11">
         <v>57.3</v>
       </c>
-      <c r="F101" s="12">
+      <c r="F101" s="11">
         <v>65.8</v>
       </c>
-      <c r="G101" s="12">
+      <c r="G101" s="11">
         <v>68</v>
       </c>
-      <c r="H101" s="12">
+      <c r="H101" s="11">
         <v>66.8</v>
       </c>
-      <c r="I101" s="12">
+      <c r="I101" s="11">
         <v>61.6</v>
       </c>
     </row>
-    <row r="102" spans="1:9">
-      <c r="A102" s="10">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A102" s="9">
         <v>45658</v>
       </c>
-      <c r="B102" s="10">
+      <c r="B102" s="9">
         <v>45692</v>
       </c>
-      <c r="C102" s="11">
+      <c r="C102" s="15">
         <v>0.4513888888888889</v>
       </c>
-      <c r="D102" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E102" s="12">
+      <c r="D102" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E102" s="11">
         <v>62</v>
       </c>
-      <c r="F102" s="12">
+      <c r="F102" s="11">
         <v>66.099999999999994</v>
       </c>
-      <c r="G102" s="12">
+      <c r="G102" s="11">
         <v>73.099999999999994</v>
       </c>
-      <c r="H102" s="12">
+      <c r="H102" s="11">
         <v>70.400000000000006</v>
       </c>
-      <c r="I102" s="12">
+      <c r="I102" s="11">
         <v>70.2</v>
       </c>
     </row>
-    <row r="103" spans="1:9">
-      <c r="A103" s="10">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A103" s="9">
         <v>45689</v>
       </c>
-      <c r="B103" s="10">
+      <c r="B103" s="9">
         <v>45720</v>
       </c>
-      <c r="C103" s="11">
+      <c r="C103" s="15">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D103" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E103" s="12">
+      <c r="D103" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E103" s="11">
         <v>62.8</v>
       </c>
-      <c r="F103" s="12">
+      <c r="F103" s="11">
         <v>66.2</v>
       </c>
-      <c r="G103" s="12">
+      <c r="G103" s="11">
         <v>77</v>
       </c>
-      <c r="H103" s="12">
+      <c r="H103" s="11">
         <v>65.5</v>
       </c>
-      <c r="I103" s="12">
+      <c r="I103" s="11">
         <v>77.3</v>
       </c>
     </row>
-    <row r="104" spans="1:9">
-      <c r="A104" s="10">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A104" s="9">
         <v>45717</v>
       </c>
-      <c r="B104" s="10">
+      <c r="B104" s="9">
         <v>45749</v>
       </c>
-      <c r="C104" s="11">
+      <c r="C104" s="15">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D104" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E104" s="12">
+      <c r="D104" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E104" s="11">
         <v>57.1</v>
       </c>
-      <c r="F104" s="12">
+      <c r="F104" s="11">
         <v>60.6</v>
       </c>
-      <c r="G104" s="12">
+      <c r="G104" s="11">
         <v>61</v>
       </c>
-      <c r="H104" s="12">
+      <c r="H104" s="11">
         <v>56.4</v>
       </c>
-      <c r="I104" s="12">
+      <c r="I104" s="11">
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="105" spans="1:9">
-      <c r="A105" s="10">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A105" s="9">
         <v>45748</v>
       </c>
-      <c r="B105" s="10">
+      <c r="B105" s="9">
         <v>45783</v>
       </c>
-      <c r="C105" s="11">
+      <c r="C105" s="15">
         <v>0.40625</v>
       </c>
-      <c r="D105" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E105" s="12">
+      <c r="D105" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E105" s="11">
         <v>58.8</v>
       </c>
-      <c r="F105" s="12">
+      <c r="F105" s="11">
         <v>60.6</v>
       </c>
-      <c r="G105" s="12">
+      <c r="G105" s="11">
         <v>72.3</v>
       </c>
-      <c r="H105" s="12">
+      <c r="H105" s="11">
         <v>62.3</v>
       </c>
-      <c r="I105" s="12">
+      <c r="I105" s="11">
         <v>75.599999999999994</v>
       </c>
     </row>
-    <row r="106" spans="1:9">
-      <c r="A106" s="10">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A106" s="9">
         <v>45778</v>
       </c>
-      <c r="B106" s="10">
+      <c r="B106" s="9">
         <v>45811</v>
       </c>
-      <c r="C106" s="11">
+      <c r="C106" s="15">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D106" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E106" s="12">
+      <c r="D106" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E106" s="11">
         <v>59.4</v>
       </c>
-      <c r="F106" s="12">
+      <c r="F106" s="11">
         <v>65.099999999999994</v>
       </c>
-      <c r="G106" s="12">
+      <c r="G106" s="11">
         <v>72.099999999999994</v>
       </c>
-      <c r="H106" s="12">
+      <c r="H106" s="11">
         <v>63.1</v>
       </c>
-      <c r="I106" s="12">
+      <c r="I106" s="11">
         <v>78.400000000000006</v>
       </c>
     </row>
-    <row r="107" spans="1:9">
-      <c r="A107" s="10">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A107" s="9">
         <v>45809</v>
       </c>
-      <c r="B107" s="10">
+      <c r="B107" s="9">
         <v>45839</v>
       </c>
-      <c r="C107" s="11">
+      <c r="C107" s="15">
         <v>0.4375</v>
       </c>
-      <c r="D107" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E107" s="12">
+      <c r="D107" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E107" s="11">
         <v>60.7</v>
       </c>
-      <c r="F107" s="12">
+      <c r="F107" s="11">
         <v>64.5</v>
       </c>
-      <c r="G107" s="12">
+      <c r="G107" s="11">
         <v>68.3</v>
       </c>
-      <c r="H107" s="12">
+      <c r="H107" s="11">
         <v>62</v>
       </c>
-      <c r="I107" s="12">
+      <c r="I107" s="11">
         <v>80.900000000000006</v>
       </c>
     </row>
-    <row r="108" spans="1:9">
-      <c r="A108" s="10">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A108" s="9">
         <v>45839</v>
       </c>
-      <c r="B108" s="10">
+      <c r="B108" s="9">
         <v>45874</v>
       </c>
-      <c r="C108" s="11">
+      <c r="C108" s="15">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D108" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E108" s="12">
+      <c r="D108" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E108" s="11">
         <v>59.2</v>
       </c>
-      <c r="F108" s="12">
+      <c r="F108" s="11">
         <v>62.6</v>
       </c>
-      <c r="G108" s="12">
+      <c r="G108" s="11">
         <v>68.3</v>
       </c>
-      <c r="H108" s="12">
+      <c r="H108" s="11">
         <v>63</v>
       </c>
-      <c r="I108" s="12">
+      <c r="I108" s="11">
         <v>71.900000000000006</v>
       </c>
     </row>
-    <row r="109" spans="1:9">
-      <c r="A109" s="10">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A109" s="9">
         <v>45870</v>
       </c>
-      <c r="B109" s="10">
+      <c r="B109" s="9">
         <v>45902</v>
       </c>
-      <c r="C109" s="11">
+      <c r="C109" s="15">
         <v>0.41666666666666669</v>
       </c>
-      <c r="D109" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E109" s="12">
+      <c r="D109" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E109" s="11">
         <v>59.3</v>
       </c>
-      <c r="F109" s="12">
+      <c r="F109" s="11">
         <v>63.9</v>
       </c>
-      <c r="G109" s="12">
+      <c r="G109" s="11">
         <v>72.2</v>
       </c>
-      <c r="H109" s="12">
+      <c r="H109" s="11">
         <v>65.099999999999994</v>
       </c>
-      <c r="I109" s="12">
+      <c r="I109" s="11">
         <v>79.2</v>
       </c>
     </row>
-    <row r="110" spans="1:9">
-      <c r="A110" s="10">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A110" s="9">
         <v>45901</v>
       </c>
-      <c r="B110" s="10">
+      <c r="B110" s="9">
         <v>45937</v>
       </c>
-      <c r="C110" s="11">
+      <c r="C110" s="15">
         <v>0.4201388888888889</v>
       </c>
-      <c r="D110" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E110" s="12">
+      <c r="D110" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E110" s="11">
         <v>57.4</v>
       </c>
-      <c r="F110" s="12">
+      <c r="F110" s="11">
         <v>59.6</v>
       </c>
-      <c r="G110" s="12">
+      <c r="G110" s="11">
         <v>66</v>
       </c>
-      <c r="H110" s="12">
+      <c r="H110" s="11">
         <v>54.2</v>
       </c>
-      <c r="I110" s="12">
+      <c r="I110" s="11">
         <v>75.5</v>
       </c>
     </row>
-    <row r="111" spans="1:9">
-      <c r="A111" s="10">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A111" s="9">
         <v>45931</v>
       </c>
-      <c r="B111" s="10">
+      <c r="B111" s="9">
         <v>45965</v>
       </c>
-      <c r="C111" s="11">
+      <c r="C111" s="15">
         <v>0.44444444444444442</v>
       </c>
-      <c r="D111" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E111" s="12">
+      <c r="D111" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E111" s="11">
         <v>57.4</v>
       </c>
-      <c r="F111" s="12">
+      <c r="F111" s="11">
         <v>64.599999999999994</v>
       </c>
-      <c r="G111" s="12">
+      <c r="G111" s="11">
         <v>67.7</v>
       </c>
-      <c r="H111" s="12">
+      <c r="H111" s="11">
         <v>61.7</v>
       </c>
-      <c r="I111" s="12">
+      <c r="I111" s="11">
         <v>73.2</v>
       </c>
     </row>
-    <row r="112" spans="1:9">
-      <c r="A112" s="10">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A112" s="9">
         <v>45962</v>
       </c>
-      <c r="B112" s="10">
+      <c r="B112" s="9">
         <v>45993</v>
       </c>
-      <c r="C112" s="11">
+      <c r="C112" s="15">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D112" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E112" s="12">
+      <c r="D112" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E112" s="11">
         <v>55.7</v>
       </c>
-      <c r="F112" s="12">
+      <c r="F112" s="11">
         <v>62.9</v>
       </c>
-      <c r="G112" s="12">
+      <c r="G112" s="11">
         <v>62.9</v>
       </c>
-      <c r="H112" s="12">
+      <c r="H112" s="11">
         <v>64.900000000000006</v>
       </c>
-      <c r="I112" s="12">
+      <c r="I112" s="11">
         <v>70.8</v>
       </c>
     </row>
-    <row r="113" spans="1:9">
-      <c r="A113" s="10">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A113" s="9">
         <v>45992</v>
       </c>
-      <c r="B113" s="10">
-        <v>45663</v>
-      </c>
-      <c r="C113" s="11">
+      <c r="B113" s="9">
+        <v>46028</v>
+      </c>
+      <c r="C113" s="15">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D113" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E113" s="12">
+      <c r="D113" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E113" s="11">
         <v>54.2</v>
       </c>
-      <c r="F113" s="13">
+      <c r="F113" s="12">
         <v>65.3</v>
       </c>
-      <c r="G113" s="13">
+      <c r="G113" s="12">
         <v>66.2</v>
       </c>
-      <c r="H113" s="13">
+      <c r="H113" s="12">
         <v>66.7</v>
       </c>
-      <c r="I113" s="13">
+      <c r="I113" s="12">
         <v>62.9</v>
       </c>
     </row>
-    <row r="114" spans="1:9">
-      <c r="A114" s="10">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A114" s="9">
         <v>46023</v>
       </c>
-      <c r="B114" s="10">
-        <v>45691</v>
-      </c>
-      <c r="C114" s="11">
+      <c r="B114" s="9">
+        <v>46056</v>
+      </c>
+      <c r="C114" s="15">
         <v>0.45833333333333331</v>
       </c>
-      <c r="D114" s="11" t="s">
-        <v>12</v>
-      </c>
-      <c r="E114" s="12">
+      <c r="D114" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E114" s="11">
         <v>59.6</v>
       </c>
-      <c r="F114" s="13">
+      <c r="F114" s="12">
         <v>65.8</v>
       </c>
-      <c r="G114" s="13">
+      <c r="G114" s="12">
         <v>64.8</v>
       </c>
-      <c r="H114" s="13">
+      <c r="H114" s="12">
         <v>71.400000000000006</v>
       </c>
-      <c r="I114" s="13">
+      <c r="I114" s="12">
         <v>71.3</v>
       </c>
     </row>
-    <row r="115" spans="1:9">
-      <c r="A115" s="10">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A115" s="9">
         <v>46054</v>
       </c>
-      <c r="B115" s="10">
-        <v>45719</v>
-      </c>
-      <c r="C115" s="11">
+      <c r="B115" s="9">
+        <v>46084</v>
+      </c>
+      <c r="C115" s="15">
         <v>0.45833333333333331</v>
+      </c>
+      <c r="D115" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E115" s="11">
+        <v>61.5</v>
+      </c>
+      <c r="F115" s="12">
+        <v>66.3</v>
+      </c>
+      <c r="G115" s="12">
+        <v>62.6</v>
+      </c>
+      <c r="H115" s="12">
+        <v>76.7</v>
+      </c>
+      <c r="I115" s="12">
+        <v>67.8</v>
+      </c>
+    </row>
+    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A116" s="9">
+        <v>46082</v>
+      </c>
+      <c r="B116" s="9">
+        <v>46119</v>
       </c>
     </row>
   </sheetData>
@@ -7900,12 +7979,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1E55565-0C4A-423B-A75C-9DC33F6F8AE5}">
   <dimension ref="B2:K3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
@@ -7921,7 +8000,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="2:11">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
@@ -7941,9 +8020,9 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A53279-3D0D-4247-AAE5-068BE8617509}">
   <dimension ref="A1"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="16384" width="9" style="14"/>
+    <col min="1" max="16384" width="9" style="13"/>
   </cols>
   <sheetData/>
   <phoneticPr fontId="2" type="noConversion"/>

--- a/data/macro/USA/Logistic manager index.xlsx
+++ b/data/macro/USA/Logistic manager index.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="20417"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\PycharmProjects\AlternativeData\data\macro\USA\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10A9A4B4-AC35-4633-B17A-346F9021296C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE65BA4A-2C94-4124-A821-EE7D801B11CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28500" yWindow="1020" windowWidth="22260" windowHeight="12645" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LMI" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="14">
   <si>
     <t>Inventory Costs</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -94,7 +94,7 @@
     <numFmt numFmtId="176" formatCode="[$-409]h:mm\ AM/PM;@"/>
     <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
     <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="180" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -220,10 +220,10 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="180" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="180" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -993,6 +993,9 @@
                 <c:pt idx="113">
                   <c:v>61.5</c:v>
                 </c:pt>
+                <c:pt idx="114">
+                  <c:v>65.7</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -1659,6 +1662,9 @@
                 <c:pt idx="113">
                   <c:v>66.3</c:v>
                 </c:pt>
+                <c:pt idx="114">
+                  <c:v>67.8</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -2397,6 +2403,9 @@
                 <c:pt idx="113">
                   <c:v>62.6</c:v>
                 </c:pt>
+                <c:pt idx="114">
+                  <c:v>67.400000000000006</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3135,6 +3144,9 @@
                 <c:pt idx="113">
                   <c:v>76.7</c:v>
                 </c:pt>
+                <c:pt idx="114">
+                  <c:v>89.4</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
@@ -3872,6 +3884,9 @@
                 </c:pt>
                 <c:pt idx="113">
                   <c:v>67.8</c:v>
+                </c:pt>
+                <c:pt idx="114">
+                  <c:v>76.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3933,8 +3948,8 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
@@ -3995,8 +4010,8 @@
                     <a:lumOff val="35000"/>
                   </a:schemeClr>
                 </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
+                <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+                <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
                 <a:cs typeface="+mn-cs"/>
               </a:defRPr>
             </a:pPr>
@@ -4038,8 +4053,8 @@
                   <a:lumOff val="35000"/>
                 </a:schemeClr>
               </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
+              <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+              <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
               <a:cs typeface="+mn-cs"/>
             </a:defRPr>
           </a:pPr>
@@ -4049,6 +4064,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -4056,7 +4072,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -4073,7 +4088,10 @@
     <a:lstStyle/>
     <a:p>
       <a:pPr>
-        <a:defRPr/>
+        <a:defRPr>
+          <a:latin typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+          <a:ea typeface="Verdana" panose="020B0604030504040204" pitchFamily="34" charset="0"/>
+        </a:defRPr>
       </a:pPr>
       <a:endParaRPr lang="ko-KR"/>
     </a:p>
@@ -4949,15 +4967,15 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:I116"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="11.375" style="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.125" style="10" customWidth="1"/>
-    <col min="5" max="5" width="8.125" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.625" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.625" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.125" style="12" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="11.3984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13" style="15" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.09765625" style="10" customWidth="1"/>
+    <col min="5" max="5" width="8.09765625" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.59765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.59765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.09765625" style="12" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="12" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="8"/>
   </cols>
@@ -7967,6 +7985,27 @@
       </c>
       <c r="B116" s="9">
         <v>46119</v>
+      </c>
+      <c r="C116" s="15">
+        <v>0.39583333333333331</v>
+      </c>
+      <c r="D116" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E116" s="11">
+        <v>65.7</v>
+      </c>
+      <c r="F116" s="12">
+        <v>67.8</v>
+      </c>
+      <c r="G116" s="12">
+        <v>67.400000000000006</v>
+      </c>
+      <c r="H116" s="12">
+        <v>89.4</v>
+      </c>
+      <c r="I116" s="12">
+        <v>76.2</v>
       </c>
     </row>
   </sheetData>
@@ -7979,12 +8018,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1E55565-0C4A-423B-A75C-9DC33F6F8AE5}">
   <dimension ref="B2:K3"/>
-  <sheetFormatPr defaultColWidth="8.875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B2" s="3" t="s">
         <v>8</v>
       </c>
@@ -8000,7 +8039,7 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="2:11" x14ac:dyDescent="0.4">
       <c r="B3" s="3" t="s">
         <v>9</v>
       </c>
@@ -8020,7 +8059,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A53279-3D0D-4247-AAE5-068BE8617509}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="16384" width="9" style="13"/>
   </cols>

--- a/data/macro/USA/Logistic manager index.xlsx
+++ b/data/macro/USA/Logistic manager index.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE65BA4A-2C94-4124-A821-EE7D801B11CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D470733-7C87-4202-9F5D-84BFEDD31382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,12 +22,21 @@
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="128" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="14">
   <si>
     <t>Inventory Costs</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -642,6 +651,9 @@
                 <c:pt idx="114">
                   <c:v>46082</c:v>
                 </c:pt>
+                <c:pt idx="115">
+                  <c:v>46113</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -995,6 +1007,9 @@
                 </c:pt>
                 <c:pt idx="114">
                   <c:v>65.7</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>69.900000000000006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1383,6 +1398,9 @@
                 <c:pt idx="114">
                   <c:v>46082</c:v>
                 </c:pt>
+                <c:pt idx="115">
+                  <c:v>46113</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1664,6 +1682,9 @@
                 </c:pt>
                 <c:pt idx="114">
                   <c:v>67.8</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>73.2</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2052,6 +2073,9 @@
                 <c:pt idx="114">
                   <c:v>46082</c:v>
                 </c:pt>
+                <c:pt idx="115">
+                  <c:v>46113</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2405,6 +2429,9 @@
                 </c:pt>
                 <c:pt idx="114">
                   <c:v>67.400000000000006</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>72.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2793,6 +2820,9 @@
                 <c:pt idx="114">
                   <c:v>46082</c:v>
                 </c:pt>
+                <c:pt idx="115">
+                  <c:v>46113</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3146,6 +3176,9 @@
                 </c:pt>
                 <c:pt idx="114">
                   <c:v>89.4</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>95</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3534,6 +3567,9 @@
                 <c:pt idx="114">
                   <c:v>46082</c:v>
                 </c:pt>
+                <c:pt idx="115">
+                  <c:v>46113</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3887,6 +3923,9 @@
                 </c:pt>
                 <c:pt idx="114">
                   <c:v>76.2</c:v>
+                </c:pt>
+                <c:pt idx="115">
+                  <c:v>74.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4966,10 +5005,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I116"/>
+  <dimension ref="A1:I117"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="2" width="11.3984375" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="15" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="11.09765625" style="10" customWidth="1"/>
     <col min="5" max="5" width="8.09765625" style="11" bestFit="1" customWidth="1"/>
@@ -8006,6 +8045,35 @@
       </c>
       <c r="I116" s="12">
         <v>76.2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A117" s="9">
+        <v>46113</v>
+      </c>
+      <c r="B117" s="9">
+        <v>46147</v>
+      </c>
+      <c r="C117" s="15">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D117" s="10" t="s">
+        <v>12</v>
+      </c>
+      <c r="E117" s="11">
+        <v>69.900000000000006</v>
+      </c>
+      <c r="F117" s="12">
+        <v>73.2</v>
+      </c>
+      <c r="G117" s="12">
+        <v>72.7</v>
+      </c>
+      <c r="H117" s="12">
+        <v>95</v>
+      </c>
+      <c r="I117" s="12">
+        <v>74.7</v>
       </c>
     </row>
   </sheetData>

--- a/data/macro/USA/Logistic manager index.xlsx
+++ b/data/macro/USA/Logistic manager index.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\krm\PycharmProjects\AlternativeData\data\macro\USA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D470733-7C87-4202-9F5D-84BFEDD31382}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57CBBA7B-2F36-465C-8330-4F0F6E69EF7D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="LMI" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="129" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="130" uniqueCount="14">
   <si>
     <t>Inventory Costs</t>
     <phoneticPr fontId="3" type="noConversion"/>
@@ -66,10 +66,6 @@
     <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
-    <t>https://tradingeconomics.com/united-states/lmi-logistics-managers-index-current</t>
-    <phoneticPr fontId="3" type="noConversion"/>
-  </si>
-  <si>
     <t>source</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -93,36 +89,39 @@
     <t>Time</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
+  <si>
+    <t>https://tradingeconomics.com/united-states/lmi-logistics-managers-index-current</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="5">
-    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="176" formatCode="[$-409]h:mm\ AM/PM;@"/>
-    <numFmt numFmtId="177" formatCode="yyyy\-mm\-dd;@"/>
-    <numFmt numFmtId="178" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="179" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
+    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="[$-409]h:mm\ AM/PM;@"/>
+    <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd;@"/>
+    <numFmt numFmtId="167" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="168" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="9">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="8"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -137,7 +136,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -145,7 +144,7 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
+      <name val="Calibri"/>
       <family val="3"/>
       <charset val="129"/>
       <scheme val="minor"/>
@@ -189,7 +188,7 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
@@ -203,36 +202,36 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="6" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="177" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="176" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="167" fontId="7" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="179" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="6" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="179" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="168" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -654,6 +653,9 @@
                 <c:pt idx="115">
                   <c:v>46113</c:v>
                 </c:pt>
+                <c:pt idx="116">
+                  <c:v>46143</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1010,6 +1012,9 @@
                 </c:pt>
                 <c:pt idx="115">
                   <c:v>69.900000000000006</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>69.5</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -1401,6 +1406,9 @@
                 <c:pt idx="115">
                   <c:v>46113</c:v>
                 </c:pt>
+                <c:pt idx="116">
+                  <c:v>46143</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -1685,6 +1693,9 @@
                 </c:pt>
                 <c:pt idx="115">
                   <c:v>73.2</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>69.400000000000006</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2076,6 +2087,9 @@
                 <c:pt idx="115">
                   <c:v>46113</c:v>
                 </c:pt>
+                <c:pt idx="116">
+                  <c:v>46143</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -2432,6 +2446,9 @@
                 </c:pt>
                 <c:pt idx="115">
                   <c:v>72.7</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>70.7</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -2823,6 +2840,9 @@
                 <c:pt idx="115">
                   <c:v>46113</c:v>
                 </c:pt>
+                <c:pt idx="116">
+                  <c:v>46143</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3179,6 +3199,9 @@
                 </c:pt>
                 <c:pt idx="115">
                   <c:v>95</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>96</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -3570,6 +3593,9 @@
                 <c:pt idx="115">
                   <c:v>46113</c:v>
                 </c:pt>
+                <c:pt idx="116">
+                  <c:v>46143</c:v>
+                </c:pt>
               </c:numCache>
             </c:numRef>
           </c:cat>
@@ -3926,6 +3952,9 @@
                 </c:pt>
                 <c:pt idx="115">
                   <c:v>74.7</c:v>
+                </c:pt>
+                <c:pt idx="116">
+                  <c:v>84.1</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5005,21 +5034,21 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I117"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:I118"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="12.6"/>
   <cols>
-    <col min="1" max="2" width="12" style="9" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12.5546875" style="9" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13" style="15" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="11.09765625" style="10" customWidth="1"/>
-    <col min="5" max="5" width="8.09765625" style="11" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.59765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.59765625" style="12" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24.09765625" style="12" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="11.109375" style="10" customWidth="1"/>
+    <col min="5" max="5" width="8.109375" style="11" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.5546875" style="12" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.109375" style="12" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="19" style="12" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9">
       <c r="A1" s="4" t="s">
         <v>6</v>
       </c>
@@ -5027,10 +5056,10 @@
         <v>5</v>
       </c>
       <c r="C1" s="14" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D1" s="5" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="E1" s="6" t="s">
         <v>4</v>
@@ -5048,7 +5077,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9">
       <c r="A2" s="9">
         <v>42614</v>
       </c>
@@ -5056,7 +5085,7 @@
         <v>42647</v>
       </c>
       <c r="D2" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2" s="11">
         <v>63.9</v>
@@ -5072,7 +5101,7 @@
         <v>67.599999999999994</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9">
       <c r="A3" s="9">
         <v>42644</v>
       </c>
@@ -5080,7 +5109,7 @@
         <v>42675</v>
       </c>
       <c r="D3" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E3" s="11">
         <v>54.9</v>
@@ -5096,7 +5125,7 @@
         <v>59.5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9">
       <c r="A4" s="9">
         <v>42675</v>
       </c>
@@ -5104,7 +5133,7 @@
         <v>42710</v>
       </c>
       <c r="D4" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E4" s="11">
         <v>62.9</v>
@@ -5120,7 +5149,7 @@
         <v>65.5</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9">
       <c r="A5" s="9">
         <v>42705</v>
       </c>
@@ -5128,7 +5157,7 @@
         <v>42738</v>
       </c>
       <c r="D5" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E5" s="11">
         <v>62.9</v>
@@ -5144,7 +5173,7 @@
         <v>65.5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9">
       <c r="A6" s="9">
         <v>42736</v>
       </c>
@@ -5152,7 +5181,7 @@
         <v>42773</v>
       </c>
       <c r="D6" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E6" s="11">
         <v>66</v>
@@ -5168,7 +5197,7 @@
         <v>65.400000000000006</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9">
       <c r="A7" s="9">
         <v>42767</v>
       </c>
@@ -5176,7 +5205,7 @@
         <v>42801</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E7" s="11">
         <v>66</v>
@@ -5192,7 +5221,7 @@
         <v>65.400000000000006</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9">
       <c r="A8" s="9">
         <v>42795</v>
       </c>
@@ -5200,7 +5229,7 @@
         <v>42829</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E8" s="11">
         <v>65.599999999999994</v>
@@ -5216,7 +5245,7 @@
         <v>68.900000000000006</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9">
       <c r="A9" s="9">
         <v>42826</v>
       </c>
@@ -5224,7 +5253,7 @@
         <v>42857</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E9" s="11">
         <v>65.599999999999994</v>
@@ -5240,7 +5269,7 @@
         <v>68.900000000000006</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9">
       <c r="A10" s="9">
         <v>42856</v>
       </c>
@@ -5248,7 +5277,7 @@
         <v>42892</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E10" s="11">
         <v>65</v>
@@ -5264,7 +5293,7 @@
         <v>75.5</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9">
       <c r="A11" s="9">
         <v>42887</v>
       </c>
@@ -5272,7 +5301,7 @@
         <v>42920</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E11" s="11">
         <v>65</v>
@@ -5288,7 +5317,7 @@
         <v>75.5</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9">
       <c r="A12" s="9">
         <v>42917</v>
       </c>
@@ -5296,7 +5325,7 @@
         <v>42948</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E12" s="11">
         <v>62.78</v>
@@ -5312,7 +5341,7 @@
         <v>70.16</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9">
       <c r="A13" s="9">
         <v>42948</v>
       </c>
@@ -5320,7 +5349,7 @@
         <v>42983</v>
       </c>
       <c r="D13" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E13" s="11">
         <v>62.78</v>
@@ -5336,7 +5365,7 @@
         <v>70.16</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9">
       <c r="A14" s="9">
         <v>42979</v>
       </c>
@@ -5344,7 +5373,7 @@
         <v>43011</v>
       </c>
       <c r="D14" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E14" s="11">
         <v>66.180000000000007</v>
@@ -5360,7 +5389,7 @@
         <v>70.8</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9">
       <c r="A15" s="9">
         <v>43009</v>
       </c>
@@ -5368,7 +5397,7 @@
         <v>43046</v>
       </c>
       <c r="D15" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E15" s="11">
         <v>66.180000000000007</v>
@@ -5384,7 +5413,7 @@
         <v>70.8</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9">
       <c r="A16" s="9">
         <v>43040</v>
       </c>
@@ -5392,7 +5421,7 @@
         <v>43074</v>
       </c>
       <c r="D16" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E16" s="11">
         <v>66.180000000000007</v>
@@ -5408,7 +5437,7 @@
         <v>70.8</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9">
       <c r="A17" s="9">
         <v>43070</v>
       </c>
@@ -5416,7 +5445,7 @@
         <v>43102</v>
       </c>
       <c r="D17" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E17" s="11">
         <v>66.180000000000007</v>
@@ -5432,7 +5461,7 @@
         <v>70.8</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9">
       <c r="A18" s="9">
         <v>43101</v>
       </c>
@@ -5440,7 +5469,7 @@
         <v>43137</v>
       </c>
       <c r="D18" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E18" s="11">
         <v>64.099999999999994</v>
@@ -5456,7 +5485,7 @@
         <v>69.400000000000006</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9">
       <c r="A19" s="9">
         <v>43132</v>
       </c>
@@ -5464,7 +5493,7 @@
         <v>43165</v>
       </c>
       <c r="D19" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E19" s="11">
         <v>64.099999999999994</v>
@@ -5480,7 +5509,7 @@
         <v>69.400000000000006</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9">
       <c r="A20" s="9">
         <v>43160</v>
       </c>
@@ -5488,7 +5517,7 @@
         <v>43193</v>
       </c>
       <c r="D20" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E20" s="11">
         <v>70.83</v>
@@ -5504,7 +5533,7 @@
         <v>81.34</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9">
       <c r="A21" s="9">
         <v>43191</v>
       </c>
@@ -5512,7 +5541,7 @@
         <v>43221</v>
       </c>
       <c r="D21" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E21" s="11">
         <v>70.83</v>
@@ -5528,7 +5557,7 @@
         <v>81.34</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9">
       <c r="A22" s="9">
         <v>43221</v>
       </c>
@@ -5536,7 +5565,7 @@
         <v>43256</v>
       </c>
       <c r="D22" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E22" s="11">
         <v>69</v>
@@ -5552,7 +5581,7 @@
         <v>76.94</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9">
       <c r="A23" s="9">
         <v>43252</v>
       </c>
@@ -5560,7 +5589,7 @@
         <v>43284</v>
       </c>
       <c r="D23" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E23" s="11">
         <v>69</v>
@@ -5576,7 +5605,7 @@
         <v>76.94</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9">
       <c r="A24" s="9">
         <v>43282</v>
       </c>
@@ -5584,7 +5613,7 @@
         <v>43319</v>
       </c>
       <c r="D24" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E24" s="11">
         <v>68.790000000000006</v>
@@ -5600,7 +5629,7 @@
         <v>79.02</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9">
       <c r="A25" s="9">
         <v>43313</v>
       </c>
@@ -5608,7 +5637,7 @@
         <v>43347</v>
       </c>
       <c r="D25" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E25" s="11">
         <v>68.790000000000006</v>
@@ -5624,7 +5653,7 @@
         <v>79.02</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9">
       <c r="A26" s="9">
         <v>43344</v>
       </c>
@@ -5632,7 +5661,7 @@
         <v>43375</v>
       </c>
       <c r="D26" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E26" s="11">
         <v>70.22</v>
@@ -5650,7 +5679,7 @@
         <v>78.78</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9">
       <c r="A27" s="9">
         <v>43374</v>
       </c>
@@ -5658,7 +5687,7 @@
         <v>43410</v>
       </c>
       <c r="D27" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E27" s="11">
         <v>69.010000000000005</v>
@@ -5676,7 +5705,7 @@
         <v>81.400000000000006</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9">
       <c r="A28" s="9">
         <v>43405</v>
       </c>
@@ -5684,7 +5713,7 @@
         <v>43438</v>
       </c>
       <c r="D28" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E28" s="11">
         <v>66.66</v>
@@ -5702,7 +5731,7 @@
         <v>73.53</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9">
       <c r="A29" s="9">
         <v>43435</v>
       </c>
@@ -5710,7 +5739,7 @@
         <v>43467</v>
       </c>
       <c r="D29" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E29" s="11">
         <v>64.650000000000006</v>
@@ -5728,7 +5757,7 @@
         <v>72.73</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9">
       <c r="A30" s="9">
         <v>43466</v>
       </c>
@@ -5736,7 +5765,7 @@
         <v>43501</v>
       </c>
       <c r="D30" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E30" s="11">
         <v>65.2</v>
@@ -5754,7 +5783,7 @@
         <v>75.650000000000006</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9">
       <c r="A31" s="9">
         <v>43497</v>
       </c>
@@ -5762,7 +5791,7 @@
         <v>43529</v>
       </c>
       <c r="D31" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E31" s="11">
         <v>61.95</v>
@@ -5780,7 +5809,7 @@
         <v>74.510000000000005</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9">
       <c r="A32" s="9">
         <v>43525</v>
       </c>
@@ -5788,7 +5817,7 @@
         <v>43557</v>
       </c>
       <c r="D32" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E32" s="11">
         <v>60.4</v>
@@ -5806,7 +5835,7 @@
         <v>69.900000000000006</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9">
       <c r="A33" s="9">
         <v>43556</v>
       </c>
@@ -5814,7 +5843,7 @@
         <v>43592</v>
       </c>
       <c r="D33" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E33" s="11">
         <v>57.9</v>
@@ -5832,7 +5861,7 @@
         <v>70.7</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9">
       <c r="A34" s="9">
         <v>43586</v>
       </c>
@@ -5840,7 +5869,7 @@
         <v>43620</v>
       </c>
       <c r="D34" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E34" s="11">
         <v>56.7</v>
@@ -5858,7 +5887,7 @@
         <v>72.55</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9">
       <c r="A35" s="9">
         <v>43617</v>
       </c>
@@ -5866,7 +5895,7 @@
         <v>43648</v>
       </c>
       <c r="D35" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E35" s="11">
         <v>56</v>
@@ -5884,7 +5913,7 @@
         <v>71.2</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9">
       <c r="A36" s="9">
         <v>43647</v>
       </c>
@@ -5892,7 +5921,7 @@
         <v>43683</v>
       </c>
       <c r="D36" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E36" s="11">
         <v>57.2</v>
@@ -5910,7 +5939,7 @@
         <v>71.2</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9">
       <c r="A37" s="9">
         <v>43678</v>
       </c>
@@ -5918,7 +5947,7 @@
         <v>43711</v>
       </c>
       <c r="D37" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E37" s="11">
         <v>56.6</v>
@@ -5936,7 +5965,7 @@
         <v>70.3</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9">
       <c r="A38" s="9">
         <v>43709</v>
       </c>
@@ -5944,7 +5973,7 @@
         <v>43739</v>
       </c>
       <c r="D38" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E38" s="11">
         <v>56.6</v>
@@ -5962,7 +5991,7 @@
         <v>67.5</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9">
       <c r="A39" s="9">
         <v>43739</v>
       </c>
@@ -5970,7 +5999,7 @@
         <v>43774</v>
       </c>
       <c r="D39" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E39" s="11">
         <v>54.4</v>
@@ -5988,7 +6017,7 @@
         <v>66.7</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9">
       <c r="A40" s="9">
         <v>43770</v>
       </c>
@@ -5996,7 +6025,7 @@
         <v>43802</v>
       </c>
       <c r="D40" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E40" s="11">
         <v>54.5</v>
@@ -6014,7 +6043,7 @@
         <v>65.400000000000006</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9">
       <c r="A41" s="9">
         <v>43800</v>
       </c>
@@ -6022,7 +6051,7 @@
         <v>43837</v>
       </c>
       <c r="D41" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E41" s="11">
         <v>53.96</v>
@@ -6040,7 +6069,7 @@
         <v>63.43</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9">
       <c r="A42" s="9">
         <v>43831</v>
       </c>
@@ -6048,7 +6077,7 @@
         <v>43865</v>
       </c>
       <c r="D42" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E42" s="11">
         <v>54.12</v>
@@ -6066,7 +6095,7 @@
         <v>66.13</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9">
       <c r="A43" s="9">
         <v>43862</v>
       </c>
@@ -6074,7 +6103,7 @@
         <v>43893</v>
       </c>
       <c r="D43" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E43" s="11">
         <v>52.62</v>
@@ -6092,7 +6121,7 @@
         <v>61.8</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9">
       <c r="A44" s="9">
         <v>43891</v>
       </c>
@@ -6100,7 +6129,7 @@
         <v>43928</v>
       </c>
       <c r="D44" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E44" s="11">
         <v>58.87</v>
@@ -6118,7 +6147,7 @@
         <v>66.489999999999995</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9">
       <c r="A45" s="9">
         <v>43922</v>
       </c>
@@ -6126,7 +6155,7 @@
         <v>43956</v>
       </c>
       <c r="D45" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E45" s="11">
         <v>51.31</v>
@@ -6144,7 +6173,7 @@
         <v>63.1</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9">
       <c r="A46" s="9">
         <v>43952</v>
       </c>
@@ -6152,7 +6181,7 @@
         <v>43984</v>
       </c>
       <c r="D46" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E46" s="11">
         <v>54.46</v>
@@ -6170,7 +6199,7 @@
         <v>66.02</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9">
       <c r="A47" s="9">
         <v>43983</v>
       </c>
@@ -6178,7 +6207,7 @@
         <v>44019</v>
       </c>
       <c r="D47" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E47" s="11">
         <v>61.71</v>
@@ -6196,7 +6225,7 @@
         <v>63.46</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9">
       <c r="A48" s="9">
         <v>44013</v>
       </c>
@@ -6204,7 +6233,7 @@
         <v>44047</v>
       </c>
       <c r="D48" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E48" s="11">
         <v>63.03</v>
@@ -6222,7 +6251,7 @@
         <v>69.12</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9">
       <c r="A49" s="9">
         <v>44044</v>
       </c>
@@ -6230,7 +6259,7 @@
         <v>44075</v>
       </c>
       <c r="D49" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E49" s="11">
         <v>66</v>
@@ -6248,7 +6277,7 @@
         <v>64.739999999999995</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9">
       <c r="A50" s="9">
         <v>44075</v>
       </c>
@@ -6256,7 +6285,7 @@
         <v>44110</v>
       </c>
       <c r="D50" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E50" s="11">
         <v>70.47</v>
@@ -6274,7 +6303,7 @@
         <v>65.84</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9">
       <c r="A51" s="9">
         <v>44105</v>
       </c>
@@ -6282,7 +6311,7 @@
         <v>44138</v>
       </c>
       <c r="D51" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E51" s="11">
         <v>71.599999999999994</v>
@@ -6300,7 +6329,7 @@
         <v>73.599999999999994</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9">
       <c r="A52" s="9">
         <v>44136</v>
       </c>
@@ -6308,7 +6337,7 @@
         <v>44166</v>
       </c>
       <c r="D52" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E52" s="11">
         <v>70.8</v>
@@ -6326,7 +6355,7 @@
         <v>73.099999999999994</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9">
       <c r="A53" s="9">
         <v>44166</v>
       </c>
@@ -6334,7 +6363,7 @@
         <v>44201</v>
       </c>
       <c r="D53" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E53" s="11">
         <v>66.7</v>
@@ -6352,7 +6381,7 @@
         <v>71.8</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9">
       <c r="A54" s="9">
         <v>44197</v>
       </c>
@@ -6360,7 +6389,7 @@
         <v>44229</v>
       </c>
       <c r="D54" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E54" s="11">
         <v>67.2</v>
@@ -6378,7 +6407,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9">
       <c r="A55" s="9">
         <v>44228</v>
       </c>
@@ -6386,7 +6415,7 @@
         <v>44257</v>
       </c>
       <c r="D55" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E55" s="11">
         <v>71.400000000000006</v>
@@ -6404,7 +6433,7 @@
         <v>76.8</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9">
       <c r="A56" s="9">
         <v>44256</v>
       </c>
@@ -6412,7 +6441,7 @@
         <v>44292</v>
       </c>
       <c r="D56" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E56" s="11">
         <v>72.2</v>
@@ -6430,7 +6459,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9">
       <c r="A57" s="9">
         <v>44287</v>
       </c>
@@ -6438,7 +6467,7 @@
         <v>44320</v>
       </c>
       <c r="D57" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E57" s="11">
         <v>74.5</v>
@@ -6456,7 +6485,7 @@
         <v>84.6</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9">
       <c r="A58" s="9">
         <v>44317</v>
       </c>
@@ -6464,7 +6493,7 @@
         <v>44348</v>
       </c>
       <c r="D58" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E58" s="11">
         <v>71.3</v>
@@ -6482,7 +6511,7 @@
         <v>83.8</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9">
       <c r="A59" s="9">
         <v>44348</v>
       </c>
@@ -6490,7 +6519,7 @@
         <v>44383</v>
       </c>
       <c r="D59" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E59" s="11">
         <v>75</v>
@@ -6508,7 +6537,7 @@
         <v>89.4</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9">
       <c r="A60" s="9">
         <v>44378</v>
       </c>
@@ -6516,7 +6545,7 @@
         <v>44411</v>
       </c>
       <c r="D60" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E60" s="11">
         <v>74.5</v>
@@ -6534,7 +6563,7 @@
         <v>88.8</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9">
       <c r="A61" s="9">
         <v>44409</v>
       </c>
@@ -6542,7 +6571,7 @@
         <v>44446</v>
       </c>
       <c r="D61" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E61" s="11">
         <v>73.8</v>
@@ -6560,7 +6589,7 @@
         <v>85.9</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9">
       <c r="A62" s="9">
         <v>44440</v>
       </c>
@@ -6568,7 +6597,7 @@
         <v>44474</v>
       </c>
       <c r="D62" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E62" s="11">
         <v>72.2</v>
@@ -6586,7 +6615,7 @@
         <v>86.6</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9">
       <c r="A63" s="9">
         <v>44470</v>
       </c>
@@ -6594,7 +6623,7 @@
         <v>44502</v>
       </c>
       <c r="D63" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E63" s="11">
         <v>72.599999999999994</v>
@@ -6612,7 +6641,7 @@
         <v>85.9</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9">
       <c r="A64" s="9">
         <v>44501</v>
       </c>
@@ -6620,7 +6649,7 @@
         <v>44537</v>
       </c>
       <c r="D64" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E64" s="11">
         <v>73.400000000000006</v>
@@ -6638,7 +6667,7 @@
         <v>87.6</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9">
       <c r="A65" s="9">
         <v>44531</v>
       </c>
@@ -6646,7 +6675,7 @@
         <v>44565</v>
       </c>
       <c r="D65" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E65" s="11">
         <v>70.099999999999994</v>
@@ -6664,7 +6693,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9">
       <c r="A66" s="9">
         <v>44562</v>
       </c>
@@ -6672,7 +6701,7 @@
         <v>44593</v>
       </c>
       <c r="D66" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E66" s="11">
         <v>71.900000000000006</v>
@@ -6690,7 +6719,7 @@
         <v>87.9</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9">
       <c r="A67" s="9">
         <v>44593</v>
       </c>
@@ -6698,7 +6727,7 @@
         <v>44621</v>
       </c>
       <c r="D67" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E67" s="11">
         <v>75.2</v>
@@ -6716,7 +6745,7 @@
         <v>90.3</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9">
       <c r="A68" s="9">
         <v>44621</v>
       </c>
@@ -6724,7 +6753,7 @@
         <v>44656</v>
       </c>
       <c r="D68" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E68" s="11">
         <v>76.2</v>
@@ -6742,7 +6771,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9">
       <c r="A69" s="9">
         <v>44652</v>
       </c>
@@ -6750,7 +6779,7 @@
         <v>44684</v>
       </c>
       <c r="D69" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E69" s="11">
         <v>69.7</v>
@@ -6768,7 +6797,7 @@
         <v>87.7</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9">
       <c r="A70" s="9">
         <v>44682</v>
       </c>
@@ -6776,7 +6805,7 @@
         <v>44719</v>
       </c>
       <c r="D70" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E70" s="11">
         <v>67.099999999999994</v>
@@ -6794,7 +6823,7 @@
         <v>88.1</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9">
       <c r="A71" s="9">
         <v>44713</v>
       </c>
@@ -6802,7 +6831,7 @@
         <v>44747</v>
       </c>
       <c r="D71" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E71" s="11">
         <v>65</v>
@@ -6820,7 +6849,7 @@
         <v>83.8</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9">
       <c r="A72" s="9">
         <v>44743</v>
       </c>
@@ -6828,7 +6857,7 @@
         <v>44775</v>
       </c>
       <c r="D72" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E72" s="11">
         <v>60.7</v>
@@ -6846,7 +6875,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9">
       <c r="A73" s="9">
         <v>44774</v>
       </c>
@@ -6854,7 +6883,7 @@
         <v>44810</v>
       </c>
       <c r="D73" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E73" s="11">
         <v>59.7</v>
@@ -6872,7 +6901,7 @@
         <v>76.8</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9">
       <c r="A74" s="9">
         <v>44805</v>
       </c>
@@ -6880,7 +6909,7 @@
         <v>44838</v>
       </c>
       <c r="D74" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E74" s="11">
         <v>61.4</v>
@@ -6898,7 +6927,7 @@
         <v>77.2</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9">
       <c r="A75" s="9">
         <v>44835</v>
       </c>
@@ -6906,7 +6935,7 @@
         <v>44866</v>
       </c>
       <c r="D75" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E75" s="11">
         <v>57.5</v>
@@ -6924,7 +6953,7 @@
         <v>80.900000000000006</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9">
       <c r="A76" s="9">
         <v>44866</v>
       </c>
@@ -6932,7 +6961,7 @@
         <v>44901</v>
       </c>
       <c r="D76" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E76" s="11">
         <v>53.6</v>
@@ -6950,7 +6979,7 @@
         <v>73.400000000000006</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9">
       <c r="A77" s="9">
         <v>44896</v>
       </c>
@@ -6958,7 +6987,7 @@
         <v>44929</v>
       </c>
       <c r="D77" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E77" s="11">
         <v>54.6</v>
@@ -6976,7 +7005,7 @@
         <v>72.8</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9">
       <c r="A78" s="9">
         <v>44927</v>
       </c>
@@ -6984,7 +7013,7 @@
         <v>44964</v>
       </c>
       <c r="D78" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E78" s="11">
         <v>57.6</v>
@@ -7002,7 +7031,7 @@
         <v>74.2</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9">
       <c r="A79" s="9">
         <v>44958</v>
       </c>
@@ -7010,7 +7039,7 @@
         <v>44992</v>
       </c>
       <c r="D79" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E79" s="11">
         <v>54.7</v>
@@ -7028,7 +7057,7 @@
         <v>70.900000000000006</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9">
       <c r="A80" s="9">
         <v>44986</v>
       </c>
@@ -7036,7 +7065,7 @@
         <v>45020</v>
       </c>
       <c r="D80" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E80" s="11">
         <v>51.1</v>
@@ -7054,7 +7083,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9">
       <c r="A81" s="9">
         <v>45017</v>
       </c>
@@ -7062,7 +7091,7 @@
         <v>45048</v>
       </c>
       <c r="D81" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E81" s="11">
         <v>50.9</v>
@@ -7080,7 +7109,7 @@
         <v>65.099999999999994</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9">
       <c r="A82" s="9">
         <v>45047</v>
       </c>
@@ -7088,7 +7117,7 @@
         <v>45083</v>
       </c>
       <c r="D82" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E82" s="11">
         <v>47.3</v>
@@ -7106,7 +7135,7 @@
         <v>64.400000000000006</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9">
       <c r="A83" s="9">
         <v>45078</v>
       </c>
@@ -7114,7 +7143,7 @@
         <v>45111</v>
       </c>
       <c r="D83" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E83" s="11">
         <v>45.6</v>
@@ -7132,7 +7161,7 @@
         <v>57.1</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9">
       <c r="A84" s="9">
         <v>45108</v>
       </c>
@@ -7140,7 +7169,7 @@
         <v>45139</v>
       </c>
       <c r="D84" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E84" s="11">
         <v>45.4</v>
@@ -7158,7 +7187,7 @@
         <v>60.5</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9">
       <c r="A85" s="9">
         <v>45139</v>
       </c>
@@ -7166,7 +7195,7 @@
         <v>45174</v>
       </c>
       <c r="D85" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E85" s="11">
         <v>51.2</v>
@@ -7184,7 +7213,7 @@
         <v>69.099999999999994</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9">
       <c r="A86" s="9">
         <v>45170</v>
       </c>
@@ -7192,7 +7221,7 @@
         <v>45202</v>
       </c>
       <c r="D86" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E86" s="11">
         <v>52.4</v>
@@ -7210,7 +7239,7 @@
         <v>64.599999999999994</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9">
       <c r="A87" s="9">
         <v>45200</v>
       </c>
@@ -7218,7 +7247,7 @@
         <v>45237</v>
       </c>
       <c r="D87" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E87" s="11">
         <v>56.5</v>
@@ -7236,7 +7265,7 @@
         <v>69.8</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9">
       <c r="A88" s="9">
         <v>45231</v>
       </c>
@@ -7244,7 +7273,7 @@
         <v>45265</v>
       </c>
       <c r="D88" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E88" s="11">
         <v>49.4</v>
@@ -7262,7 +7291,7 @@
         <v>62.1</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9">
       <c r="A89" s="9">
         <v>45261</v>
       </c>
@@ -7270,7 +7299,7 @@
         <v>45293</v>
       </c>
       <c r="D89" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E89" s="11">
         <v>50.6</v>
@@ -7288,7 +7317,7 @@
         <v>55.8</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9">
       <c r="A90" s="9">
         <v>45292</v>
       </c>
@@ -7296,7 +7325,7 @@
         <v>45328</v>
       </c>
       <c r="D90" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E90" s="11">
         <v>55.6</v>
@@ -7314,7 +7343,7 @@
         <v>66.8</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9">
       <c r="A91" s="9">
         <v>45323</v>
       </c>
@@ -7322,7 +7351,7 @@
         <v>45356</v>
       </c>
       <c r="D91" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E91" s="11">
         <v>56.5</v>
@@ -7340,7 +7369,7 @@
         <v>62.9</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9">
       <c r="A92" s="9">
         <v>45352</v>
       </c>
@@ -7348,7 +7377,7 @@
         <v>45384</v>
       </c>
       <c r="D92" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E92" s="11">
         <v>58.3</v>
@@ -7366,7 +7395,7 @@
         <v>66.8</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9">
       <c r="A93" s="9">
         <v>45383</v>
       </c>
@@ -7374,7 +7403,7 @@
         <v>45419</v>
       </c>
       <c r="D93" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E93" s="11">
         <v>52.9</v>
@@ -7392,7 +7421,7 @@
         <v>68.5</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9">
       <c r="A94" s="9">
         <v>45413</v>
       </c>
@@ -7400,7 +7429,7 @@
         <v>45447</v>
       </c>
       <c r="D94" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E94" s="11">
         <v>55.6</v>
@@ -7418,7 +7447,7 @@
         <v>65.2</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9">
       <c r="A95" s="9">
         <v>45444</v>
       </c>
@@ -7426,7 +7455,7 @@
         <v>45475</v>
       </c>
       <c r="D95" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E95" s="11">
         <v>55.3</v>
@@ -7444,7 +7473,7 @@
         <v>63.6</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9">
       <c r="A96" s="9">
         <v>45474</v>
       </c>
@@ -7452,7 +7481,7 @@
         <v>45510</v>
       </c>
       <c r="D96" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E96" s="11">
         <v>56.5</v>
@@ -7470,7 +7499,7 @@
         <v>65.7</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9">
       <c r="A97" s="9">
         <v>45505</v>
       </c>
@@ -7478,7 +7507,7 @@
         <v>45538</v>
       </c>
       <c r="D97" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E97" s="11">
         <v>56.4</v>
@@ -7496,7 +7525,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9">
       <c r="A98" s="9">
         <v>45536</v>
       </c>
@@ -7507,7 +7536,7 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D98" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E98" s="11">
         <v>58.6</v>
@@ -7525,7 +7554,7 @@
         <v>71.3</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9">
       <c r="A99" s="9">
         <v>45566</v>
       </c>
@@ -7536,7 +7565,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D99" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E99" s="11">
         <v>58.9</v>
@@ -7554,7 +7583,7 @@
         <v>65.8</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9">
       <c r="A100" s="9">
         <v>45597</v>
       </c>
@@ -7565,7 +7594,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D100" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E100" s="11">
         <v>58.4</v>
@@ -7583,7 +7612,7 @@
         <v>68.8</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9">
       <c r="A101" s="9">
         <v>45627</v>
       </c>
@@ -7594,7 +7623,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D101" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E101" s="11">
         <v>57.3</v>
@@ -7612,7 +7641,7 @@
         <v>61.6</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9">
       <c r="A102" s="9">
         <v>45658</v>
       </c>
@@ -7623,7 +7652,7 @@
         <v>0.4513888888888889</v>
       </c>
       <c r="D102" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E102" s="11">
         <v>62</v>
@@ -7641,7 +7670,7 @@
         <v>70.2</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9">
       <c r="A103" s="9">
         <v>45689</v>
       </c>
@@ -7652,7 +7681,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D103" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E103" s="11">
         <v>62.8</v>
@@ -7670,7 +7699,7 @@
         <v>77.3</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9">
       <c r="A104" s="9">
         <v>45717</v>
       </c>
@@ -7681,7 +7710,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D104" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E104" s="11">
         <v>57.1</v>
@@ -7699,7 +7728,7 @@
         <v>70.599999999999994</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9">
       <c r="A105" s="9">
         <v>45748</v>
       </c>
@@ -7710,7 +7739,7 @@
         <v>0.40625</v>
       </c>
       <c r="D105" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E105" s="11">
         <v>58.8</v>
@@ -7728,7 +7757,7 @@
         <v>75.599999999999994</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9">
       <c r="A106" s="9">
         <v>45778</v>
       </c>
@@ -7739,7 +7768,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D106" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E106" s="11">
         <v>59.4</v>
@@ -7757,7 +7786,7 @@
         <v>78.400000000000006</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9">
       <c r="A107" s="9">
         <v>45809</v>
       </c>
@@ -7768,7 +7797,7 @@
         <v>0.4375</v>
       </c>
       <c r="D107" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E107" s="11">
         <v>60.7</v>
@@ -7786,7 +7815,7 @@
         <v>80.900000000000006</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9">
       <c r="A108" s="9">
         <v>45839</v>
       </c>
@@ -7797,7 +7826,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D108" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E108" s="11">
         <v>59.2</v>
@@ -7815,7 +7844,7 @@
         <v>71.900000000000006</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9">
       <c r="A109" s="9">
         <v>45870</v>
       </c>
@@ -7826,7 +7855,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D109" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E109" s="11">
         <v>59.3</v>
@@ -7844,7 +7873,7 @@
         <v>79.2</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9">
       <c r="A110" s="9">
         <v>45901</v>
       </c>
@@ -7855,7 +7884,7 @@
         <v>0.4201388888888889</v>
       </c>
       <c r="D110" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E110" s="11">
         <v>57.4</v>
@@ -7873,7 +7902,7 @@
         <v>75.5</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9">
       <c r="A111" s="9">
         <v>45931</v>
       </c>
@@ -7884,7 +7913,7 @@
         <v>0.44444444444444442</v>
       </c>
       <c r="D111" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E111" s="11">
         <v>57.4</v>
@@ -7902,7 +7931,7 @@
         <v>73.2</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9">
       <c r="A112" s="9">
         <v>45962</v>
       </c>
@@ -7913,7 +7942,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D112" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E112" s="11">
         <v>55.7</v>
@@ -7931,7 +7960,7 @@
         <v>70.8</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9">
       <c r="A113" s="9">
         <v>45992</v>
       </c>
@@ -7942,7 +7971,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D113" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E113" s="11">
         <v>54.2</v>
@@ -7960,7 +7989,7 @@
         <v>62.9</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9">
       <c r="A114" s="9">
         <v>46023</v>
       </c>
@@ -7971,7 +8000,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D114" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E114" s="11">
         <v>59.6</v>
@@ -7989,7 +8018,7 @@
         <v>71.3</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9">
       <c r="A115" s="9">
         <v>46054</v>
       </c>
@@ -8000,7 +8029,7 @@
         <v>0.45833333333333331</v>
       </c>
       <c r="D115" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E115" s="11">
         <v>61.5</v>
@@ -8018,7 +8047,7 @@
         <v>67.8</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9">
       <c r="A116" s="9">
         <v>46082</v>
       </c>
@@ -8029,7 +8058,7 @@
         <v>0.39583333333333331</v>
       </c>
       <c r="D116" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E116" s="11">
         <v>65.7</v>
@@ -8047,7 +8076,7 @@
         <v>76.2</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9">
       <c r="A117" s="9">
         <v>46113</v>
       </c>
@@ -8058,7 +8087,7 @@
         <v>0.41666666666666669</v>
       </c>
       <c r="D117" s="10" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E117" s="11">
         <v>69.900000000000006</v>
@@ -8074,6 +8103,35 @@
       </c>
       <c r="I117" s="12">
         <v>74.7</v>
+      </c>
+    </row>
+    <row r="118" spans="1:9">
+      <c r="A118" s="9">
+        <v>46143</v>
+      </c>
+      <c r="B118" s="9">
+        <v>46175</v>
+      </c>
+      <c r="C118" s="15">
+        <v>0.41666666666666669</v>
+      </c>
+      <c r="D118" s="10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E118" s="11">
+        <v>69.5</v>
+      </c>
+      <c r="F118" s="12">
+        <v>69.400000000000006</v>
+      </c>
+      <c r="G118" s="12">
+        <v>70.7</v>
+      </c>
+      <c r="H118" s="12">
+        <v>96</v>
+      </c>
+      <c r="I118" s="12">
+        <v>84.1</v>
       </c>
     </row>
   </sheetData>
@@ -8086,17 +8144,17 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F1E55565-0C4A-423B-A75C-9DC33F6F8AE5}">
   <dimension ref="B2:K3"/>
-  <sheetFormatPr defaultColWidth="8.8984375" defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4"/>
   <cols>
-    <col min="2" max="2" width="10.5" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="2" spans="2:11">
       <c r="B2" s="3" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1"/>
@@ -8107,12 +8165,12 @@
       <c r="J2" s="1"/>
       <c r="K2" s="1"/>
     </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.4">
+    <row r="3" spans="2:11">
       <c r="B3" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>9</v>
-      </c>
-      <c r="C3" t="s">
-        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -8127,7 +8185,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{86A53279-3D0D-4247-AAE5-068BE8617509}">
   <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="13.8"/>
   <cols>
     <col min="1" max="16384" width="9" style="13"/>
   </cols>
